--- a/packages/server/src/arpa_reporter/data/treasury/project211214BulkUpload.xlsx
+++ b/packages/server/src/arpa_reporter/data/treasury/project211214BulkUpload.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29622"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mac\Home\Documents\Projects\arpa-reporter\packages\server\src\arpa_reporter\data\treasury\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kgu82\Desktop\SLFRFBulkUploadTemplates\SLFRFBulkUploadTemplates\SLFRFBulkUploadTemplates\SLFRFBulkUploadTemplates\Quarter 4 2025 Project Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23228BC-57F6-4C3D-AF06-B79664DC546C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{EF293074-3F2D-45CA-99F3-B01D8AD0FDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D2FF0F8-1CB3-4160-A6B0-E9158F32B32F}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22875" windowHeight="13141" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -539,7 +539,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -610,12 +610,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -717,7 +723,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -958,7 +964,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AL1000"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="53" style="4" customWidth="1"/>
     <col min="2" max="5" width="35.625" style="4" customWidth="1"/>
@@ -974,7 +980,7 @@
     <col min="39" max="16384" width="12.625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:38" ht="13.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1016,7 +1022,7 @@
       <c r="AK1" s="6"/>
       <c r="AL1" s="6"/>
     </row>
-    <row r="2" spans="1:38" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:38" ht="24.95" customHeight="1">
       <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
@@ -1058,7 +1064,7 @@
       <c r="AK2" s="6"/>
       <c r="AL2" s="6"/>
     </row>
-    <row r="3" spans="1:38" ht="246.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:38" ht="246.95" customHeight="1">
       <c r="A3" s="13" t="s">
         <v>2</v>
       </c>
@@ -1100,7 +1106,7 @@
       <c r="AK3" s="6"/>
       <c r="AL3" s="6"/>
     </row>
-    <row r="4" spans="1:38" ht="54.6" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:38" ht="54.6" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1216,7 +1222,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:38" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>41</v>
       </c>
@@ -1332,7 +1338,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="51" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:38" ht="52.9">
       <c r="A6" s="1" t="s">
         <v>45</v>
       </c>
@@ -1448,7 +1454,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:38" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:38" ht="409.6">
       <c r="A7" s="1" t="s">
         <v>82</v>
       </c>
@@ -1564,7 +1570,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:38" ht="60.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:38" ht="60.75" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1603,7 +1609,7 @@
       <c r="AK8" s="6"/>
       <c r="AL8" s="6"/>
     </row>
-    <row r="9" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:38" ht="13.15">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1643,7 +1649,7 @@
       <c r="AK9" s="6"/>
       <c r="AL9" s="6"/>
     </row>
-    <row r="10" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:38" ht="13.15">
       <c r="A10" s="14"/>
       <c r="B10" s="14"/>
       <c r="C10" s="3"/>
@@ -1683,7 +1689,7 @@
       <c r="AK10" s="6"/>
       <c r="AL10" s="6"/>
     </row>
-    <row r="11" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:38" ht="13.15">
       <c r="A11" s="15"/>
       <c r="B11" s="15"/>
       <c r="C11" s="3"/>
@@ -1723,7 +1729,7 @@
       <c r="AK11" s="6"/>
       <c r="AL11" s="6"/>
     </row>
-    <row r="12" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:38" ht="13.15">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -1763,7 +1769,7 @@
       <c r="AK12" s="6"/>
       <c r="AL12" s="6"/>
     </row>
-    <row r="13" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:38" ht="13.15">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -1803,7 +1809,7 @@
       <c r="AK13" s="6"/>
       <c r="AL13" s="6"/>
     </row>
-    <row r="14" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:38" ht="13.15">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -1843,7 +1849,7 @@
       <c r="AK14" s="6"/>
       <c r="AL14" s="6"/>
     </row>
-    <row r="15" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:38" ht="13.15">
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -1883,7 +1889,7 @@
       <c r="AK15" s="6"/>
       <c r="AL15" s="6"/>
     </row>
-    <row r="16" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:38" ht="13.15">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -1923,7 +1929,7 @@
       <c r="AK16" s="6"/>
       <c r="AL16" s="6"/>
     </row>
-    <row r="17" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:38" ht="13.15">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1963,7 +1969,7 @@
       <c r="AK17" s="6"/>
       <c r="AL17" s="6"/>
     </row>
-    <row r="18" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:38" ht="13.15">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -2003,7 +2009,7 @@
       <c r="AK18" s="6"/>
       <c r="AL18" s="6"/>
     </row>
-    <row r="19" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:38" ht="13.15">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -2043,7 +2049,7 @@
       <c r="AK19" s="6"/>
       <c r="AL19" s="6"/>
     </row>
-    <row r="20" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:38" ht="13.15">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -2083,7 +2089,7 @@
       <c r="AK20" s="6"/>
       <c r="AL20" s="6"/>
     </row>
-    <row r="21" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:38" ht="15.95" customHeight="1">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -2123,7 +2129,7 @@
       <c r="AK21" s="6"/>
       <c r="AL21" s="6"/>
     </row>
-    <row r="22" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:38" ht="15.95" customHeight="1">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -2163,7 +2169,7 @@
       <c r="AK22" s="6"/>
       <c r="AL22" s="6"/>
     </row>
-    <row r="23" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:38" ht="15.95" customHeight="1">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -2203,7 +2209,7 @@
       <c r="AK23" s="6"/>
       <c r="AL23" s="6"/>
     </row>
-    <row r="24" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:38" ht="15.95" customHeight="1">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -2243,7 +2249,7 @@
       <c r="AK24" s="6"/>
       <c r="AL24" s="6"/>
     </row>
-    <row r="25" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:38" ht="15.95" customHeight="1">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -2283,7 +2289,7 @@
       <c r="AK25" s="6"/>
       <c r="AL25" s="6"/>
     </row>
-    <row r="26" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:38" ht="15.95" customHeight="1">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -2323,7 +2329,7 @@
       <c r="AK26" s="6"/>
       <c r="AL26" s="6"/>
     </row>
-    <row r="27" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:38" ht="15.95" customHeight="1">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -2363,7 +2369,7 @@
       <c r="AK27" s="6"/>
       <c r="AL27" s="6"/>
     </row>
-    <row r="28" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:38" ht="15.95" customHeight="1">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -2403,7 +2409,7 @@
       <c r="AK28" s="6"/>
       <c r="AL28" s="6"/>
     </row>
-    <row r="29" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:38" ht="15.95" customHeight="1">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -2443,7 +2449,7 @@
       <c r="AK29" s="6"/>
       <c r="AL29" s="6"/>
     </row>
-    <row r="30" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:38" ht="15.95" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -2483,7 +2489,7 @@
       <c r="AK30" s="6"/>
       <c r="AL30" s="6"/>
     </row>
-    <row r="31" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:38" ht="15.95" customHeight="1">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -2523,7 +2529,7 @@
       <c r="AK31" s="6"/>
       <c r="AL31" s="6"/>
     </row>
-    <row r="32" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:38" ht="15.95" customHeight="1">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -2563,7 +2569,7 @@
       <c r="AK32" s="6"/>
       <c r="AL32" s="6"/>
     </row>
-    <row r="33" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:38" ht="15.95" customHeight="1">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -2603,7 +2609,7 @@
       <c r="AK33" s="6"/>
       <c r="AL33" s="6"/>
     </row>
-    <row r="34" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:38" ht="15.95" customHeight="1">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -2643,7 +2649,7 @@
       <c r="AK34" s="6"/>
       <c r="AL34" s="6"/>
     </row>
-    <row r="35" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:38" ht="15.95" customHeight="1">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -2683,7 +2689,7 @@
       <c r="AK35" s="6"/>
       <c r="AL35" s="6"/>
     </row>
-    <row r="36" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:38" ht="15.95" customHeight="1">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -2723,7 +2729,7 @@
       <c r="AK36" s="6"/>
       <c r="AL36" s="6"/>
     </row>
-    <row r="37" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:38" ht="15.95" customHeight="1">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -2763,7 +2769,7 @@
       <c r="AK37" s="6"/>
       <c r="AL37" s="6"/>
     </row>
-    <row r="38" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:38" ht="15.95" customHeight="1">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -2803,7 +2809,7 @@
       <c r="AK38" s="6"/>
       <c r="AL38" s="6"/>
     </row>
-    <row r="39" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:38" ht="15.95" customHeight="1">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -2843,7 +2849,7 @@
       <c r="AK39" s="6"/>
       <c r="AL39" s="6"/>
     </row>
-    <row r="40" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:38" ht="15.95" customHeight="1">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -2883,7 +2889,7 @@
       <c r="AK40" s="6"/>
       <c r="AL40" s="6"/>
     </row>
-    <row r="41" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:38" ht="15.95" customHeight="1">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -2923,7 +2929,7 @@
       <c r="AK41" s="6"/>
       <c r="AL41" s="6"/>
     </row>
-    <row r="42" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:38" ht="15.95" customHeight="1">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -2963,7 +2969,7 @@
       <c r="AK42" s="6"/>
       <c r="AL42" s="6"/>
     </row>
-    <row r="43" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:38" ht="15.95" customHeight="1">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -3003,7 +3009,7 @@
       <c r="AK43" s="6"/>
       <c r="AL43" s="6"/>
     </row>
-    <row r="44" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:38" ht="15.95" customHeight="1">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -3043,7 +3049,7 @@
       <c r="AK44" s="6"/>
       <c r="AL44" s="6"/>
     </row>
-    <row r="45" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:38" ht="15.95" customHeight="1">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -3083,7 +3089,7 @@
       <c r="AK45" s="6"/>
       <c r="AL45" s="6"/>
     </row>
-    <row r="46" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:38" ht="15.95" customHeight="1">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -3123,7 +3129,7 @@
       <c r="AK46" s="6"/>
       <c r="AL46" s="6"/>
     </row>
-    <row r="47" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:38" ht="15.95" customHeight="1">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -3163,7 +3169,7 @@
       <c r="AK47" s="6"/>
       <c r="AL47" s="6"/>
     </row>
-    <row r="48" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:38" ht="15.95" customHeight="1">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -3203,7 +3209,7 @@
       <c r="AK48" s="6"/>
       <c r="AL48" s="6"/>
     </row>
-    <row r="49" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:38" ht="15.95" customHeight="1">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -3243,7 +3249,7 @@
       <c r="AK49" s="6"/>
       <c r="AL49" s="6"/>
     </row>
-    <row r="50" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:38" ht="15.95" customHeight="1">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -3283,7 +3289,7 @@
       <c r="AK50" s="6"/>
       <c r="AL50" s="6"/>
     </row>
-    <row r="51" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:38" ht="15.95" customHeight="1">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -3323,7 +3329,7 @@
       <c r="AK51" s="6"/>
       <c r="AL51" s="6"/>
     </row>
-    <row r="52" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:38" ht="15.95" customHeight="1">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -3363,7 +3369,7 @@
       <c r="AK52" s="6"/>
       <c r="AL52" s="6"/>
     </row>
-    <row r="53" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:38" ht="15.95" customHeight="1">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -3403,7 +3409,7 @@
       <c r="AK53" s="6"/>
       <c r="AL53" s="6"/>
     </row>
-    <row r="54" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:38" ht="15.95" customHeight="1">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -3443,7 +3449,7 @@
       <c r="AK54" s="6"/>
       <c r="AL54" s="6"/>
     </row>
-    <row r="55" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:38" ht="15.95" customHeight="1">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -3483,7 +3489,7 @@
       <c r="AK55" s="6"/>
       <c r="AL55" s="6"/>
     </row>
-    <row r="56" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:38" ht="15.95" customHeight="1">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -3523,7 +3529,7 @@
       <c r="AK56" s="6"/>
       <c r="AL56" s="6"/>
     </row>
-    <row r="57" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:38" ht="15.95" customHeight="1">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -3563,7 +3569,7 @@
       <c r="AK57" s="6"/>
       <c r="AL57" s="6"/>
     </row>
-    <row r="58" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:38" ht="15.95" customHeight="1">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -3603,7 +3609,7 @@
       <c r="AK58" s="6"/>
       <c r="AL58" s="6"/>
     </row>
-    <row r="59" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:38" ht="15.95" customHeight="1">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -3643,7 +3649,7 @@
       <c r="AK59" s="6"/>
       <c r="AL59" s="6"/>
     </row>
-    <row r="60" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:38" ht="15.95" customHeight="1">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -3683,7 +3689,7 @@
       <c r="AK60" s="6"/>
       <c r="AL60" s="6"/>
     </row>
-    <row r="61" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:38" ht="15.95" customHeight="1">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -3723,7 +3729,7 @@
       <c r="AK61" s="6"/>
       <c r="AL61" s="6"/>
     </row>
-    <row r="62" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:38" ht="15.95" customHeight="1">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -3763,7 +3769,7 @@
       <c r="AK62" s="6"/>
       <c r="AL62" s="6"/>
     </row>
-    <row r="63" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:38" ht="15.95" customHeight="1">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -3803,7 +3809,7 @@
       <c r="AK63" s="6"/>
       <c r="AL63" s="6"/>
     </row>
-    <row r="64" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:38" ht="15.95" customHeight="1">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -3843,7 +3849,7 @@
       <c r="AK64" s="6"/>
       <c r="AL64" s="6"/>
     </row>
-    <row r="65" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:38" ht="15.95" customHeight="1">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -3883,7 +3889,7 @@
       <c r="AK65" s="6"/>
       <c r="AL65" s="6"/>
     </row>
-    <row r="66" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:38" ht="15.95" customHeight="1">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -3923,7 +3929,7 @@
       <c r="AK66" s="6"/>
       <c r="AL66" s="6"/>
     </row>
-    <row r="67" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:38" ht="15.95" customHeight="1">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -3963,7 +3969,7 @@
       <c r="AK67" s="6"/>
       <c r="AL67" s="6"/>
     </row>
-    <row r="68" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:38" ht="15.95" customHeight="1">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -4003,7 +4009,7 @@
       <c r="AK68" s="6"/>
       <c r="AL68" s="6"/>
     </row>
-    <row r="69" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:38" ht="15.95" customHeight="1">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -4043,7 +4049,7 @@
       <c r="AK69" s="6"/>
       <c r="AL69" s="6"/>
     </row>
-    <row r="70" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:38" ht="15.95" customHeight="1">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -4083,7 +4089,7 @@
       <c r="AK70" s="6"/>
       <c r="AL70" s="6"/>
     </row>
-    <row r="71" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:38" ht="15.95" customHeight="1">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -4123,7 +4129,7 @@
       <c r="AK71" s="6"/>
       <c r="AL71" s="6"/>
     </row>
-    <row r="72" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:38" ht="15.95" customHeight="1">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -4163,7 +4169,7 @@
       <c r="AK72" s="6"/>
       <c r="AL72" s="6"/>
     </row>
-    <row r="73" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:38" ht="15.95" customHeight="1">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -4203,7 +4209,7 @@
       <c r="AK73" s="6"/>
       <c r="AL73" s="6"/>
     </row>
-    <row r="74" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:38" ht="15.95" customHeight="1">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -4243,7 +4249,7 @@
       <c r="AK74" s="6"/>
       <c r="AL74" s="6"/>
     </row>
-    <row r="75" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:38" ht="15.95" customHeight="1">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -4283,7 +4289,7 @@
       <c r="AK75" s="6"/>
       <c r="AL75" s="6"/>
     </row>
-    <row r="76" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:38" ht="15.95" customHeight="1">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -4323,7 +4329,7 @@
       <c r="AK76" s="6"/>
       <c r="AL76" s="6"/>
     </row>
-    <row r="77" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:38" ht="15.95" customHeight="1">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -4363,7 +4369,7 @@
       <c r="AK77" s="6"/>
       <c r="AL77" s="6"/>
     </row>
-    <row r="78" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:38" ht="15.95" customHeight="1">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -4403,7 +4409,7 @@
       <c r="AK78" s="6"/>
       <c r="AL78" s="6"/>
     </row>
-    <row r="79" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:38" ht="15.95" customHeight="1">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -4443,7 +4449,7 @@
       <c r="AK79" s="6"/>
       <c r="AL79" s="6"/>
     </row>
-    <row r="80" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:38" ht="15.95" customHeight="1">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -4483,7 +4489,7 @@
       <c r="AK80" s="6"/>
       <c r="AL80" s="6"/>
     </row>
-    <row r="81" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:38" ht="15.95" customHeight="1">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -4523,7 +4529,7 @@
       <c r="AK81" s="6"/>
       <c r="AL81" s="6"/>
     </row>
-    <row r="82" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:38" ht="15.95" customHeight="1">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -4563,7 +4569,7 @@
       <c r="AK82" s="6"/>
       <c r="AL82" s="6"/>
     </row>
-    <row r="83" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:38" ht="15.95" customHeight="1">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -4603,7 +4609,7 @@
       <c r="AK83" s="6"/>
       <c r="AL83" s="6"/>
     </row>
-    <row r="84" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:38" ht="15.95" customHeight="1">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -4643,7 +4649,7 @@
       <c r="AK84" s="6"/>
       <c r="AL84" s="6"/>
     </row>
-    <row r="85" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:38" ht="15.95" customHeight="1">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -4683,7 +4689,7 @@
       <c r="AK85" s="6"/>
       <c r="AL85" s="6"/>
     </row>
-    <row r="86" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:38" ht="15.95" customHeight="1">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -4723,7 +4729,7 @@
       <c r="AK86" s="6"/>
       <c r="AL86" s="6"/>
     </row>
-    <row r="87" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:38" ht="15.95" customHeight="1">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -4763,7 +4769,7 @@
       <c r="AK87" s="6"/>
       <c r="AL87" s="6"/>
     </row>
-    <row r="88" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:38" ht="15.95" customHeight="1">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -4803,7 +4809,7 @@
       <c r="AK88" s="6"/>
       <c r="AL88" s="6"/>
     </row>
-    <row r="89" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:38" ht="15.95" customHeight="1">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -4843,7 +4849,7 @@
       <c r="AK89" s="6"/>
       <c r="AL89" s="6"/>
     </row>
-    <row r="90" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:38" ht="15.95" customHeight="1">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -4883,7 +4889,7 @@
       <c r="AK90" s="6"/>
       <c r="AL90" s="6"/>
     </row>
-    <row r="91" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:38" ht="15.95" customHeight="1">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -4923,7 +4929,7 @@
       <c r="AK91" s="6"/>
       <c r="AL91" s="6"/>
     </row>
-    <row r="92" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:38" ht="15.95" customHeight="1">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -4963,7 +4969,7 @@
       <c r="AK92" s="6"/>
       <c r="AL92" s="6"/>
     </row>
-    <row r="93" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:38" ht="15.95" customHeight="1">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -5003,7 +5009,7 @@
       <c r="AK93" s="6"/>
       <c r="AL93" s="6"/>
     </row>
-    <row r="94" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:38" ht="15.95" customHeight="1">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -5043,7 +5049,7 @@
       <c r="AK94" s="6"/>
       <c r="AL94" s="6"/>
     </row>
-    <row r="95" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:38" ht="15.95" customHeight="1">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -5083,7 +5089,7 @@
       <c r="AK95" s="6"/>
       <c r="AL95" s="6"/>
     </row>
-    <row r="96" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:38" ht="15.95" customHeight="1">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -5123,7 +5129,7 @@
       <c r="AK96" s="6"/>
       <c r="AL96" s="6"/>
     </row>
-    <row r="97" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:38" ht="15.95" customHeight="1">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -5163,7 +5169,7 @@
       <c r="AK97" s="6"/>
       <c r="AL97" s="6"/>
     </row>
-    <row r="98" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:38" ht="15.95" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -5203,7 +5209,7 @@
       <c r="AK98" s="6"/>
       <c r="AL98" s="6"/>
     </row>
-    <row r="99" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:38" ht="15.95" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -5243,7 +5249,7 @@
       <c r="AK99" s="6"/>
       <c r="AL99" s="6"/>
     </row>
-    <row r="100" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:38" ht="15.95" customHeight="1">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -5283,7 +5289,7 @@
       <c r="AK100" s="6"/>
       <c r="AL100" s="6"/>
     </row>
-    <row r="101" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:38" ht="15.95" customHeight="1">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -5323,7 +5329,7 @@
       <c r="AK101" s="6"/>
       <c r="AL101" s="6"/>
     </row>
-    <row r="102" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:38" ht="15.95" customHeight="1">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -5363,7 +5369,7 @@
       <c r="AK102" s="6"/>
       <c r="AL102" s="6"/>
     </row>
-    <row r="103" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:38" ht="15.95" customHeight="1">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -5403,7 +5409,7 @@
       <c r="AK103" s="6"/>
       <c r="AL103" s="6"/>
     </row>
-    <row r="104" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:38" ht="15.95" customHeight="1">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -5443,7 +5449,7 @@
       <c r="AK104" s="6"/>
       <c r="AL104" s="6"/>
     </row>
-    <row r="105" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:38" ht="15.95" customHeight="1">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -5483,7 +5489,7 @@
       <c r="AK105" s="6"/>
       <c r="AL105" s="6"/>
     </row>
-    <row r="106" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:38" ht="15.95" customHeight="1">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -5523,7 +5529,7 @@
       <c r="AK106" s="6"/>
       <c r="AL106" s="6"/>
     </row>
-    <row r="107" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:38" ht="15.95" customHeight="1">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -5563,7 +5569,7 @@
       <c r="AK107" s="6"/>
       <c r="AL107" s="6"/>
     </row>
-    <row r="108" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:38" ht="15.95" customHeight="1">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -5603,7 +5609,7 @@
       <c r="AK108" s="6"/>
       <c r="AL108" s="6"/>
     </row>
-    <row r="109" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:38" ht="15.95" customHeight="1">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -5643,7 +5649,7 @@
       <c r="AK109" s="6"/>
       <c r="AL109" s="6"/>
     </row>
-    <row r="110" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:38" ht="15.95" customHeight="1">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -5683,7 +5689,7 @@
       <c r="AK110" s="6"/>
       <c r="AL110" s="6"/>
     </row>
-    <row r="111" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:38" ht="15.95" customHeight="1">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -5723,7 +5729,7 @@
       <c r="AK111" s="6"/>
       <c r="AL111" s="6"/>
     </row>
-    <row r="112" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:38" ht="15.95" customHeight="1">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -5763,7 +5769,7 @@
       <c r="AK112" s="6"/>
       <c r="AL112" s="6"/>
     </row>
-    <row r="113" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:38" ht="15.95" customHeight="1">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -5803,7 +5809,7 @@
       <c r="AK113" s="6"/>
       <c r="AL113" s="6"/>
     </row>
-    <row r="114" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:38" ht="15.95" customHeight="1">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -5843,7 +5849,7 @@
       <c r="AK114" s="6"/>
       <c r="AL114" s="6"/>
     </row>
-    <row r="115" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:38" ht="15.95" customHeight="1">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -5883,7 +5889,7 @@
       <c r="AK115" s="6"/>
       <c r="AL115" s="6"/>
     </row>
-    <row r="116" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:38" ht="15.95" customHeight="1">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -5923,7 +5929,7 @@
       <c r="AK116" s="6"/>
       <c r="AL116" s="6"/>
     </row>
-    <row r="117" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:38" ht="15.95" customHeight="1">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -5963,7 +5969,7 @@
       <c r="AK117" s="6"/>
       <c r="AL117" s="6"/>
     </row>
-    <row r="118" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:38" ht="15.95" customHeight="1">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -6003,7 +6009,7 @@
       <c r="AK118" s="6"/>
       <c r="AL118" s="6"/>
     </row>
-    <row r="119" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:38" ht="15.95" customHeight="1">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -6043,7 +6049,7 @@
       <c r="AK119" s="6"/>
       <c r="AL119" s="6"/>
     </row>
-    <row r="120" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:38" ht="15.95" customHeight="1">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -6083,7 +6089,7 @@
       <c r="AK120" s="6"/>
       <c r="AL120" s="6"/>
     </row>
-    <row r="121" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:38" ht="15.95" customHeight="1">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -6123,7 +6129,7 @@
       <c r="AK121" s="6"/>
       <c r="AL121" s="6"/>
     </row>
-    <row r="122" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:38" ht="15.95" customHeight="1">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -6163,7 +6169,7 @@
       <c r="AK122" s="6"/>
       <c r="AL122" s="6"/>
     </row>
-    <row r="123" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:38" ht="15.95" customHeight="1">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -6203,7 +6209,7 @@
       <c r="AK123" s="6"/>
       <c r="AL123" s="6"/>
     </row>
-    <row r="124" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:38" ht="15.95" customHeight="1">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -6243,7 +6249,7 @@
       <c r="AK124" s="6"/>
       <c r="AL124" s="6"/>
     </row>
-    <row r="125" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:38" ht="15.95" customHeight="1">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -6283,7 +6289,7 @@
       <c r="AK125" s="6"/>
       <c r="AL125" s="6"/>
     </row>
-    <row r="126" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:38" ht="15.95" customHeight="1">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -6323,7 +6329,7 @@
       <c r="AK126" s="6"/>
       <c r="AL126" s="6"/>
     </row>
-    <row r="127" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:38" ht="15.95" customHeight="1">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -6363,7 +6369,7 @@
       <c r="AK127" s="6"/>
       <c r="AL127" s="6"/>
     </row>
-    <row r="128" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:38" ht="15.95" customHeight="1">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -6403,7 +6409,7 @@
       <c r="AK128" s="6"/>
       <c r="AL128" s="6"/>
     </row>
-    <row r="129" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:38" ht="15.95" customHeight="1">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -6443,7 +6449,7 @@
       <c r="AK129" s="6"/>
       <c r="AL129" s="6"/>
     </row>
-    <row r="130" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:38" ht="15.95" customHeight="1">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -6483,7 +6489,7 @@
       <c r="AK130" s="6"/>
       <c r="AL130" s="6"/>
     </row>
-    <row r="131" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:38" ht="15.95" customHeight="1">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -6523,7 +6529,7 @@
       <c r="AK131" s="6"/>
       <c r="AL131" s="6"/>
     </row>
-    <row r="132" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:38" ht="15.95" customHeight="1">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -6563,7 +6569,7 @@
       <c r="AK132" s="6"/>
       <c r="AL132" s="6"/>
     </row>
-    <row r="133" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:38" ht="15.95" customHeight="1">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -6603,7 +6609,7 @@
       <c r="AK133" s="6"/>
       <c r="AL133" s="6"/>
     </row>
-    <row r="134" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:38" ht="15.95" customHeight="1">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -6643,7 +6649,7 @@
       <c r="AK134" s="6"/>
       <c r="AL134" s="6"/>
     </row>
-    <row r="135" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:38" ht="15.95" customHeight="1">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -6683,7 +6689,7 @@
       <c r="AK135" s="6"/>
       <c r="AL135" s="6"/>
     </row>
-    <row r="136" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:38" ht="15.95" customHeight="1">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -6723,7 +6729,7 @@
       <c r="AK136" s="6"/>
       <c r="AL136" s="6"/>
     </row>
-    <row r="137" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:38" ht="15.95" customHeight="1">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -6763,7 +6769,7 @@
       <c r="AK137" s="6"/>
       <c r="AL137" s="6"/>
     </row>
-    <row r="138" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:38" ht="15.95" customHeight="1">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -6803,7 +6809,7 @@
       <c r="AK138" s="6"/>
       <c r="AL138" s="6"/>
     </row>
-    <row r="139" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:38" ht="15.95" customHeight="1">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -6843,7 +6849,7 @@
       <c r="AK139" s="6"/>
       <c r="AL139" s="6"/>
     </row>
-    <row r="140" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:38" ht="15.95" customHeight="1">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -6883,7 +6889,7 @@
       <c r="AK140" s="6"/>
       <c r="AL140" s="6"/>
     </row>
-    <row r="141" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:38" ht="15.95" customHeight="1">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -6923,7 +6929,7 @@
       <c r="AK141" s="6"/>
       <c r="AL141" s="6"/>
     </row>
-    <row r="142" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:38" ht="15.95" customHeight="1">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -6963,7 +6969,7 @@
       <c r="AK142" s="6"/>
       <c r="AL142" s="6"/>
     </row>
-    <row r="143" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:38" ht="15.95" customHeight="1">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -7003,7 +7009,7 @@
       <c r="AK143" s="6"/>
       <c r="AL143" s="6"/>
     </row>
-    <row r="144" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:38" ht="15.95" customHeight="1">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -7043,7 +7049,7 @@
       <c r="AK144" s="6"/>
       <c r="AL144" s="6"/>
     </row>
-    <row r="145" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:38" ht="15.95" customHeight="1">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -7083,7 +7089,7 @@
       <c r="AK145" s="6"/>
       <c r="AL145" s="6"/>
     </row>
-    <row r="146" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:38" ht="15.95" customHeight="1">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -7123,7 +7129,7 @@
       <c r="AK146" s="6"/>
       <c r="AL146" s="6"/>
     </row>
-    <row r="147" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:38" ht="15.95" customHeight="1">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -7163,7 +7169,7 @@
       <c r="AK147" s="6"/>
       <c r="AL147" s="6"/>
     </row>
-    <row r="148" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:38" ht="15.95" customHeight="1">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -7203,7 +7209,7 @@
       <c r="AK148" s="6"/>
       <c r="AL148" s="6"/>
     </row>
-    <row r="149" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:38" ht="15.95" customHeight="1">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -7243,7 +7249,7 @@
       <c r="AK149" s="6"/>
       <c r="AL149" s="6"/>
     </row>
-    <row r="150" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:38" ht="15.95" customHeight="1">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -7283,7 +7289,7 @@
       <c r="AK150" s="6"/>
       <c r="AL150" s="6"/>
     </row>
-    <row r="151" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:38" ht="15.95" customHeight="1">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -7323,7 +7329,7 @@
       <c r="AK151" s="6"/>
       <c r="AL151" s="6"/>
     </row>
-    <row r="152" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:38" ht="15.95" customHeight="1">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -7363,7 +7369,7 @@
       <c r="AK152" s="6"/>
       <c r="AL152" s="6"/>
     </row>
-    <row r="153" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:38" ht="15.95" customHeight="1">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -7403,7 +7409,7 @@
       <c r="AK153" s="6"/>
       <c r="AL153" s="6"/>
     </row>
-    <row r="154" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:38" ht="15.95" customHeight="1">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -7443,7 +7449,7 @@
       <c r="AK154" s="6"/>
       <c r="AL154" s="6"/>
     </row>
-    <row r="155" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:38" ht="15.95" customHeight="1">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -7483,7 +7489,7 @@
       <c r="AK155" s="6"/>
       <c r="AL155" s="6"/>
     </row>
-    <row r="156" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:38" ht="15.95" customHeight="1">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -7523,7 +7529,7 @@
       <c r="AK156" s="6"/>
       <c r="AL156" s="6"/>
     </row>
-    <row r="157" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:38" ht="15.95" customHeight="1">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -7563,7 +7569,7 @@
       <c r="AK157" s="6"/>
       <c r="AL157" s="6"/>
     </row>
-    <row r="158" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:38" ht="15.95" customHeight="1">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -7603,7 +7609,7 @@
       <c r="AK158" s="6"/>
       <c r="AL158" s="6"/>
     </row>
-    <row r="159" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:38" ht="15.95" customHeight="1">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -7643,7 +7649,7 @@
       <c r="AK159" s="6"/>
       <c r="AL159" s="6"/>
     </row>
-    <row r="160" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:38" ht="15.95" customHeight="1">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -7683,7 +7689,7 @@
       <c r="AK160" s="6"/>
       <c r="AL160" s="6"/>
     </row>
-    <row r="161" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:38" ht="15.95" customHeight="1">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -7723,7 +7729,7 @@
       <c r="AK161" s="6"/>
       <c r="AL161" s="6"/>
     </row>
-    <row r="162" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:38" ht="15.95" customHeight="1">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -7763,7 +7769,7 @@
       <c r="AK162" s="6"/>
       <c r="AL162" s="6"/>
     </row>
-    <row r="163" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:38" ht="15.95" customHeight="1">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -7803,7 +7809,7 @@
       <c r="AK163" s="6"/>
       <c r="AL163" s="6"/>
     </row>
-    <row r="164" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:38" ht="15.95" customHeight="1">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -7843,7 +7849,7 @@
       <c r="AK164" s="6"/>
       <c r="AL164" s="6"/>
     </row>
-    <row r="165" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:38" ht="15.95" customHeight="1">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -7883,7 +7889,7 @@
       <c r="AK165" s="6"/>
       <c r="AL165" s="6"/>
     </row>
-    <row r="166" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:38" ht="15.95" customHeight="1">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -7923,7 +7929,7 @@
       <c r="AK166" s="6"/>
       <c r="AL166" s="6"/>
     </row>
-    <row r="167" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:38" ht="15.95" customHeight="1">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -7963,7 +7969,7 @@
       <c r="AK167" s="6"/>
       <c r="AL167" s="6"/>
     </row>
-    <row r="168" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:38" ht="15.95" customHeight="1">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -8003,7 +8009,7 @@
       <c r="AK168" s="6"/>
       <c r="AL168" s="6"/>
     </row>
-    <row r="169" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:38" ht="15.95" customHeight="1">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -8043,7 +8049,7 @@
       <c r="AK169" s="6"/>
       <c r="AL169" s="6"/>
     </row>
-    <row r="170" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:38" ht="15.95" customHeight="1">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -8083,7 +8089,7 @@
       <c r="AK170" s="6"/>
       <c r="AL170" s="6"/>
     </row>
-    <row r="171" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:38" ht="15.95" customHeight="1">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -8123,7 +8129,7 @@
       <c r="AK171" s="6"/>
       <c r="AL171" s="6"/>
     </row>
-    <row r="172" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:38" ht="15.95" customHeight="1">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -8163,7 +8169,7 @@
       <c r="AK172" s="6"/>
       <c r="AL172" s="6"/>
     </row>
-    <row r="173" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:38" ht="15.95" customHeight="1">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -8203,7 +8209,7 @@
       <c r="AK173" s="6"/>
       <c r="AL173" s="6"/>
     </row>
-    <row r="174" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:38" ht="15.95" customHeight="1">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -8243,7 +8249,7 @@
       <c r="AK174" s="6"/>
       <c r="AL174" s="6"/>
     </row>
-    <row r="175" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:38" ht="15.95" customHeight="1">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -8283,7 +8289,7 @@
       <c r="AK175" s="6"/>
       <c r="AL175" s="6"/>
     </row>
-    <row r="176" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:38" ht="15.95" customHeight="1">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -8323,7 +8329,7 @@
       <c r="AK176" s="6"/>
       <c r="AL176" s="6"/>
     </row>
-    <row r="177" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:38" ht="15.95" customHeight="1">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -8363,7 +8369,7 @@
       <c r="AK177" s="6"/>
       <c r="AL177" s="6"/>
     </row>
-    <row r="178" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:38" ht="15.95" customHeight="1">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -8403,7 +8409,7 @@
       <c r="AK178" s="6"/>
       <c r="AL178" s="6"/>
     </row>
-    <row r="179" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:38" ht="15.95" customHeight="1">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -8443,7 +8449,7 @@
       <c r="AK179" s="6"/>
       <c r="AL179" s="6"/>
     </row>
-    <row r="180" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:38" ht="15.95" customHeight="1">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -8483,7 +8489,7 @@
       <c r="AK180" s="6"/>
       <c r="AL180" s="6"/>
     </row>
-    <row r="181" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:38" ht="15.95" customHeight="1">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -8523,7 +8529,7 @@
       <c r="AK181" s="6"/>
       <c r="AL181" s="6"/>
     </row>
-    <row r="182" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:38" ht="15.95" customHeight="1">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -8563,7 +8569,7 @@
       <c r="AK182" s="6"/>
       <c r="AL182" s="6"/>
     </row>
-    <row r="183" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:38" ht="15.95" customHeight="1">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -8603,7 +8609,7 @@
       <c r="AK183" s="6"/>
       <c r="AL183" s="6"/>
     </row>
-    <row r="184" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:38" ht="15.95" customHeight="1">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -8643,7 +8649,7 @@
       <c r="AK184" s="6"/>
       <c r="AL184" s="6"/>
     </row>
-    <row r="185" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:38" ht="15.95" customHeight="1">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -8683,7 +8689,7 @@
       <c r="AK185" s="6"/>
       <c r="AL185" s="6"/>
     </row>
-    <row r="186" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:38" ht="15.95" customHeight="1">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -8723,7 +8729,7 @@
       <c r="AK186" s="6"/>
       <c r="AL186" s="6"/>
     </row>
-    <row r="187" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:38" ht="15.95" customHeight="1">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -8763,7 +8769,7 @@
       <c r="AK187" s="6"/>
       <c r="AL187" s="6"/>
     </row>
-    <row r="188" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:38" ht="15.95" customHeight="1">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -8803,7 +8809,7 @@
       <c r="AK188" s="6"/>
       <c r="AL188" s="6"/>
     </row>
-    <row r="189" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:38" ht="15.95" customHeight="1">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -8843,7 +8849,7 @@
       <c r="AK189" s="6"/>
       <c r="AL189" s="6"/>
     </row>
-    <row r="190" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:38" ht="15.95" customHeight="1">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -8883,7 +8889,7 @@
       <c r="AK190" s="6"/>
       <c r="AL190" s="6"/>
     </row>
-    <row r="191" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:38" ht="15.95" customHeight="1">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -8923,7 +8929,7 @@
       <c r="AK191" s="6"/>
       <c r="AL191" s="6"/>
     </row>
-    <row r="192" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:38" ht="15.95" customHeight="1">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -8963,7 +8969,7 @@
       <c r="AK192" s="6"/>
       <c r="AL192" s="6"/>
     </row>
-    <row r="193" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:38" ht="15.95" customHeight="1">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -9003,7 +9009,7 @@
       <c r="AK193" s="6"/>
       <c r="AL193" s="6"/>
     </row>
-    <row r="194" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:38" ht="15.95" customHeight="1">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -9043,7 +9049,7 @@
       <c r="AK194" s="6"/>
       <c r="AL194" s="6"/>
     </row>
-    <row r="195" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:38" ht="15.95" customHeight="1">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -9083,7 +9089,7 @@
       <c r="AK195" s="6"/>
       <c r="AL195" s="6"/>
     </row>
-    <row r="196" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:38" ht="15.95" customHeight="1">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -9123,7 +9129,7 @@
       <c r="AK196" s="6"/>
       <c r="AL196" s="6"/>
     </row>
-    <row r="197" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:38" ht="15.95" customHeight="1">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -9163,7 +9169,7 @@
       <c r="AK197" s="6"/>
       <c r="AL197" s="6"/>
     </row>
-    <row r="198" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:38" ht="15.95" customHeight="1">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -9203,7 +9209,7 @@
       <c r="AK198" s="6"/>
       <c r="AL198" s="6"/>
     </row>
-    <row r="199" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:38" ht="15.95" customHeight="1">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -9243,7 +9249,7 @@
       <c r="AK199" s="6"/>
       <c r="AL199" s="6"/>
     </row>
-    <row r="200" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:38" ht="15.95" customHeight="1">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -9283,7 +9289,7 @@
       <c r="AK200" s="6"/>
       <c r="AL200" s="6"/>
     </row>
-    <row r="201" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:38" ht="15.95" customHeight="1">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -9323,7 +9329,7 @@
       <c r="AK201" s="6"/>
       <c r="AL201" s="6"/>
     </row>
-    <row r="202" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:38" ht="15.95" customHeight="1">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -9363,7 +9369,7 @@
       <c r="AK202" s="6"/>
       <c r="AL202" s="6"/>
     </row>
-    <row r="203" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:38" ht="15.95" customHeight="1">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -9403,7 +9409,7 @@
       <c r="AK203" s="6"/>
       <c r="AL203" s="6"/>
     </row>
-    <row r="204" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:38" ht="15.95" customHeight="1">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -9443,7 +9449,7 @@
       <c r="AK204" s="6"/>
       <c r="AL204" s="6"/>
     </row>
-    <row r="205" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:38" ht="15.95" customHeight="1">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -9483,7 +9489,7 @@
       <c r="AK205" s="6"/>
       <c r="AL205" s="6"/>
     </row>
-    <row r="206" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:38" ht="15.95" customHeight="1">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -9523,7 +9529,7 @@
       <c r="AK206" s="6"/>
       <c r="AL206" s="6"/>
     </row>
-    <row r="207" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:38" ht="15.95" customHeight="1">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
@@ -9563,7 +9569,7 @@
       <c r="AK207" s="6"/>
       <c r="AL207" s="6"/>
     </row>
-    <row r="208" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:38" ht="15.95" customHeight="1">
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -9603,7 +9609,7 @@
       <c r="AK208" s="6"/>
       <c r="AL208" s="6"/>
     </row>
-    <row r="209" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:38" ht="15.95" customHeight="1">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
@@ -9643,7 +9649,7 @@
       <c r="AK209" s="6"/>
       <c r="AL209" s="6"/>
     </row>
-    <row r="210" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:38" ht="15.95" customHeight="1">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -9683,7 +9689,7 @@
       <c r="AK210" s="6"/>
       <c r="AL210" s="6"/>
     </row>
-    <row r="211" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:38" ht="15.95" customHeight="1">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
@@ -9723,7 +9729,7 @@
       <c r="AK211" s="6"/>
       <c r="AL211" s="6"/>
     </row>
-    <row r="212" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:38" ht="15.95" customHeight="1">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
@@ -9763,7 +9769,7 @@
       <c r="AK212" s="6"/>
       <c r="AL212" s="6"/>
     </row>
-    <row r="213" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:38" ht="15.95" customHeight="1">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
@@ -9803,7 +9809,7 @@
       <c r="AK213" s="6"/>
       <c r="AL213" s="6"/>
     </row>
-    <row r="214" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:38" ht="15.95" customHeight="1">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
@@ -9843,7 +9849,7 @@
       <c r="AK214" s="6"/>
       <c r="AL214" s="6"/>
     </row>
-    <row r="215" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:38" ht="15.95" customHeight="1">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -9883,7 +9889,7 @@
       <c r="AK215" s="6"/>
       <c r="AL215" s="6"/>
     </row>
-    <row r="216" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:38" ht="15.95" customHeight="1">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
@@ -9923,7 +9929,7 @@
       <c r="AK216" s="6"/>
       <c r="AL216" s="6"/>
     </row>
-    <row r="217" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:38" ht="15.95" customHeight="1">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
@@ -9963,7 +9969,7 @@
       <c r="AK217" s="6"/>
       <c r="AL217" s="6"/>
     </row>
-    <row r="218" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:38" ht="15.95" customHeight="1">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
@@ -10003,7 +10009,7 @@
       <c r="AK218" s="6"/>
       <c r="AL218" s="6"/>
     </row>
-    <row r="219" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:38" ht="15.95" customHeight="1">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
@@ -10043,7 +10049,7 @@
       <c r="AK219" s="6"/>
       <c r="AL219" s="6"/>
     </row>
-    <row r="220" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:38" ht="15.95" customHeight="1">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
@@ -10083,7 +10089,7 @@
       <c r="AK220" s="6"/>
       <c r="AL220" s="6"/>
     </row>
-    <row r="221" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:38" ht="15.95" customHeight="1">
       <c r="A221" s="3"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
@@ -10123,7 +10129,7 @@
       <c r="AK221" s="6"/>
       <c r="AL221" s="6"/>
     </row>
-    <row r="222" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:38" ht="15.95" customHeight="1">
       <c r="A222" s="3"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
@@ -10163,7 +10169,7 @@
       <c r="AK222" s="6"/>
       <c r="AL222" s="6"/>
     </row>
-    <row r="223" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:38" ht="15.95" customHeight="1">
       <c r="A223" s="3"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
@@ -10203,7 +10209,7 @@
       <c r="AK223" s="6"/>
       <c r="AL223" s="6"/>
     </row>
-    <row r="224" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:38" ht="15.95" customHeight="1">
       <c r="A224" s="3"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
@@ -10243,7 +10249,7 @@
       <c r="AK224" s="6"/>
       <c r="AL224" s="6"/>
     </row>
-    <row r="225" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:38" ht="15.95" customHeight="1">
       <c r="A225" s="3"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
@@ -10283,7 +10289,7 @@
       <c r="AK225" s="6"/>
       <c r="AL225" s="6"/>
     </row>
-    <row r="226" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:38" ht="15.95" customHeight="1">
       <c r="A226" s="3"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
@@ -10323,7 +10329,7 @@
       <c r="AK226" s="6"/>
       <c r="AL226" s="6"/>
     </row>
-    <row r="227" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:38" ht="15.95" customHeight="1">
       <c r="A227" s="3"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
@@ -10363,7 +10369,7 @@
       <c r="AK227" s="6"/>
       <c r="AL227" s="6"/>
     </row>
-    <row r="228" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:38" ht="15.95" customHeight="1">
       <c r="A228" s="3"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
@@ -10403,7 +10409,7 @@
       <c r="AK228" s="6"/>
       <c r="AL228" s="6"/>
     </row>
-    <row r="229" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:38" ht="15.95" customHeight="1">
       <c r="A229" s="3"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
@@ -10443,7 +10449,7 @@
       <c r="AK229" s="6"/>
       <c r="AL229" s="6"/>
     </row>
-    <row r="230" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:38" ht="15.95" customHeight="1">
       <c r="A230" s="3"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
@@ -10483,7 +10489,7 @@
       <c r="AK230" s="6"/>
       <c r="AL230" s="6"/>
     </row>
-    <row r="231" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:38" ht="15.95" customHeight="1">
       <c r="A231" s="3"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
@@ -10523,7 +10529,7 @@
       <c r="AK231" s="6"/>
       <c r="AL231" s="6"/>
     </row>
-    <row r="232" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:38" ht="15.95" customHeight="1">
       <c r="A232" s="3"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
@@ -10563,7 +10569,7 @@
       <c r="AK232" s="6"/>
       <c r="AL232" s="6"/>
     </row>
-    <row r="233" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:38" ht="15.95" customHeight="1">
       <c r="A233" s="3"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
@@ -10603,7 +10609,7 @@
       <c r="AK233" s="6"/>
       <c r="AL233" s="6"/>
     </row>
-    <row r="234" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:38" ht="15.95" customHeight="1">
       <c r="A234" s="3"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
@@ -10643,7 +10649,7 @@
       <c r="AK234" s="6"/>
       <c r="AL234" s="6"/>
     </row>
-    <row r="235" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:38" ht="15.95" customHeight="1">
       <c r="A235" s="3"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
@@ -10683,7 +10689,7 @@
       <c r="AK235" s="6"/>
       <c r="AL235" s="6"/>
     </row>
-    <row r="236" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:38" ht="15.95" customHeight="1">
       <c r="A236" s="3"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
@@ -10723,7 +10729,7 @@
       <c r="AK236" s="6"/>
       <c r="AL236" s="6"/>
     </row>
-    <row r="237" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:38" ht="15.95" customHeight="1">
       <c r="A237" s="3"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
@@ -10763,7 +10769,7 @@
       <c r="AK237" s="6"/>
       <c r="AL237" s="6"/>
     </row>
-    <row r="238" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:38" ht="15.95" customHeight="1">
       <c r="A238" s="3"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
@@ -10803,7 +10809,7 @@
       <c r="AK238" s="6"/>
       <c r="AL238" s="6"/>
     </row>
-    <row r="239" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:38" ht="15.95" customHeight="1">
       <c r="A239" s="3"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
@@ -10843,7 +10849,7 @@
       <c r="AK239" s="6"/>
       <c r="AL239" s="6"/>
     </row>
-    <row r="240" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:38" ht="15.95" customHeight="1">
       <c r="A240" s="3"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
@@ -10883,7 +10889,7 @@
       <c r="AK240" s="6"/>
       <c r="AL240" s="6"/>
     </row>
-    <row r="241" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:38" ht="15.95" customHeight="1">
       <c r="A241" s="3"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
@@ -10923,7 +10929,7 @@
       <c r="AK241" s="6"/>
       <c r="AL241" s="6"/>
     </row>
-    <row r="242" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:38" ht="15.95" customHeight="1">
       <c r="A242" s="3"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
@@ -10963,7 +10969,7 @@
       <c r="AK242" s="6"/>
       <c r="AL242" s="6"/>
     </row>
-    <row r="243" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:38" ht="15.95" customHeight="1">
       <c r="A243" s="3"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
@@ -11003,7 +11009,7 @@
       <c r="AK243" s="6"/>
       <c r="AL243" s="6"/>
     </row>
-    <row r="244" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:38" ht="15.95" customHeight="1">
       <c r="A244" s="3"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
@@ -11043,7 +11049,7 @@
       <c r="AK244" s="6"/>
       <c r="AL244" s="6"/>
     </row>
-    <row r="245" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:38" ht="15.95" customHeight="1">
       <c r="A245" s="3"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
@@ -11083,7 +11089,7 @@
       <c r="AK245" s="6"/>
       <c r="AL245" s="6"/>
     </row>
-    <row r="246" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:38" ht="15.95" customHeight="1">
       <c r="A246" s="3"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
@@ -11123,7 +11129,7 @@
       <c r="AK246" s="6"/>
       <c r="AL246" s="6"/>
     </row>
-    <row r="247" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:38" ht="15.95" customHeight="1">
       <c r="A247" s="3"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
@@ -11163,7 +11169,7 @@
       <c r="AK247" s="6"/>
       <c r="AL247" s="6"/>
     </row>
-    <row r="248" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:38" ht="15.95" customHeight="1">
       <c r="A248" s="3"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
@@ -11203,7 +11209,7 @@
       <c r="AK248" s="6"/>
       <c r="AL248" s="6"/>
     </row>
-    <row r="249" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:38" ht="15.95" customHeight="1">
       <c r="A249" s="3"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
@@ -11243,7 +11249,7 @@
       <c r="AK249" s="6"/>
       <c r="AL249" s="6"/>
     </row>
-    <row r="250" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:38" ht="15.95" customHeight="1">
       <c r="A250" s="3"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
@@ -11283,7 +11289,7 @@
       <c r="AK250" s="6"/>
       <c r="AL250" s="6"/>
     </row>
-    <row r="251" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:38" ht="15.95" customHeight="1">
       <c r="A251" s="3"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
@@ -11323,7 +11329,7 @@
       <c r="AK251" s="6"/>
       <c r="AL251" s="6"/>
     </row>
-    <row r="252" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:38" ht="15.95" customHeight="1">
       <c r="A252" s="3"/>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
@@ -11363,7 +11369,7 @@
       <c r="AK252" s="6"/>
       <c r="AL252" s="6"/>
     </row>
-    <row r="253" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:38" ht="15.95" customHeight="1">
       <c r="A253" s="3"/>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
@@ -11403,7 +11409,7 @@
       <c r="AK253" s="6"/>
       <c r="AL253" s="6"/>
     </row>
-    <row r="254" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:38" ht="15.95" customHeight="1">
       <c r="A254" s="3"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
@@ -11443,7 +11449,7 @@
       <c r="AK254" s="6"/>
       <c r="AL254" s="6"/>
     </row>
-    <row r="255" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:38" ht="15.95" customHeight="1">
       <c r="A255" s="3"/>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
@@ -11483,7 +11489,7 @@
       <c r="AK255" s="6"/>
       <c r="AL255" s="6"/>
     </row>
-    <row r="256" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:38" ht="15.95" customHeight="1">
       <c r="A256" s="3"/>
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
@@ -11523,7 +11529,7 @@
       <c r="AK256" s="6"/>
       <c r="AL256" s="6"/>
     </row>
-    <row r="257" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:38" ht="15.95" customHeight="1">
       <c r="A257" s="3"/>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
@@ -11563,7 +11569,7 @@
       <c r="AK257" s="6"/>
       <c r="AL257" s="6"/>
     </row>
-    <row r="258" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:38" ht="15.95" customHeight="1">
       <c r="A258" s="3"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
@@ -11603,7 +11609,7 @@
       <c r="AK258" s="6"/>
       <c r="AL258" s="6"/>
     </row>
-    <row r="259" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:38" ht="15.95" customHeight="1">
       <c r="A259" s="3"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
@@ -11643,7 +11649,7 @@
       <c r="AK259" s="6"/>
       <c r="AL259" s="6"/>
     </row>
-    <row r="260" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:38" ht="15.95" customHeight="1">
       <c r="A260" s="3"/>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
@@ -11683,7 +11689,7 @@
       <c r="AK260" s="6"/>
       <c r="AL260" s="6"/>
     </row>
-    <row r="261" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:38" ht="15.95" customHeight="1">
       <c r="A261" s="3"/>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
@@ -11723,7 +11729,7 @@
       <c r="AK261" s="6"/>
       <c r="AL261" s="6"/>
     </row>
-    <row r="262" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:38" ht="15.95" customHeight="1">
       <c r="A262" s="3"/>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
@@ -11763,7 +11769,7 @@
       <c r="AK262" s="6"/>
       <c r="AL262" s="6"/>
     </row>
-    <row r="263" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:38" ht="15.95" customHeight="1">
       <c r="A263" s="3"/>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
@@ -11803,7 +11809,7 @@
       <c r="AK263" s="6"/>
       <c r="AL263" s="6"/>
     </row>
-    <row r="264" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:38" ht="15.95" customHeight="1">
       <c r="A264" s="3"/>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
@@ -11843,7 +11849,7 @@
       <c r="AK264" s="6"/>
       <c r="AL264" s="6"/>
     </row>
-    <row r="265" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:38" ht="15.95" customHeight="1">
       <c r="A265" s="3"/>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
@@ -11883,7 +11889,7 @@
       <c r="AK265" s="6"/>
       <c r="AL265" s="6"/>
     </row>
-    <row r="266" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:38" ht="15.95" customHeight="1">
       <c r="A266" s="3"/>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
@@ -11923,7 +11929,7 @@
       <c r="AK266" s="6"/>
       <c r="AL266" s="6"/>
     </row>
-    <row r="267" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:38" ht="15.95" customHeight="1">
       <c r="A267" s="3"/>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
@@ -11963,7 +11969,7 @@
       <c r="AK267" s="6"/>
       <c r="AL267" s="6"/>
     </row>
-    <row r="268" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:38" ht="15.95" customHeight="1">
       <c r="A268" s="3"/>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
@@ -12003,7 +12009,7 @@
       <c r="AK268" s="6"/>
       <c r="AL268" s="6"/>
     </row>
-    <row r="269" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:38" ht="15.95" customHeight="1">
       <c r="A269" s="3"/>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
@@ -12043,7 +12049,7 @@
       <c r="AK269" s="6"/>
       <c r="AL269" s="6"/>
     </row>
-    <row r="270" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:38" ht="15.95" customHeight="1">
       <c r="A270" s="3"/>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
@@ -12083,7 +12089,7 @@
       <c r="AK270" s="6"/>
       <c r="AL270" s="6"/>
     </row>
-    <row r="271" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:38" ht="15.95" customHeight="1">
       <c r="A271" s="3"/>
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
@@ -12123,7 +12129,7 @@
       <c r="AK271" s="6"/>
       <c r="AL271" s="6"/>
     </row>
-    <row r="272" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:38" ht="15.95" customHeight="1">
       <c r="A272" s="3"/>
       <c r="B272" s="3"/>
       <c r="C272" s="3"/>
@@ -12163,7 +12169,7 @@
       <c r="AK272" s="6"/>
       <c r="AL272" s="6"/>
     </row>
-    <row r="273" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:38" ht="15.95" customHeight="1">
       <c r="A273" s="3"/>
       <c r="B273" s="3"/>
       <c r="C273" s="3"/>
@@ -12203,7 +12209,7 @@
       <c r="AK273" s="6"/>
       <c r="AL273" s="6"/>
     </row>
-    <row r="274" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:38" ht="15.95" customHeight="1">
       <c r="A274" s="3"/>
       <c r="B274" s="3"/>
       <c r="C274" s="3"/>
@@ -12243,7 +12249,7 @@
       <c r="AK274" s="6"/>
       <c r="AL274" s="6"/>
     </row>
-    <row r="275" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:38" ht="15.95" customHeight="1">
       <c r="A275" s="3"/>
       <c r="B275" s="3"/>
       <c r="C275" s="3"/>
@@ -12283,7 +12289,7 @@
       <c r="AK275" s="6"/>
       <c r="AL275" s="6"/>
     </row>
-    <row r="276" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:38" ht="15.95" customHeight="1">
       <c r="A276" s="3"/>
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
@@ -12323,7 +12329,7 @@
       <c r="AK276" s="6"/>
       <c r="AL276" s="6"/>
     </row>
-    <row r="277" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:38" ht="15.95" customHeight="1">
       <c r="A277" s="3"/>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
@@ -12363,7 +12369,7 @@
       <c r="AK277" s="6"/>
       <c r="AL277" s="6"/>
     </row>
-    <row r="278" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:38" ht="15.95" customHeight="1">
       <c r="A278" s="3"/>
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
@@ -12403,7 +12409,7 @@
       <c r="AK278" s="6"/>
       <c r="AL278" s="6"/>
     </row>
-    <row r="279" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:38" ht="15.95" customHeight="1">
       <c r="A279" s="3"/>
       <c r="B279" s="3"/>
       <c r="C279" s="3"/>
@@ -12443,7 +12449,7 @@
       <c r="AK279" s="6"/>
       <c r="AL279" s="6"/>
     </row>
-    <row r="280" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:38" ht="15.95" customHeight="1">
       <c r="A280" s="3"/>
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
@@ -12483,7 +12489,7 @@
       <c r="AK280" s="6"/>
       <c r="AL280" s="6"/>
     </row>
-    <row r="281" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:38" ht="15.95" customHeight="1">
       <c r="A281" s="3"/>
       <c r="B281" s="3"/>
       <c r="C281" s="3"/>
@@ -12523,7 +12529,7 @@
       <c r="AK281" s="6"/>
       <c r="AL281" s="6"/>
     </row>
-    <row r="282" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:38" ht="15.95" customHeight="1">
       <c r="A282" s="3"/>
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
@@ -12563,7 +12569,7 @@
       <c r="AK282" s="6"/>
       <c r="AL282" s="6"/>
     </row>
-    <row r="283" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:38" ht="15.95" customHeight="1">
       <c r="A283" s="3"/>
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
@@ -12603,7 +12609,7 @@
       <c r="AK283" s="6"/>
       <c r="AL283" s="6"/>
     </row>
-    <row r="284" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:38" ht="15.95" customHeight="1">
       <c r="A284" s="3"/>
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
@@ -12643,7 +12649,7 @@
       <c r="AK284" s="6"/>
       <c r="AL284" s="6"/>
     </row>
-    <row r="285" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:38" ht="15.95" customHeight="1">
       <c r="A285" s="3"/>
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
@@ -12683,7 +12689,7 @@
       <c r="AK285" s="6"/>
       <c r="AL285" s="6"/>
     </row>
-    <row r="286" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:38" ht="15.95" customHeight="1">
       <c r="A286" s="3"/>
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
@@ -12723,7 +12729,7 @@
       <c r="AK286" s="6"/>
       <c r="AL286" s="6"/>
     </row>
-    <row r="287" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:38" ht="15.95" customHeight="1">
       <c r="A287" s="3"/>
       <c r="B287" s="3"/>
       <c r="C287" s="3"/>
@@ -12763,7 +12769,7 @@
       <c r="AK287" s="6"/>
       <c r="AL287" s="6"/>
     </row>
-    <row r="288" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:38" ht="15.95" customHeight="1">
       <c r="A288" s="3"/>
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
@@ -12803,7 +12809,7 @@
       <c r="AK288" s="6"/>
       <c r="AL288" s="6"/>
     </row>
-    <row r="289" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:38" ht="15.95" customHeight="1">
       <c r="A289" s="3"/>
       <c r="B289" s="3"/>
       <c r="C289" s="3"/>
@@ -12843,7 +12849,7 @@
       <c r="AK289" s="6"/>
       <c r="AL289" s="6"/>
     </row>
-    <row r="290" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:38" ht="15.95" customHeight="1">
       <c r="A290" s="3"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
@@ -12883,7 +12889,7 @@
       <c r="AK290" s="6"/>
       <c r="AL290" s="6"/>
     </row>
-    <row r="291" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:38" ht="15.95" customHeight="1">
       <c r="A291" s="3"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
@@ -12923,7 +12929,7 @@
       <c r="AK291" s="6"/>
       <c r="AL291" s="6"/>
     </row>
-    <row r="292" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:38" ht="15.95" customHeight="1">
       <c r="A292" s="3"/>
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
@@ -12963,7 +12969,7 @@
       <c r="AK292" s="6"/>
       <c r="AL292" s="6"/>
     </row>
-    <row r="293" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:38" ht="15.95" customHeight="1">
       <c r="A293" s="3"/>
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
@@ -13003,7 +13009,7 @@
       <c r="AK293" s="6"/>
       <c r="AL293" s="6"/>
     </row>
-    <row r="294" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:38" ht="15.95" customHeight="1">
       <c r="A294" s="3"/>
       <c r="B294" s="3"/>
       <c r="C294" s="3"/>
@@ -13043,7 +13049,7 @@
       <c r="AK294" s="6"/>
       <c r="AL294" s="6"/>
     </row>
-    <row r="295" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:38" ht="15.95" customHeight="1">
       <c r="A295" s="3"/>
       <c r="B295" s="3"/>
       <c r="C295" s="3"/>
@@ -13083,7 +13089,7 @@
       <c r="AK295" s="6"/>
       <c r="AL295" s="6"/>
     </row>
-    <row r="296" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:38" ht="15.95" customHeight="1">
       <c r="A296" s="3"/>
       <c r="B296" s="3"/>
       <c r="C296" s="3"/>
@@ -13123,7 +13129,7 @@
       <c r="AK296" s="6"/>
       <c r="AL296" s="6"/>
     </row>
-    <row r="297" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:38" ht="15.95" customHeight="1">
       <c r="A297" s="3"/>
       <c r="B297" s="3"/>
       <c r="C297" s="3"/>
@@ -13163,7 +13169,7 @@
       <c r="AK297" s="6"/>
       <c r="AL297" s="6"/>
     </row>
-    <row r="298" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:38" ht="15.95" customHeight="1">
       <c r="A298" s="3"/>
       <c r="B298" s="3"/>
       <c r="C298" s="3"/>
@@ -13203,7 +13209,7 @@
       <c r="AK298" s="6"/>
       <c r="AL298" s="6"/>
     </row>
-    <row r="299" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:38" ht="15.95" customHeight="1">
       <c r="A299" s="3"/>
       <c r="B299" s="3"/>
       <c r="C299" s="3"/>
@@ -13243,7 +13249,7 @@
       <c r="AK299" s="6"/>
       <c r="AL299" s="6"/>
     </row>
-    <row r="300" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:38" ht="15.95" customHeight="1">
       <c r="A300" s="3"/>
       <c r="B300" s="3"/>
       <c r="C300" s="3"/>
@@ -13283,7 +13289,7 @@
       <c r="AK300" s="6"/>
       <c r="AL300" s="6"/>
     </row>
-    <row r="301" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:38" ht="15.95" customHeight="1">
       <c r="A301" s="3"/>
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
@@ -13323,7 +13329,7 @@
       <c r="AK301" s="6"/>
       <c r="AL301" s="6"/>
     </row>
-    <row r="302" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:38" ht="15.95" customHeight="1">
       <c r="A302" s="3"/>
       <c r="B302" s="3"/>
       <c r="C302" s="3"/>
@@ -13363,7 +13369,7 @@
       <c r="AK302" s="6"/>
       <c r="AL302" s="6"/>
     </row>
-    <row r="303" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:38" ht="15.95" customHeight="1">
       <c r="A303" s="3"/>
       <c r="B303" s="3"/>
       <c r="C303" s="3"/>
@@ -13403,7 +13409,7 @@
       <c r="AK303" s="6"/>
       <c r="AL303" s="6"/>
     </row>
-    <row r="304" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:38" ht="15.95" customHeight="1">
       <c r="A304" s="3"/>
       <c r="B304" s="3"/>
       <c r="C304" s="3"/>
@@ -13443,7 +13449,7 @@
       <c r="AK304" s="6"/>
       <c r="AL304" s="6"/>
     </row>
-    <row r="305" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:38" ht="15.95" customHeight="1">
       <c r="A305" s="3"/>
       <c r="B305" s="3"/>
       <c r="C305" s="3"/>
@@ -13483,7 +13489,7 @@
       <c r="AK305" s="6"/>
       <c r="AL305" s="6"/>
     </row>
-    <row r="306" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:38" ht="15.95" customHeight="1">
       <c r="A306" s="3"/>
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
@@ -13523,7 +13529,7 @@
       <c r="AK306" s="6"/>
       <c r="AL306" s="6"/>
     </row>
-    <row r="307" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:38" ht="15.95" customHeight="1">
       <c r="A307" s="3"/>
       <c r="B307" s="3"/>
       <c r="C307" s="3"/>
@@ -13563,7 +13569,7 @@
       <c r="AK307" s="6"/>
       <c r="AL307" s="6"/>
     </row>
-    <row r="308" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:38" ht="15.95" customHeight="1">
       <c r="A308" s="3"/>
       <c r="B308" s="3"/>
       <c r="C308" s="3"/>
@@ -13603,7 +13609,7 @@
       <c r="AK308" s="6"/>
       <c r="AL308" s="6"/>
     </row>
-    <row r="309" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:38" ht="15.95" customHeight="1">
       <c r="A309" s="3"/>
       <c r="B309" s="3"/>
       <c r="C309" s="3"/>
@@ -13643,7 +13649,7 @@
       <c r="AK309" s="6"/>
       <c r="AL309" s="6"/>
     </row>
-    <row r="310" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:38" ht="15.95" customHeight="1">
       <c r="A310" s="3"/>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
@@ -13683,7 +13689,7 @@
       <c r="AK310" s="6"/>
       <c r="AL310" s="6"/>
     </row>
-    <row r="311" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:38" ht="15.95" customHeight="1">
       <c r="A311" s="3"/>
       <c r="B311" s="3"/>
       <c r="C311" s="3"/>
@@ -13723,7 +13729,7 @@
       <c r="AK311" s="6"/>
       <c r="AL311" s="6"/>
     </row>
-    <row r="312" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:38" ht="15.95" customHeight="1">
       <c r="A312" s="3"/>
       <c r="B312" s="3"/>
       <c r="C312" s="3"/>
@@ -13763,7 +13769,7 @@
       <c r="AK312" s="6"/>
       <c r="AL312" s="6"/>
     </row>
-    <row r="313" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:38" ht="15.95" customHeight="1">
       <c r="A313" s="3"/>
       <c r="B313" s="3"/>
       <c r="C313" s="3"/>
@@ -13803,7 +13809,7 @@
       <c r="AK313" s="6"/>
       <c r="AL313" s="6"/>
     </row>
-    <row r="314" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:38" ht="15.95" customHeight="1">
       <c r="A314" s="3"/>
       <c r="B314" s="3"/>
       <c r="C314" s="3"/>
@@ -13843,7 +13849,7 @@
       <c r="AK314" s="6"/>
       <c r="AL314" s="6"/>
     </row>
-    <row r="315" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:38" ht="15.95" customHeight="1">
       <c r="A315" s="3"/>
       <c r="B315" s="3"/>
       <c r="C315" s="3"/>
@@ -13883,7 +13889,7 @@
       <c r="AK315" s="6"/>
       <c r="AL315" s="6"/>
     </row>
-    <row r="316" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:38" ht="15.95" customHeight="1">
       <c r="A316" s="3"/>
       <c r="B316" s="3"/>
       <c r="C316" s="3"/>
@@ -13923,7 +13929,7 @@
       <c r="AK316" s="6"/>
       <c r="AL316" s="6"/>
     </row>
-    <row r="317" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:38" ht="15.95" customHeight="1">
       <c r="A317" s="3"/>
       <c r="B317" s="3"/>
       <c r="C317" s="3"/>
@@ -13963,7 +13969,7 @@
       <c r="AK317" s="6"/>
       <c r="AL317" s="6"/>
     </row>
-    <row r="318" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:38" ht="15.95" customHeight="1">
       <c r="A318" s="3"/>
       <c r="B318" s="3"/>
       <c r="C318" s="3"/>
@@ -14003,7 +14009,7 @@
       <c r="AK318" s="6"/>
       <c r="AL318" s="6"/>
     </row>
-    <row r="319" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:38" ht="15.95" customHeight="1">
       <c r="A319" s="3"/>
       <c r="B319" s="3"/>
       <c r="C319" s="3"/>
@@ -14043,7 +14049,7 @@
       <c r="AK319" s="6"/>
       <c r="AL319" s="6"/>
     </row>
-    <row r="320" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:38" ht="15.95" customHeight="1">
       <c r="A320" s="3"/>
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
@@ -14083,7 +14089,7 @@
       <c r="AK320" s="6"/>
       <c r="AL320" s="6"/>
     </row>
-    <row r="321" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:38" ht="15.95" customHeight="1">
       <c r="A321" s="3"/>
       <c r="B321" s="3"/>
       <c r="C321" s="3"/>
@@ -14123,7 +14129,7 @@
       <c r="AK321" s="6"/>
       <c r="AL321" s="6"/>
     </row>
-    <row r="322" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:38" ht="15.95" customHeight="1">
       <c r="A322" s="3"/>
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
@@ -14163,7 +14169,7 @@
       <c r="AK322" s="6"/>
       <c r="AL322" s="6"/>
     </row>
-    <row r="323" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:38" ht="15.95" customHeight="1">
       <c r="A323" s="3"/>
       <c r="B323" s="3"/>
       <c r="C323" s="3"/>
@@ -14203,7 +14209,7 @@
       <c r="AK323" s="6"/>
       <c r="AL323" s="6"/>
     </row>
-    <row r="324" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:38" ht="15.95" customHeight="1">
       <c r="A324" s="3"/>
       <c r="B324" s="3"/>
       <c r="C324" s="3"/>
@@ -14243,7 +14249,7 @@
       <c r="AK324" s="6"/>
       <c r="AL324" s="6"/>
     </row>
-    <row r="325" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:38" ht="15.95" customHeight="1">
       <c r="A325" s="3"/>
       <c r="B325" s="3"/>
       <c r="C325" s="3"/>
@@ -14283,7 +14289,7 @@
       <c r="AK325" s="6"/>
       <c r="AL325" s="6"/>
     </row>
-    <row r="326" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:38" ht="15.95" customHeight="1">
       <c r="A326" s="3"/>
       <c r="B326" s="3"/>
       <c r="C326" s="3"/>
@@ -14323,7 +14329,7 @@
       <c r="AK326" s="6"/>
       <c r="AL326" s="6"/>
     </row>
-    <row r="327" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:38" ht="15.95" customHeight="1">
       <c r="A327" s="3"/>
       <c r="B327" s="3"/>
       <c r="C327" s="3"/>
@@ -14363,7 +14369,7 @@
       <c r="AK327" s="6"/>
       <c r="AL327" s="6"/>
     </row>
-    <row r="328" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:38" ht="15.95" customHeight="1">
       <c r="A328" s="3"/>
       <c r="B328" s="3"/>
       <c r="C328" s="3"/>
@@ -14403,7 +14409,7 @@
       <c r="AK328" s="6"/>
       <c r="AL328" s="6"/>
     </row>
-    <row r="329" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:38" ht="15.95" customHeight="1">
       <c r="A329" s="3"/>
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
@@ -14443,7 +14449,7 @@
       <c r="AK329" s="6"/>
       <c r="AL329" s="6"/>
     </row>
-    <row r="330" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:38" ht="15.95" customHeight="1">
       <c r="A330" s="3"/>
       <c r="B330" s="3"/>
       <c r="C330" s="3"/>
@@ -14483,7 +14489,7 @@
       <c r="AK330" s="6"/>
       <c r="AL330" s="6"/>
     </row>
-    <row r="331" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:38" ht="15.95" customHeight="1">
       <c r="A331" s="3"/>
       <c r="B331" s="3"/>
       <c r="C331" s="3"/>
@@ -14523,7 +14529,7 @@
       <c r="AK331" s="6"/>
       <c r="AL331" s="6"/>
     </row>
-    <row r="332" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:38" ht="15.95" customHeight="1">
       <c r="A332" s="3"/>
       <c r="B332" s="3"/>
       <c r="C332" s="3"/>
@@ -14563,7 +14569,7 @@
       <c r="AK332" s="6"/>
       <c r="AL332" s="6"/>
     </row>
-    <row r="333" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:38" ht="15.95" customHeight="1">
       <c r="A333" s="3"/>
       <c r="B333" s="3"/>
       <c r="C333" s="3"/>
@@ -14603,7 +14609,7 @@
       <c r="AK333" s="6"/>
       <c r="AL333" s="6"/>
     </row>
-    <row r="334" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:38" ht="15.95" customHeight="1">
       <c r="A334" s="3"/>
       <c r="B334" s="3"/>
       <c r="C334" s="3"/>
@@ -14643,7 +14649,7 @@
       <c r="AK334" s="6"/>
       <c r="AL334" s="6"/>
     </row>
-    <row r="335" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:38" ht="15.95" customHeight="1">
       <c r="A335" s="3"/>
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
@@ -14683,7 +14689,7 @@
       <c r="AK335" s="6"/>
       <c r="AL335" s="6"/>
     </row>
-    <row r="336" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:38" ht="15.95" customHeight="1">
       <c r="A336" s="3"/>
       <c r="B336" s="3"/>
       <c r="C336" s="3"/>
@@ -14723,7 +14729,7 @@
       <c r="AK336" s="6"/>
       <c r="AL336" s="6"/>
     </row>
-    <row r="337" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:38" ht="15.95" customHeight="1">
       <c r="A337" s="3"/>
       <c r="B337" s="3"/>
       <c r="C337" s="3"/>
@@ -14763,7 +14769,7 @@
       <c r="AK337" s="6"/>
       <c r="AL337" s="6"/>
     </row>
-    <row r="338" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:38" ht="15.95" customHeight="1">
       <c r="A338" s="3"/>
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
@@ -14803,7 +14809,7 @@
       <c r="AK338" s="6"/>
       <c r="AL338" s="6"/>
     </row>
-    <row r="339" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:38" ht="15.95" customHeight="1">
       <c r="A339" s="3"/>
       <c r="B339" s="3"/>
       <c r="C339" s="3"/>
@@ -14843,7 +14849,7 @@
       <c r="AK339" s="6"/>
       <c r="AL339" s="6"/>
     </row>
-    <row r="340" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:38" ht="15.95" customHeight="1">
       <c r="A340" s="3"/>
       <c r="B340" s="3"/>
       <c r="C340" s="3"/>
@@ -14883,7 +14889,7 @@
       <c r="AK340" s="6"/>
       <c r="AL340" s="6"/>
     </row>
-    <row r="341" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:38" ht="15.95" customHeight="1">
       <c r="A341" s="3"/>
       <c r="B341" s="3"/>
       <c r="C341" s="3"/>
@@ -14923,7 +14929,7 @@
       <c r="AK341" s="6"/>
       <c r="AL341" s="6"/>
     </row>
-    <row r="342" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:38" ht="15.95" customHeight="1">
       <c r="A342" s="3"/>
       <c r="B342" s="3"/>
       <c r="C342" s="3"/>
@@ -14963,7 +14969,7 @@
       <c r="AK342" s="6"/>
       <c r="AL342" s="6"/>
     </row>
-    <row r="343" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:38" ht="15.95" customHeight="1">
       <c r="A343" s="3"/>
       <c r="B343" s="3"/>
       <c r="C343" s="3"/>
@@ -15003,7 +15009,7 @@
       <c r="AK343" s="6"/>
       <c r="AL343" s="6"/>
     </row>
-    <row r="344" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:38" ht="15.95" customHeight="1">
       <c r="A344" s="3"/>
       <c r="B344" s="3"/>
       <c r="C344" s="3"/>
@@ -15043,7 +15049,7 @@
       <c r="AK344" s="6"/>
       <c r="AL344" s="6"/>
     </row>
-    <row r="345" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:38" ht="15.95" customHeight="1">
       <c r="A345" s="3"/>
       <c r="B345" s="3"/>
       <c r="C345" s="3"/>
@@ -15083,7 +15089,7 @@
       <c r="AK345" s="6"/>
       <c r="AL345" s="6"/>
     </row>
-    <row r="346" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:38" ht="15.95" customHeight="1">
       <c r="A346" s="3"/>
       <c r="B346" s="3"/>
       <c r="C346" s="3"/>
@@ -15123,7 +15129,7 @@
       <c r="AK346" s="6"/>
       <c r="AL346" s="6"/>
     </row>
-    <row r="347" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:38" ht="15.95" customHeight="1">
       <c r="A347" s="3"/>
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
@@ -15163,7 +15169,7 @@
       <c r="AK347" s="6"/>
       <c r="AL347" s="6"/>
     </row>
-    <row r="348" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:38" ht="15.95" customHeight="1">
       <c r="A348" s="3"/>
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
@@ -15203,7 +15209,7 @@
       <c r="AK348" s="6"/>
       <c r="AL348" s="6"/>
     </row>
-    <row r="349" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:38" ht="15.95" customHeight="1">
       <c r="A349" s="3"/>
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
@@ -15243,7 +15249,7 @@
       <c r="AK349" s="6"/>
       <c r="AL349" s="6"/>
     </row>
-    <row r="350" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:38" ht="15.95" customHeight="1">
       <c r="A350" s="3"/>
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
@@ -15283,7 +15289,7 @@
       <c r="AK350" s="6"/>
       <c r="AL350" s="6"/>
     </row>
-    <row r="351" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:38" ht="15.95" customHeight="1">
       <c r="A351" s="3"/>
       <c r="B351" s="3"/>
       <c r="C351" s="3"/>
@@ -15323,7 +15329,7 @@
       <c r="AK351" s="6"/>
       <c r="AL351" s="6"/>
     </row>
-    <row r="352" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:38" ht="15.95" customHeight="1">
       <c r="A352" s="3"/>
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
@@ -15363,7 +15369,7 @@
       <c r="AK352" s="6"/>
       <c r="AL352" s="6"/>
     </row>
-    <row r="353" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:38" ht="15.95" customHeight="1">
       <c r="A353" s="3"/>
       <c r="B353" s="3"/>
       <c r="C353" s="3"/>
@@ -15403,7 +15409,7 @@
       <c r="AK353" s="6"/>
       <c r="AL353" s="6"/>
     </row>
-    <row r="354" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:38" ht="15.95" customHeight="1">
       <c r="A354" s="3"/>
       <c r="B354" s="3"/>
       <c r="C354" s="3"/>
@@ -15443,7 +15449,7 @@
       <c r="AK354" s="6"/>
       <c r="AL354" s="6"/>
     </row>
-    <row r="355" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:38" ht="15.95" customHeight="1">
       <c r="A355" s="3"/>
       <c r="B355" s="3"/>
       <c r="C355" s="3"/>
@@ -15483,7 +15489,7 @@
       <c r="AK355" s="6"/>
       <c r="AL355" s="6"/>
     </row>
-    <row r="356" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:38" ht="15.95" customHeight="1">
       <c r="A356" s="3"/>
       <c r="B356" s="3"/>
       <c r="C356" s="3"/>
@@ -15523,7 +15529,7 @@
       <c r="AK356" s="6"/>
       <c r="AL356" s="6"/>
     </row>
-    <row r="357" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:38" ht="15.95" customHeight="1">
       <c r="A357" s="3"/>
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
@@ -15563,7 +15569,7 @@
       <c r="AK357" s="6"/>
       <c r="AL357" s="6"/>
     </row>
-    <row r="358" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:38" ht="15.95" customHeight="1">
       <c r="A358" s="3"/>
       <c r="B358" s="3"/>
       <c r="C358" s="3"/>
@@ -15603,7 +15609,7 @@
       <c r="AK358" s="6"/>
       <c r="AL358" s="6"/>
     </row>
-    <row r="359" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:38" ht="15.95" customHeight="1">
       <c r="A359" s="3"/>
       <c r="B359" s="3"/>
       <c r="C359" s="3"/>
@@ -15643,7 +15649,7 @@
       <c r="AK359" s="6"/>
       <c r="AL359" s="6"/>
     </row>
-    <row r="360" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:38" ht="15.95" customHeight="1">
       <c r="A360" s="3"/>
       <c r="B360" s="3"/>
       <c r="C360" s="3"/>
@@ -15683,7 +15689,7 @@
       <c r="AK360" s="6"/>
       <c r="AL360" s="6"/>
     </row>
-    <row r="361" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:38" ht="15.95" customHeight="1">
       <c r="A361" s="3"/>
       <c r="B361" s="3"/>
       <c r="C361" s="3"/>
@@ -15723,7 +15729,7 @@
       <c r="AK361" s="6"/>
       <c r="AL361" s="6"/>
     </row>
-    <row r="362" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:38" ht="15.95" customHeight="1">
       <c r="A362" s="3"/>
       <c r="B362" s="3"/>
       <c r="C362" s="3"/>
@@ -15763,7 +15769,7 @@
       <c r="AK362" s="6"/>
       <c r="AL362" s="6"/>
     </row>
-    <row r="363" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:38" ht="15.95" customHeight="1">
       <c r="A363" s="3"/>
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
@@ -15803,7 +15809,7 @@
       <c r="AK363" s="6"/>
       <c r="AL363" s="6"/>
     </row>
-    <row r="364" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:38" ht="15.95" customHeight="1">
       <c r="A364" s="3"/>
       <c r="B364" s="3"/>
       <c r="C364" s="3"/>
@@ -15843,7 +15849,7 @@
       <c r="AK364" s="6"/>
       <c r="AL364" s="6"/>
     </row>
-    <row r="365" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:38" ht="15.95" customHeight="1">
       <c r="A365" s="3"/>
       <c r="B365" s="3"/>
       <c r="C365" s="3"/>
@@ -15883,7 +15889,7 @@
       <c r="AK365" s="6"/>
       <c r="AL365" s="6"/>
     </row>
-    <row r="366" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:38" ht="15.95" customHeight="1">
       <c r="A366" s="3"/>
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
@@ -15923,7 +15929,7 @@
       <c r="AK366" s="6"/>
       <c r="AL366" s="6"/>
     </row>
-    <row r="367" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:38" ht="15.95" customHeight="1">
       <c r="A367" s="3"/>
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
@@ -15963,7 +15969,7 @@
       <c r="AK367" s="6"/>
       <c r="AL367" s="6"/>
     </row>
-    <row r="368" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:38" ht="15.95" customHeight="1">
       <c r="A368" s="3"/>
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
@@ -16003,7 +16009,7 @@
       <c r="AK368" s="6"/>
       <c r="AL368" s="6"/>
     </row>
-    <row r="369" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:38" ht="15.95" customHeight="1">
       <c r="A369" s="3"/>
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
@@ -16043,7 +16049,7 @@
       <c r="AK369" s="6"/>
       <c r="AL369" s="6"/>
     </row>
-    <row r="370" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:38" ht="15.95" customHeight="1">
       <c r="A370" s="3"/>
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
@@ -16083,7 +16089,7 @@
       <c r="AK370" s="6"/>
       <c r="AL370" s="6"/>
     </row>
-    <row r="371" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:38" ht="15.95" customHeight="1">
       <c r="A371" s="3"/>
       <c r="B371" s="3"/>
       <c r="C371" s="3"/>
@@ -16123,7 +16129,7 @@
       <c r="AK371" s="6"/>
       <c r="AL371" s="6"/>
     </row>
-    <row r="372" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:38" ht="15.95" customHeight="1">
       <c r="A372" s="3"/>
       <c r="B372" s="3"/>
       <c r="C372" s="3"/>
@@ -16163,7 +16169,7 @@
       <c r="AK372" s="6"/>
       <c r="AL372" s="6"/>
     </row>
-    <row r="373" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:38" ht="15.95" customHeight="1">
       <c r="A373" s="3"/>
       <c r="B373" s="3"/>
       <c r="C373" s="3"/>
@@ -16203,7 +16209,7 @@
       <c r="AK373" s="6"/>
       <c r="AL373" s="6"/>
     </row>
-    <row r="374" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:38" ht="15.95" customHeight="1">
       <c r="A374" s="3"/>
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
@@ -16243,7 +16249,7 @@
       <c r="AK374" s="6"/>
       <c r="AL374" s="6"/>
     </row>
-    <row r="375" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:38" ht="15.95" customHeight="1">
       <c r="A375" s="3"/>
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
@@ -16283,7 +16289,7 @@
       <c r="AK375" s="6"/>
       <c r="AL375" s="6"/>
     </row>
-    <row r="376" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:38" ht="15.95" customHeight="1">
       <c r="A376" s="3"/>
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
@@ -16323,7 +16329,7 @@
       <c r="AK376" s="6"/>
       <c r="AL376" s="6"/>
     </row>
-    <row r="377" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:38" ht="15.95" customHeight="1">
       <c r="A377" s="3"/>
       <c r="B377" s="3"/>
       <c r="C377" s="3"/>
@@ -16363,7 +16369,7 @@
       <c r="AK377" s="6"/>
       <c r="AL377" s="6"/>
     </row>
-    <row r="378" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:38" ht="15.95" customHeight="1">
       <c r="A378" s="3"/>
       <c r="B378" s="3"/>
       <c r="C378" s="3"/>
@@ -16403,7 +16409,7 @@
       <c r="AK378" s="6"/>
       <c r="AL378" s="6"/>
     </row>
-    <row r="379" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:38" ht="15.95" customHeight="1">
       <c r="A379" s="3"/>
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
@@ -16443,7 +16449,7 @@
       <c r="AK379" s="6"/>
       <c r="AL379" s="6"/>
     </row>
-    <row r="380" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:38" ht="15.95" customHeight="1">
       <c r="A380" s="3"/>
       <c r="B380" s="3"/>
       <c r="C380" s="3"/>
@@ -16483,7 +16489,7 @@
       <c r="AK380" s="6"/>
       <c r="AL380" s="6"/>
     </row>
-    <row r="381" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:38" ht="15.95" customHeight="1">
       <c r="A381" s="3"/>
       <c r="B381" s="3"/>
       <c r="C381" s="3"/>
@@ -16523,7 +16529,7 @@
       <c r="AK381" s="6"/>
       <c r="AL381" s="6"/>
     </row>
-    <row r="382" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:38" ht="15.95" customHeight="1">
       <c r="A382" s="3"/>
       <c r="B382" s="3"/>
       <c r="C382" s="3"/>
@@ -16563,7 +16569,7 @@
       <c r="AK382" s="6"/>
       <c r="AL382" s="6"/>
     </row>
-    <row r="383" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:38" ht="15.95" customHeight="1">
       <c r="A383" s="3"/>
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
@@ -16603,7 +16609,7 @@
       <c r="AK383" s="6"/>
       <c r="AL383" s="6"/>
     </row>
-    <row r="384" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:38" ht="15.95" customHeight="1">
       <c r="A384" s="3"/>
       <c r="B384" s="3"/>
       <c r="C384" s="3"/>
@@ -16643,7 +16649,7 @@
       <c r="AK384" s="6"/>
       <c r="AL384" s="6"/>
     </row>
-    <row r="385" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:38" ht="15.95" customHeight="1">
       <c r="A385" s="3"/>
       <c r="B385" s="3"/>
       <c r="C385" s="3"/>
@@ -16683,7 +16689,7 @@
       <c r="AK385" s="6"/>
       <c r="AL385" s="6"/>
     </row>
-    <row r="386" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:38" ht="15.95" customHeight="1">
       <c r="A386" s="3"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
@@ -16723,7 +16729,7 @@
       <c r="AK386" s="6"/>
       <c r="AL386" s="6"/>
     </row>
-    <row r="387" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:38" ht="15.95" customHeight="1">
       <c r="A387" s="3"/>
       <c r="B387" s="3"/>
       <c r="C387" s="3"/>
@@ -16763,7 +16769,7 @@
       <c r="AK387" s="6"/>
       <c r="AL387" s="6"/>
     </row>
-    <row r="388" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:38" ht="15.95" customHeight="1">
       <c r="A388" s="3"/>
       <c r="B388" s="3"/>
       <c r="C388" s="3"/>
@@ -16803,7 +16809,7 @@
       <c r="AK388" s="6"/>
       <c r="AL388" s="6"/>
     </row>
-    <row r="389" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:38" ht="15.95" customHeight="1">
       <c r="A389" s="3"/>
       <c r="B389" s="3"/>
       <c r="C389" s="3"/>
@@ -16843,7 +16849,7 @@
       <c r="AK389" s="6"/>
       <c r="AL389" s="6"/>
     </row>
-    <row r="390" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:38" ht="15.95" customHeight="1">
       <c r="A390" s="3"/>
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
@@ -16883,7 +16889,7 @@
       <c r="AK390" s="6"/>
       <c r="AL390" s="6"/>
     </row>
-    <row r="391" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:38" ht="15.95" customHeight="1">
       <c r="A391" s="3"/>
       <c r="B391" s="3"/>
       <c r="C391" s="3"/>
@@ -16923,7 +16929,7 @@
       <c r="AK391" s="6"/>
       <c r="AL391" s="6"/>
     </row>
-    <row r="392" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:38" ht="15.95" customHeight="1">
       <c r="A392" s="3"/>
       <c r="B392" s="3"/>
       <c r="C392" s="3"/>
@@ -16963,7 +16969,7 @@
       <c r="AK392" s="6"/>
       <c r="AL392" s="6"/>
     </row>
-    <row r="393" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:38" ht="15.95" customHeight="1">
       <c r="A393" s="3"/>
       <c r="B393" s="3"/>
       <c r="C393" s="3"/>
@@ -17003,7 +17009,7 @@
       <c r="AK393" s="6"/>
       <c r="AL393" s="6"/>
     </row>
-    <row r="394" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:38" ht="15.95" customHeight="1">
       <c r="A394" s="3"/>
       <c r="B394" s="3"/>
       <c r="C394" s="3"/>
@@ -17043,7 +17049,7 @@
       <c r="AK394" s="6"/>
       <c r="AL394" s="6"/>
     </row>
-    <row r="395" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:38" ht="15.95" customHeight="1">
       <c r="A395" s="3"/>
       <c r="B395" s="3"/>
       <c r="C395" s="3"/>
@@ -17083,7 +17089,7 @@
       <c r="AK395" s="6"/>
       <c r="AL395" s="6"/>
     </row>
-    <row r="396" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:38" ht="15.95" customHeight="1">
       <c r="A396" s="3"/>
       <c r="B396" s="3"/>
       <c r="C396" s="3"/>
@@ -17123,7 +17129,7 @@
       <c r="AK396" s="6"/>
       <c r="AL396" s="6"/>
     </row>
-    <row r="397" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:38" ht="15.95" customHeight="1">
       <c r="A397" s="3"/>
       <c r="B397" s="3"/>
       <c r="C397" s="3"/>
@@ -17163,7 +17169,7 @@
       <c r="AK397" s="6"/>
       <c r="AL397" s="6"/>
     </row>
-    <row r="398" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:38" ht="15.95" customHeight="1">
       <c r="A398" s="3"/>
       <c r="B398" s="3"/>
       <c r="C398" s="3"/>
@@ -17203,7 +17209,7 @@
       <c r="AK398" s="6"/>
       <c r="AL398" s="6"/>
     </row>
-    <row r="399" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:38" ht="15.95" customHeight="1">
       <c r="A399" s="3"/>
       <c r="B399" s="3"/>
       <c r="C399" s="3"/>
@@ -17243,7 +17249,7 @@
       <c r="AK399" s="6"/>
       <c r="AL399" s="6"/>
     </row>
-    <row r="400" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:38" ht="15.95" customHeight="1">
       <c r="A400" s="3"/>
       <c r="B400" s="3"/>
       <c r="C400" s="3"/>
@@ -17283,7 +17289,7 @@
       <c r="AK400" s="6"/>
       <c r="AL400" s="6"/>
     </row>
-    <row r="401" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:38" ht="15.95" customHeight="1">
       <c r="A401" s="3"/>
       <c r="B401" s="3"/>
       <c r="C401" s="3"/>
@@ -17323,7 +17329,7 @@
       <c r="AK401" s="6"/>
       <c r="AL401" s="6"/>
     </row>
-    <row r="402" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:38" ht="15.95" customHeight="1">
       <c r="A402" s="3"/>
       <c r="B402" s="3"/>
       <c r="C402" s="3"/>
@@ -17363,7 +17369,7 @@
       <c r="AK402" s="6"/>
       <c r="AL402" s="6"/>
     </row>
-    <row r="403" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:38" ht="15.95" customHeight="1">
       <c r="A403" s="3"/>
       <c r="B403" s="3"/>
       <c r="C403" s="3"/>
@@ -17403,7 +17409,7 @@
       <c r="AK403" s="6"/>
       <c r="AL403" s="6"/>
     </row>
-    <row r="404" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:38" ht="15.95" customHeight="1">
       <c r="A404" s="3"/>
       <c r="B404" s="3"/>
       <c r="C404" s="3"/>
@@ -17443,7 +17449,7 @@
       <c r="AK404" s="6"/>
       <c r="AL404" s="6"/>
     </row>
-    <row r="405" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:38" ht="15.95" customHeight="1">
       <c r="A405" s="3"/>
       <c r="B405" s="3"/>
       <c r="C405" s="3"/>
@@ -17483,7 +17489,7 @@
       <c r="AK405" s="6"/>
       <c r="AL405" s="6"/>
     </row>
-    <row r="406" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:38" ht="15.95" customHeight="1">
       <c r="A406" s="3"/>
       <c r="B406" s="3"/>
       <c r="C406" s="3"/>
@@ -17523,7 +17529,7 @@
       <c r="AK406" s="6"/>
       <c r="AL406" s="6"/>
     </row>
-    <row r="407" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:38" ht="15.95" customHeight="1">
       <c r="A407" s="3"/>
       <c r="B407" s="3"/>
       <c r="C407" s="3"/>
@@ -17563,7 +17569,7 @@
       <c r="AK407" s="6"/>
       <c r="AL407" s="6"/>
     </row>
-    <row r="408" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:38" ht="15.95" customHeight="1">
       <c r="A408" s="3"/>
       <c r="B408" s="3"/>
       <c r="C408" s="3"/>
@@ -17603,7 +17609,7 @@
       <c r="AK408" s="6"/>
       <c r="AL408" s="6"/>
     </row>
-    <row r="409" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:38" ht="15.95" customHeight="1">
       <c r="A409" s="3"/>
       <c r="B409" s="3"/>
       <c r="C409" s="3"/>
@@ -17643,7 +17649,7 @@
       <c r="AK409" s="6"/>
       <c r="AL409" s="6"/>
     </row>
-    <row r="410" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:38" ht="15.95" customHeight="1">
       <c r="A410" s="3"/>
       <c r="B410" s="3"/>
       <c r="C410" s="3"/>
@@ -17683,7 +17689,7 @@
       <c r="AK410" s="6"/>
       <c r="AL410" s="6"/>
     </row>
-    <row r="411" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:38" ht="15.95" customHeight="1">
       <c r="A411" s="3"/>
       <c r="B411" s="3"/>
       <c r="C411" s="3"/>
@@ -17723,7 +17729,7 @@
       <c r="AK411" s="6"/>
       <c r="AL411" s="6"/>
     </row>
-    <row r="412" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:38" ht="15.95" customHeight="1">
       <c r="A412" s="3"/>
       <c r="B412" s="3"/>
       <c r="C412" s="3"/>
@@ -17763,7 +17769,7 @@
       <c r="AK412" s="6"/>
       <c r="AL412" s="6"/>
     </row>
-    <row r="413" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:38" ht="15.95" customHeight="1">
       <c r="A413" s="3"/>
       <c r="B413" s="3"/>
       <c r="C413" s="3"/>
@@ -17803,7 +17809,7 @@
       <c r="AK413" s="6"/>
       <c r="AL413" s="6"/>
     </row>
-    <row r="414" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:38" ht="15.95" customHeight="1">
       <c r="A414" s="3"/>
       <c r="B414" s="3"/>
       <c r="C414" s="3"/>
@@ -17843,7 +17849,7 @@
       <c r="AK414" s="6"/>
       <c r="AL414" s="6"/>
     </row>
-    <row r="415" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:38" ht="15.95" customHeight="1">
       <c r="A415" s="3"/>
       <c r="B415" s="3"/>
       <c r="C415" s="3"/>
@@ -17883,7 +17889,7 @@
       <c r="AK415" s="6"/>
       <c r="AL415" s="6"/>
     </row>
-    <row r="416" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:38" ht="15.95" customHeight="1">
       <c r="A416" s="3"/>
       <c r="B416" s="3"/>
       <c r="C416" s="3"/>
@@ -17923,7 +17929,7 @@
       <c r="AK416" s="6"/>
       <c r="AL416" s="6"/>
     </row>
-    <row r="417" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:38" ht="15.95" customHeight="1">
       <c r="A417" s="3"/>
       <c r="B417" s="3"/>
       <c r="C417" s="3"/>
@@ -17963,7 +17969,7 @@
       <c r="AK417" s="6"/>
       <c r="AL417" s="6"/>
     </row>
-    <row r="418" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:38" ht="15.95" customHeight="1">
       <c r="A418" s="3"/>
       <c r="B418" s="3"/>
       <c r="C418" s="3"/>
@@ -18003,7 +18009,7 @@
       <c r="AK418" s="6"/>
       <c r="AL418" s="6"/>
     </row>
-    <row r="419" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:38" ht="15.95" customHeight="1">
       <c r="A419" s="3"/>
       <c r="B419" s="3"/>
       <c r="C419" s="3"/>
@@ -18043,7 +18049,7 @@
       <c r="AK419" s="6"/>
       <c r="AL419" s="6"/>
     </row>
-    <row r="420" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:38" ht="15.95" customHeight="1">
       <c r="A420" s="3"/>
       <c r="B420" s="3"/>
       <c r="C420" s="3"/>
@@ -18083,7 +18089,7 @@
       <c r="AK420" s="6"/>
       <c r="AL420" s="6"/>
     </row>
-    <row r="421" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:38" ht="15.95" customHeight="1">
       <c r="A421" s="3"/>
       <c r="B421" s="3"/>
       <c r="C421" s="3"/>
@@ -18123,7 +18129,7 @@
       <c r="AK421" s="6"/>
       <c r="AL421" s="6"/>
     </row>
-    <row r="422" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:38" ht="15.95" customHeight="1">
       <c r="A422" s="3"/>
       <c r="B422" s="3"/>
       <c r="C422" s="3"/>
@@ -18163,7 +18169,7 @@
       <c r="AK422" s="6"/>
       <c r="AL422" s="6"/>
     </row>
-    <row r="423" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:38" ht="15.95" customHeight="1">
       <c r="A423" s="3"/>
       <c r="B423" s="3"/>
       <c r="C423" s="3"/>
@@ -18203,7 +18209,7 @@
       <c r="AK423" s="6"/>
       <c r="AL423" s="6"/>
     </row>
-    <row r="424" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:38" ht="15.95" customHeight="1">
       <c r="A424" s="3"/>
       <c r="B424" s="3"/>
       <c r="C424" s="3"/>
@@ -18243,7 +18249,7 @@
       <c r="AK424" s="6"/>
       <c r="AL424" s="6"/>
     </row>
-    <row r="425" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:38" ht="15.95" customHeight="1">
       <c r="A425" s="3"/>
       <c r="B425" s="3"/>
       <c r="C425" s="3"/>
@@ -18283,7 +18289,7 @@
       <c r="AK425" s="6"/>
       <c r="AL425" s="6"/>
     </row>
-    <row r="426" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:38" ht="15.95" customHeight="1">
       <c r="A426" s="3"/>
       <c r="B426" s="3"/>
       <c r="C426" s="3"/>
@@ -18323,7 +18329,7 @@
       <c r="AK426" s="6"/>
       <c r="AL426" s="6"/>
     </row>
-    <row r="427" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:38" ht="15.95" customHeight="1">
       <c r="A427" s="3"/>
       <c r="B427" s="3"/>
       <c r="C427" s="3"/>
@@ -18363,7 +18369,7 @@
       <c r="AK427" s="6"/>
       <c r="AL427" s="6"/>
     </row>
-    <row r="428" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:38" ht="15.95" customHeight="1">
       <c r="A428" s="3"/>
       <c r="B428" s="3"/>
       <c r="C428" s="3"/>
@@ -18403,7 +18409,7 @@
       <c r="AK428" s="6"/>
       <c r="AL428" s="6"/>
     </row>
-    <row r="429" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:38" ht="15.95" customHeight="1">
       <c r="A429" s="3"/>
       <c r="B429" s="3"/>
       <c r="C429" s="3"/>
@@ -18443,7 +18449,7 @@
       <c r="AK429" s="6"/>
       <c r="AL429" s="6"/>
     </row>
-    <row r="430" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:38" ht="15.95" customHeight="1">
       <c r="A430" s="3"/>
       <c r="B430" s="3"/>
       <c r="C430" s="3"/>
@@ -18483,7 +18489,7 @@
       <c r="AK430" s="6"/>
       <c r="AL430" s="6"/>
     </row>
-    <row r="431" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:38" ht="15.95" customHeight="1">
       <c r="A431" s="3"/>
       <c r="B431" s="3"/>
       <c r="C431" s="3"/>
@@ -18523,7 +18529,7 @@
       <c r="AK431" s="6"/>
       <c r="AL431" s="6"/>
     </row>
-    <row r="432" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:38" ht="15.95" customHeight="1">
       <c r="A432" s="3"/>
       <c r="B432" s="3"/>
       <c r="C432" s="3"/>
@@ -18563,7 +18569,7 @@
       <c r="AK432" s="6"/>
       <c r="AL432" s="6"/>
     </row>
-    <row r="433" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:38" ht="15.95" customHeight="1">
       <c r="A433" s="3"/>
       <c r="B433" s="3"/>
       <c r="C433" s="3"/>
@@ -18603,7 +18609,7 @@
       <c r="AK433" s="6"/>
       <c r="AL433" s="6"/>
     </row>
-    <row r="434" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:38" ht="15.95" customHeight="1">
       <c r="A434" s="3"/>
       <c r="B434" s="3"/>
       <c r="C434" s="3"/>
@@ -18643,7 +18649,7 @@
       <c r="AK434" s="6"/>
       <c r="AL434" s="6"/>
     </row>
-    <row r="435" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:38" ht="15.95" customHeight="1">
       <c r="A435" s="3"/>
       <c r="B435" s="3"/>
       <c r="C435" s="3"/>
@@ -18683,7 +18689,7 @@
       <c r="AK435" s="6"/>
       <c r="AL435" s="6"/>
     </row>
-    <row r="436" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:38" ht="15.95" customHeight="1">
       <c r="A436" s="3"/>
       <c r="B436" s="3"/>
       <c r="C436" s="3"/>
@@ -18723,7 +18729,7 @@
       <c r="AK436" s="6"/>
       <c r="AL436" s="6"/>
     </row>
-    <row r="437" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:38" ht="15.95" customHeight="1">
       <c r="A437" s="3"/>
       <c r="B437" s="3"/>
       <c r="C437" s="3"/>
@@ -18763,7 +18769,7 @@
       <c r="AK437" s="6"/>
       <c r="AL437" s="6"/>
     </row>
-    <row r="438" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:38" ht="15.95" customHeight="1">
       <c r="A438" s="3"/>
       <c r="B438" s="3"/>
       <c r="C438" s="3"/>
@@ -18803,7 +18809,7 @@
       <c r="AK438" s="6"/>
       <c r="AL438" s="6"/>
     </row>
-    <row r="439" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:38" ht="15.95" customHeight="1">
       <c r="A439" s="3"/>
       <c r="B439" s="3"/>
       <c r="C439" s="3"/>
@@ -18843,7 +18849,7 @@
       <c r="AK439" s="6"/>
       <c r="AL439" s="6"/>
     </row>
-    <row r="440" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:38" ht="15.95" customHeight="1">
       <c r="A440" s="3"/>
       <c r="B440" s="3"/>
       <c r="C440" s="3"/>
@@ -18883,7 +18889,7 @@
       <c r="AK440" s="6"/>
       <c r="AL440" s="6"/>
     </row>
-    <row r="441" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:38" ht="15.95" customHeight="1">
       <c r="A441" s="3"/>
       <c r="B441" s="3"/>
       <c r="C441" s="3"/>
@@ -18923,7 +18929,7 @@
       <c r="AK441" s="6"/>
       <c r="AL441" s="6"/>
     </row>
-    <row r="442" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:38" ht="15.95" customHeight="1">
       <c r="A442" s="3"/>
       <c r="B442" s="3"/>
       <c r="C442" s="3"/>
@@ -18963,7 +18969,7 @@
       <c r="AK442" s="6"/>
       <c r="AL442" s="6"/>
     </row>
-    <row r="443" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:38" ht="15.95" customHeight="1">
       <c r="A443" s="3"/>
       <c r="B443" s="3"/>
       <c r="C443" s="3"/>
@@ -19003,7 +19009,7 @@
       <c r="AK443" s="6"/>
       <c r="AL443" s="6"/>
     </row>
-    <row r="444" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:38" ht="15.95" customHeight="1">
       <c r="A444" s="3"/>
       <c r="B444" s="3"/>
       <c r="C444" s="3"/>
@@ -19043,7 +19049,7 @@
       <c r="AK444" s="6"/>
       <c r="AL444" s="6"/>
     </row>
-    <row r="445" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:38" ht="15.95" customHeight="1">
       <c r="A445" s="3"/>
       <c r="B445" s="3"/>
       <c r="C445" s="3"/>
@@ -19083,7 +19089,7 @@
       <c r="AK445" s="6"/>
       <c r="AL445" s="6"/>
     </row>
-    <row r="446" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:38" ht="15.95" customHeight="1">
       <c r="A446" s="3"/>
       <c r="B446" s="3"/>
       <c r="C446" s="3"/>
@@ -19123,7 +19129,7 @@
       <c r="AK446" s="6"/>
       <c r="AL446" s="6"/>
     </row>
-    <row r="447" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:38" ht="15.95" customHeight="1">
       <c r="A447" s="3"/>
       <c r="B447" s="3"/>
       <c r="C447" s="3"/>
@@ -19163,7 +19169,7 @@
       <c r="AK447" s="6"/>
       <c r="AL447" s="6"/>
     </row>
-    <row r="448" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:38" ht="15.95" customHeight="1">
       <c r="A448" s="3"/>
       <c r="B448" s="3"/>
       <c r="C448" s="3"/>
@@ -19203,7 +19209,7 @@
       <c r="AK448" s="6"/>
       <c r="AL448" s="6"/>
     </row>
-    <row r="449" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:38" ht="15.95" customHeight="1">
       <c r="A449" s="3"/>
       <c r="B449" s="3"/>
       <c r="C449" s="3"/>
@@ -19243,7 +19249,7 @@
       <c r="AK449" s="6"/>
       <c r="AL449" s="6"/>
     </row>
-    <row r="450" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:38" ht="15.95" customHeight="1">
       <c r="A450" s="3"/>
       <c r="B450" s="3"/>
       <c r="C450" s="3"/>
@@ -19283,7 +19289,7 @@
       <c r="AK450" s="6"/>
       <c r="AL450" s="6"/>
     </row>
-    <row r="451" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:38" ht="15.95" customHeight="1">
       <c r="A451" s="3"/>
       <c r="B451" s="3"/>
       <c r="C451" s="3"/>
@@ -19323,7 +19329,7 @@
       <c r="AK451" s="6"/>
       <c r="AL451" s="6"/>
     </row>
-    <row r="452" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:38" ht="15.95" customHeight="1">
       <c r="A452" s="3"/>
       <c r="B452" s="3"/>
       <c r="C452" s="3"/>
@@ -19363,7 +19369,7 @@
       <c r="AK452" s="6"/>
       <c r="AL452" s="6"/>
     </row>
-    <row r="453" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:38" ht="15.95" customHeight="1">
       <c r="A453" s="3"/>
       <c r="B453" s="3"/>
       <c r="C453" s="3"/>
@@ -19403,7 +19409,7 @@
       <c r="AK453" s="6"/>
       <c r="AL453" s="6"/>
     </row>
-    <row r="454" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:38" ht="15.95" customHeight="1">
       <c r="A454" s="3"/>
       <c r="B454" s="3"/>
       <c r="C454" s="3"/>
@@ -19443,7 +19449,7 @@
       <c r="AK454" s="6"/>
       <c r="AL454" s="6"/>
     </row>
-    <row r="455" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:38" ht="15.95" customHeight="1">
       <c r="A455" s="3"/>
       <c r="B455" s="3"/>
       <c r="C455" s="3"/>
@@ -19483,7 +19489,7 @@
       <c r="AK455" s="6"/>
       <c r="AL455" s="6"/>
     </row>
-    <row r="456" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:38" ht="15.95" customHeight="1">
       <c r="A456" s="3"/>
       <c r="B456" s="3"/>
       <c r="C456" s="3"/>
@@ -19523,7 +19529,7 @@
       <c r="AK456" s="6"/>
       <c r="AL456" s="6"/>
     </row>
-    <row r="457" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:38" ht="15.95" customHeight="1">
       <c r="A457" s="3"/>
       <c r="B457" s="3"/>
       <c r="C457" s="3"/>
@@ -19563,7 +19569,7 @@
       <c r="AK457" s="6"/>
       <c r="AL457" s="6"/>
     </row>
-    <row r="458" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:38" ht="15.95" customHeight="1">
       <c r="A458" s="3"/>
       <c r="B458" s="3"/>
       <c r="C458" s="3"/>
@@ -19603,7 +19609,7 @@
       <c r="AK458" s="6"/>
       <c r="AL458" s="6"/>
     </row>
-    <row r="459" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:38" ht="15.95" customHeight="1">
       <c r="A459" s="3"/>
       <c r="B459" s="3"/>
       <c r="C459" s="3"/>
@@ -19643,7 +19649,7 @@
       <c r="AK459" s="6"/>
       <c r="AL459" s="6"/>
     </row>
-    <row r="460" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:38" ht="15.95" customHeight="1">
       <c r="A460" s="3"/>
       <c r="B460" s="3"/>
       <c r="C460" s="3"/>
@@ -19683,7 +19689,7 @@
       <c r="AK460" s="6"/>
       <c r="AL460" s="6"/>
     </row>
-    <row r="461" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:38" ht="15.95" customHeight="1">
       <c r="A461" s="3"/>
       <c r="B461" s="3"/>
       <c r="C461" s="3"/>
@@ -19723,7 +19729,7 @@
       <c r="AK461" s="6"/>
       <c r="AL461" s="6"/>
     </row>
-    <row r="462" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:38" ht="15.95" customHeight="1">
       <c r="A462" s="3"/>
       <c r="B462" s="3"/>
       <c r="C462" s="3"/>
@@ -19763,7 +19769,7 @@
       <c r="AK462" s="6"/>
       <c r="AL462" s="6"/>
     </row>
-    <row r="463" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:38" ht="15.95" customHeight="1">
       <c r="A463" s="3"/>
       <c r="B463" s="3"/>
       <c r="C463" s="3"/>
@@ -19803,7 +19809,7 @@
       <c r="AK463" s="6"/>
       <c r="AL463" s="6"/>
     </row>
-    <row r="464" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:38" ht="15.95" customHeight="1">
       <c r="A464" s="3"/>
       <c r="B464" s="3"/>
       <c r="C464" s="3"/>
@@ -19843,7 +19849,7 @@
       <c r="AK464" s="6"/>
       <c r="AL464" s="6"/>
     </row>
-    <row r="465" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:38" ht="15.95" customHeight="1">
       <c r="A465" s="3"/>
       <c r="B465" s="3"/>
       <c r="C465" s="3"/>
@@ -19883,7 +19889,7 @@
       <c r="AK465" s="6"/>
       <c r="AL465" s="6"/>
     </row>
-    <row r="466" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:38" ht="15.95" customHeight="1">
       <c r="A466" s="3"/>
       <c r="B466" s="3"/>
       <c r="C466" s="3"/>
@@ -19923,7 +19929,7 @@
       <c r="AK466" s="6"/>
       <c r="AL466" s="6"/>
     </row>
-    <row r="467" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:38" ht="15.95" customHeight="1">
       <c r="A467" s="3"/>
       <c r="B467" s="3"/>
       <c r="C467" s="3"/>
@@ -19963,7 +19969,7 @@
       <c r="AK467" s="6"/>
       <c r="AL467" s="6"/>
     </row>
-    <row r="468" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:38" ht="15.95" customHeight="1">
       <c r="A468" s="3"/>
       <c r="B468" s="3"/>
       <c r="C468" s="3"/>
@@ -20003,7 +20009,7 @@
       <c r="AK468" s="6"/>
       <c r="AL468" s="6"/>
     </row>
-    <row r="469" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:38" ht="15.95" customHeight="1">
       <c r="A469" s="3"/>
       <c r="B469" s="3"/>
       <c r="C469" s="3"/>
@@ -20043,7 +20049,7 @@
       <c r="AK469" s="6"/>
       <c r="AL469" s="6"/>
     </row>
-    <row r="470" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:38" ht="15.95" customHeight="1">
       <c r="A470" s="3"/>
       <c r="B470" s="3"/>
       <c r="C470" s="3"/>
@@ -20083,7 +20089,7 @@
       <c r="AK470" s="6"/>
       <c r="AL470" s="6"/>
     </row>
-    <row r="471" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:38" ht="15.95" customHeight="1">
       <c r="A471" s="3"/>
       <c r="B471" s="3"/>
       <c r="C471" s="3"/>
@@ -20123,7 +20129,7 @@
       <c r="AK471" s="6"/>
       <c r="AL471" s="6"/>
     </row>
-    <row r="472" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:38" ht="15.95" customHeight="1">
       <c r="A472" s="3"/>
       <c r="B472" s="3"/>
       <c r="C472" s="3"/>
@@ -20163,7 +20169,7 @@
       <c r="AK472" s="6"/>
       <c r="AL472" s="6"/>
     </row>
-    <row r="473" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:38" ht="15.95" customHeight="1">
       <c r="A473" s="3"/>
       <c r="B473" s="3"/>
       <c r="C473" s="3"/>
@@ -20203,7 +20209,7 @@
       <c r="AK473" s="6"/>
       <c r="AL473" s="6"/>
     </row>
-    <row r="474" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:38" ht="15.95" customHeight="1">
       <c r="A474" s="3"/>
       <c r="B474" s="3"/>
       <c r="C474" s="3"/>
@@ -20243,7 +20249,7 @@
       <c r="AK474" s="6"/>
       <c r="AL474" s="6"/>
     </row>
-    <row r="475" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:38" ht="15.95" customHeight="1">
       <c r="A475" s="3"/>
       <c r="B475" s="3"/>
       <c r="C475" s="3"/>
@@ -20283,7 +20289,7 @@
       <c r="AK475" s="6"/>
       <c r="AL475" s="6"/>
     </row>
-    <row r="476" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:38" ht="15.95" customHeight="1">
       <c r="A476" s="3"/>
       <c r="B476" s="3"/>
       <c r="C476" s="3"/>
@@ -20323,7 +20329,7 @@
       <c r="AK476" s="6"/>
       <c r="AL476" s="6"/>
     </row>
-    <row r="477" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:38" ht="15.95" customHeight="1">
       <c r="A477" s="3"/>
       <c r="B477" s="3"/>
       <c r="C477" s="3"/>
@@ -20363,7 +20369,7 @@
       <c r="AK477" s="6"/>
       <c r="AL477" s="6"/>
     </row>
-    <row r="478" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:38" ht="15.95" customHeight="1">
       <c r="A478" s="3"/>
       <c r="B478" s="3"/>
       <c r="C478" s="3"/>
@@ -20403,7 +20409,7 @@
       <c r="AK478" s="6"/>
       <c r="AL478" s="6"/>
     </row>
-    <row r="479" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:38" ht="15.95" customHeight="1">
       <c r="A479" s="3"/>
       <c r="B479" s="3"/>
       <c r="C479" s="3"/>
@@ -20443,7 +20449,7 @@
       <c r="AK479" s="6"/>
       <c r="AL479" s="6"/>
     </row>
-    <row r="480" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:38" ht="15.95" customHeight="1">
       <c r="A480" s="3"/>
       <c r="B480" s="3"/>
       <c r="C480" s="3"/>
@@ -20483,7 +20489,7 @@
       <c r="AK480" s="6"/>
       <c r="AL480" s="6"/>
     </row>
-    <row r="481" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:38" ht="15.95" customHeight="1">
       <c r="A481" s="3"/>
       <c r="B481" s="3"/>
       <c r="C481" s="3"/>
@@ -20523,7 +20529,7 @@
       <c r="AK481" s="6"/>
       <c r="AL481" s="6"/>
     </row>
-    <row r="482" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:38" ht="15.95" customHeight="1">
       <c r="A482" s="3"/>
       <c r="B482" s="3"/>
       <c r="C482" s="3"/>
@@ -20563,7 +20569,7 @@
       <c r="AK482" s="6"/>
       <c r="AL482" s="6"/>
     </row>
-    <row r="483" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:38" ht="15.95" customHeight="1">
       <c r="A483" s="3"/>
       <c r="B483" s="3"/>
       <c r="C483" s="3"/>
@@ -20603,7 +20609,7 @@
       <c r="AK483" s="6"/>
       <c r="AL483" s="6"/>
     </row>
-    <row r="484" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:38" ht="15.95" customHeight="1">
       <c r="A484" s="3"/>
       <c r="B484" s="3"/>
       <c r="C484" s="3"/>
@@ -20643,7 +20649,7 @@
       <c r="AK484" s="6"/>
       <c r="AL484" s="6"/>
     </row>
-    <row r="485" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:38" ht="15.95" customHeight="1">
       <c r="A485" s="3"/>
       <c r="B485" s="3"/>
       <c r="C485" s="3"/>
@@ -20683,7 +20689,7 @@
       <c r="AK485" s="6"/>
       <c r="AL485" s="6"/>
     </row>
-    <row r="486" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:38" ht="15.95" customHeight="1">
       <c r="A486" s="3"/>
       <c r="B486" s="3"/>
       <c r="C486" s="3"/>
@@ -20723,7 +20729,7 @@
       <c r="AK486" s="6"/>
       <c r="AL486" s="6"/>
     </row>
-    <row r="487" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:38" ht="15.95" customHeight="1">
       <c r="A487" s="3"/>
       <c r="B487" s="3"/>
       <c r="C487" s="3"/>
@@ -20763,7 +20769,7 @@
       <c r="AK487" s="6"/>
       <c r="AL487" s="6"/>
     </row>
-    <row r="488" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:38" ht="15.95" customHeight="1">
       <c r="A488" s="3"/>
       <c r="B488" s="3"/>
       <c r="C488" s="3"/>
@@ -20803,7 +20809,7 @@
       <c r="AK488" s="6"/>
       <c r="AL488" s="6"/>
     </row>
-    <row r="489" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:38" ht="15.95" customHeight="1">
       <c r="A489" s="3"/>
       <c r="B489" s="3"/>
       <c r="C489" s="3"/>
@@ -20843,7 +20849,7 @@
       <c r="AK489" s="6"/>
       <c r="AL489" s="6"/>
     </row>
-    <row r="490" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:38" ht="15.95" customHeight="1">
       <c r="A490" s="3"/>
       <c r="B490" s="3"/>
       <c r="C490" s="3"/>
@@ -20883,7 +20889,7 @@
       <c r="AK490" s="6"/>
       <c r="AL490" s="6"/>
     </row>
-    <row r="491" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:38" ht="15.95" customHeight="1">
       <c r="A491" s="3"/>
       <c r="B491" s="3"/>
       <c r="C491" s="3"/>
@@ -20923,7 +20929,7 @@
       <c r="AK491" s="6"/>
       <c r="AL491" s="6"/>
     </row>
-    <row r="492" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:38" ht="15.95" customHeight="1">
       <c r="A492" s="3"/>
       <c r="B492" s="3"/>
       <c r="C492" s="3"/>
@@ -20963,7 +20969,7 @@
       <c r="AK492" s="6"/>
       <c r="AL492" s="6"/>
     </row>
-    <row r="493" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:38" ht="15.95" customHeight="1">
       <c r="A493" s="3"/>
       <c r="B493" s="3"/>
       <c r="C493" s="3"/>
@@ -21003,7 +21009,7 @@
       <c r="AK493" s="6"/>
       <c r="AL493" s="6"/>
     </row>
-    <row r="494" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:38" ht="15.95" customHeight="1">
       <c r="A494" s="3"/>
       <c r="B494" s="3"/>
       <c r="C494" s="3"/>
@@ -21043,7 +21049,7 @@
       <c r="AK494" s="6"/>
       <c r="AL494" s="6"/>
     </row>
-    <row r="495" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:38" ht="15.95" customHeight="1">
       <c r="A495" s="3"/>
       <c r="B495" s="3"/>
       <c r="C495" s="3"/>
@@ -21083,7 +21089,7 @@
       <c r="AK495" s="6"/>
       <c r="AL495" s="6"/>
     </row>
-    <row r="496" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:38" ht="15.95" customHeight="1">
       <c r="A496" s="3"/>
       <c r="B496" s="3"/>
       <c r="C496" s="3"/>
@@ -21123,7 +21129,7 @@
       <c r="AK496" s="6"/>
       <c r="AL496" s="6"/>
     </row>
-    <row r="497" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:38" ht="15.95" customHeight="1">
       <c r="A497" s="3"/>
       <c r="B497" s="3"/>
       <c r="C497" s="3"/>
@@ -21163,7 +21169,7 @@
       <c r="AK497" s="6"/>
       <c r="AL497" s="6"/>
     </row>
-    <row r="498" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:38" ht="15.95" customHeight="1">
       <c r="A498" s="3"/>
       <c r="B498" s="3"/>
       <c r="C498" s="3"/>
@@ -21203,7 +21209,7 @@
       <c r="AK498" s="6"/>
       <c r="AL498" s="6"/>
     </row>
-    <row r="499" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:38" ht="15.95" customHeight="1">
       <c r="A499" s="3"/>
       <c r="B499" s="3"/>
       <c r="C499" s="3"/>
@@ -21243,7 +21249,7 @@
       <c r="AK499" s="6"/>
       <c r="AL499" s="6"/>
     </row>
-    <row r="500" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:38" ht="15.95" customHeight="1">
       <c r="A500" s="3"/>
       <c r="B500" s="3"/>
       <c r="C500" s="3"/>
@@ -21283,7 +21289,7 @@
       <c r="AK500" s="6"/>
       <c r="AL500" s="6"/>
     </row>
-    <row r="501" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:38" ht="15.95" customHeight="1">
       <c r="A501" s="3"/>
       <c r="B501" s="3"/>
       <c r="C501" s="3"/>
@@ -21323,7 +21329,7 @@
       <c r="AK501" s="6"/>
       <c r="AL501" s="6"/>
     </row>
-    <row r="502" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:38" ht="15.95" customHeight="1">
       <c r="A502" s="3"/>
       <c r="B502" s="3"/>
       <c r="C502" s="3"/>
@@ -21363,7 +21369,7 @@
       <c r="AK502" s="6"/>
       <c r="AL502" s="6"/>
     </row>
-    <row r="503" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:38" ht="15.95" customHeight="1">
       <c r="A503" s="3"/>
       <c r="B503" s="3"/>
       <c r="C503" s="3"/>
@@ -21403,7 +21409,7 @@
       <c r="AK503" s="6"/>
       <c r="AL503" s="6"/>
     </row>
-    <row r="504" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:38" ht="15.95" customHeight="1">
       <c r="A504" s="3"/>
       <c r="B504" s="3"/>
       <c r="C504" s="3"/>
@@ -21443,7 +21449,7 @@
       <c r="AK504" s="6"/>
       <c r="AL504" s="6"/>
     </row>
-    <row r="505" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:38" ht="15.95" customHeight="1">
       <c r="A505" s="3"/>
       <c r="B505" s="3"/>
       <c r="C505" s="3"/>
@@ -21483,7 +21489,7 @@
       <c r="AK505" s="6"/>
       <c r="AL505" s="6"/>
     </row>
-    <row r="506" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:38" ht="15.95" customHeight="1">
       <c r="A506" s="3"/>
       <c r="B506" s="3"/>
       <c r="C506" s="3"/>
@@ -21523,7 +21529,7 @@
       <c r="AK506" s="6"/>
       <c r="AL506" s="6"/>
     </row>
-    <row r="507" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:38" ht="15.95" customHeight="1">
       <c r="A507" s="3"/>
       <c r="B507" s="3"/>
       <c r="C507" s="3"/>
@@ -21563,7 +21569,7 @@
       <c r="AK507" s="6"/>
       <c r="AL507" s="6"/>
     </row>
-    <row r="508" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:38" ht="15.95" customHeight="1">
       <c r="A508" s="3"/>
       <c r="B508" s="3"/>
       <c r="C508" s="3"/>
@@ -21603,7 +21609,7 @@
       <c r="AK508" s="6"/>
       <c r="AL508" s="6"/>
     </row>
-    <row r="509" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:38" ht="15.95" customHeight="1">
       <c r="A509" s="3"/>
       <c r="B509" s="3"/>
       <c r="C509" s="3"/>
@@ -21643,7 +21649,7 @@
       <c r="AK509" s="6"/>
       <c r="AL509" s="6"/>
     </row>
-    <row r="510" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:38" ht="15.95" customHeight="1">
       <c r="A510" s="3"/>
       <c r="B510" s="3"/>
       <c r="C510" s="3"/>
@@ -21683,7 +21689,7 @@
       <c r="AK510" s="6"/>
       <c r="AL510" s="6"/>
     </row>
-    <row r="511" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:38" ht="15.95" customHeight="1">
       <c r="A511" s="3"/>
       <c r="B511" s="3"/>
       <c r="C511" s="3"/>
@@ -21723,7 +21729,7 @@
       <c r="AK511" s="6"/>
       <c r="AL511" s="6"/>
     </row>
-    <row r="512" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:38" ht="15.95" customHeight="1">
       <c r="A512" s="3"/>
       <c r="B512" s="3"/>
       <c r="C512" s="3"/>
@@ -21763,7 +21769,7 @@
       <c r="AK512" s="6"/>
       <c r="AL512" s="6"/>
     </row>
-    <row r="513" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:38" ht="15.95" customHeight="1">
       <c r="A513" s="3"/>
       <c r="B513" s="3"/>
       <c r="C513" s="3"/>
@@ -21803,7 +21809,7 @@
       <c r="AK513" s="6"/>
       <c r="AL513" s="6"/>
     </row>
-    <row r="514" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:38" ht="15.95" customHeight="1">
       <c r="A514" s="3"/>
       <c r="B514" s="3"/>
       <c r="C514" s="3"/>
@@ -21843,7 +21849,7 @@
       <c r="AK514" s="6"/>
       <c r="AL514" s="6"/>
     </row>
-    <row r="515" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:38" ht="15.95" customHeight="1">
       <c r="A515" s="3"/>
       <c r="B515" s="3"/>
       <c r="C515" s="3"/>
@@ -21883,7 +21889,7 @@
       <c r="AK515" s="6"/>
       <c r="AL515" s="6"/>
     </row>
-    <row r="516" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:38" ht="15.95" customHeight="1">
       <c r="A516" s="3"/>
       <c r="B516" s="3"/>
       <c r="C516" s="3"/>
@@ -21923,7 +21929,7 @@
       <c r="AK516" s="6"/>
       <c r="AL516" s="6"/>
     </row>
-    <row r="517" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:38" ht="15.95" customHeight="1">
       <c r="A517" s="3"/>
       <c r="B517" s="3"/>
       <c r="C517" s="3"/>
@@ -21963,7 +21969,7 @@
       <c r="AK517" s="6"/>
       <c r="AL517" s="6"/>
     </row>
-    <row r="518" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:38" ht="15.95" customHeight="1">
       <c r="A518" s="3"/>
       <c r="B518" s="3"/>
       <c r="C518" s="3"/>
@@ -22003,7 +22009,7 @@
       <c r="AK518" s="6"/>
       <c r="AL518" s="6"/>
     </row>
-    <row r="519" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:38" ht="15.95" customHeight="1">
       <c r="A519" s="3"/>
       <c r="B519" s="3"/>
       <c r="C519" s="3"/>
@@ -22043,7 +22049,7 @@
       <c r="AK519" s="6"/>
       <c r="AL519" s="6"/>
     </row>
-    <row r="520" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:38" ht="15.95" customHeight="1">
       <c r="A520" s="3"/>
       <c r="B520" s="3"/>
       <c r="C520" s="3"/>
@@ -22083,7 +22089,7 @@
       <c r="AK520" s="6"/>
       <c r="AL520" s="6"/>
     </row>
-    <row r="521" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:38" ht="15.95" customHeight="1">
       <c r="A521" s="3"/>
       <c r="B521" s="3"/>
       <c r="C521" s="3"/>
@@ -22123,7 +22129,7 @@
       <c r="AK521" s="6"/>
       <c r="AL521" s="6"/>
     </row>
-    <row r="522" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:38" ht="15.95" customHeight="1">
       <c r="A522" s="3"/>
       <c r="B522" s="3"/>
       <c r="C522" s="3"/>
@@ -22163,7 +22169,7 @@
       <c r="AK522" s="6"/>
       <c r="AL522" s="6"/>
     </row>
-    <row r="523" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:38" ht="15.95" customHeight="1">
       <c r="A523" s="3"/>
       <c r="B523" s="3"/>
       <c r="C523" s="3"/>
@@ -22203,7 +22209,7 @@
       <c r="AK523" s="6"/>
       <c r="AL523" s="6"/>
     </row>
-    <row r="524" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:38" ht="15.95" customHeight="1">
       <c r="A524" s="3"/>
       <c r="B524" s="3"/>
       <c r="C524" s="3"/>
@@ -22243,7 +22249,7 @@
       <c r="AK524" s="6"/>
       <c r="AL524" s="6"/>
     </row>
-    <row r="525" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:38" ht="15.95" customHeight="1">
       <c r="A525" s="3"/>
       <c r="B525" s="3"/>
       <c r="C525" s="3"/>
@@ -22283,7 +22289,7 @@
       <c r="AK525" s="6"/>
       <c r="AL525" s="6"/>
     </row>
-    <row r="526" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:38" ht="15.95" customHeight="1">
       <c r="A526" s="3"/>
       <c r="B526" s="3"/>
       <c r="C526" s="3"/>
@@ -22323,7 +22329,7 @@
       <c r="AK526" s="6"/>
       <c r="AL526" s="6"/>
     </row>
-    <row r="527" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:38" ht="15.95" customHeight="1">
       <c r="A527" s="3"/>
       <c r="B527" s="3"/>
       <c r="C527" s="3"/>
@@ -22363,7 +22369,7 @@
       <c r="AK527" s="6"/>
       <c r="AL527" s="6"/>
     </row>
-    <row r="528" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:38" ht="15.95" customHeight="1">
       <c r="A528" s="3"/>
       <c r="B528" s="3"/>
       <c r="C528" s="3"/>
@@ -22403,7 +22409,7 @@
       <c r="AK528" s="6"/>
       <c r="AL528" s="6"/>
     </row>
-    <row r="529" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:38" ht="15.95" customHeight="1">
       <c r="A529" s="3"/>
       <c r="B529" s="3"/>
       <c r="C529" s="3"/>
@@ -22443,7 +22449,7 @@
       <c r="AK529" s="6"/>
       <c r="AL529" s="6"/>
     </row>
-    <row r="530" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:38" ht="15.95" customHeight="1">
       <c r="A530" s="3"/>
       <c r="B530" s="3"/>
       <c r="C530" s="3"/>
@@ -22483,7 +22489,7 @@
       <c r="AK530" s="6"/>
       <c r="AL530" s="6"/>
     </row>
-    <row r="531" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:38" ht="15.95" customHeight="1">
       <c r="A531" s="3"/>
       <c r="B531" s="3"/>
       <c r="C531" s="3"/>
@@ -22523,7 +22529,7 @@
       <c r="AK531" s="6"/>
       <c r="AL531" s="6"/>
     </row>
-    <row r="532" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:38" ht="15.95" customHeight="1">
       <c r="A532" s="3"/>
       <c r="B532" s="3"/>
       <c r="C532" s="3"/>
@@ -22563,7 +22569,7 @@
       <c r="AK532" s="6"/>
       <c r="AL532" s="6"/>
     </row>
-    <row r="533" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:38" ht="15.95" customHeight="1">
       <c r="A533" s="3"/>
       <c r="B533" s="3"/>
       <c r="C533" s="3"/>
@@ -22603,7 +22609,7 @@
       <c r="AK533" s="6"/>
       <c r="AL533" s="6"/>
     </row>
-    <row r="534" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:38" ht="15.95" customHeight="1">
       <c r="A534" s="3"/>
       <c r="B534" s="3"/>
       <c r="C534" s="3"/>
@@ -22643,7 +22649,7 @@
       <c r="AK534" s="6"/>
       <c r="AL534" s="6"/>
     </row>
-    <row r="535" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:38" ht="15.95" customHeight="1">
       <c r="A535" s="3"/>
       <c r="B535" s="3"/>
       <c r="C535" s="3"/>
@@ -22683,7 +22689,7 @@
       <c r="AK535" s="6"/>
       <c r="AL535" s="6"/>
     </row>
-    <row r="536" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:38" ht="15.95" customHeight="1">
       <c r="A536" s="3"/>
       <c r="B536" s="3"/>
       <c r="C536" s="3"/>
@@ -22723,7 +22729,7 @@
       <c r="AK536" s="6"/>
       <c r="AL536" s="6"/>
     </row>
-    <row r="537" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:38" ht="15.95" customHeight="1">
       <c r="A537" s="3"/>
       <c r="B537" s="3"/>
       <c r="C537" s="3"/>
@@ -22763,7 +22769,7 @@
       <c r="AK537" s="6"/>
       <c r="AL537" s="6"/>
     </row>
-    <row r="538" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:38" ht="15.95" customHeight="1">
       <c r="A538" s="3"/>
       <c r="B538" s="3"/>
       <c r="C538" s="3"/>
@@ -22803,7 +22809,7 @@
       <c r="AK538" s="6"/>
       <c r="AL538" s="6"/>
     </row>
-    <row r="539" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:38" ht="15.95" customHeight="1">
       <c r="A539" s="3"/>
       <c r="B539" s="3"/>
       <c r="C539" s="3"/>
@@ -22843,7 +22849,7 @@
       <c r="AK539" s="6"/>
       <c r="AL539" s="6"/>
     </row>
-    <row r="540" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:38" ht="15.95" customHeight="1">
       <c r="A540" s="3"/>
       <c r="B540" s="3"/>
       <c r="C540" s="3"/>
@@ -22883,7 +22889,7 @@
       <c r="AK540" s="6"/>
       <c r="AL540" s="6"/>
     </row>
-    <row r="541" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:38" ht="15.95" customHeight="1">
       <c r="A541" s="3"/>
       <c r="B541" s="3"/>
       <c r="C541" s="3"/>
@@ -22923,7 +22929,7 @@
       <c r="AK541" s="6"/>
       <c r="AL541" s="6"/>
     </row>
-    <row r="542" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:38" ht="15.95" customHeight="1">
       <c r="A542" s="3"/>
       <c r="B542" s="3"/>
       <c r="C542" s="3"/>
@@ -22963,7 +22969,7 @@
       <c r="AK542" s="6"/>
       <c r="AL542" s="6"/>
     </row>
-    <row r="543" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:38" ht="15.95" customHeight="1">
       <c r="A543" s="3"/>
       <c r="B543" s="3"/>
       <c r="C543" s="3"/>
@@ -23003,7 +23009,7 @@
       <c r="AK543" s="6"/>
       <c r="AL543" s="6"/>
     </row>
-    <row r="544" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:38" ht="15.95" customHeight="1">
       <c r="A544" s="3"/>
       <c r="B544" s="3"/>
       <c r="C544" s="3"/>
@@ -23043,7 +23049,7 @@
       <c r="AK544" s="6"/>
       <c r="AL544" s="6"/>
     </row>
-    <row r="545" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:38" ht="15.95" customHeight="1">
       <c r="A545" s="3"/>
       <c r="B545" s="3"/>
       <c r="C545" s="3"/>
@@ -23083,7 +23089,7 @@
       <c r="AK545" s="6"/>
       <c r="AL545" s="6"/>
     </row>
-    <row r="546" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:38" ht="15.95" customHeight="1">
       <c r="A546" s="3"/>
       <c r="B546" s="3"/>
       <c r="C546" s="3"/>
@@ -23123,7 +23129,7 @@
       <c r="AK546" s="6"/>
       <c r="AL546" s="6"/>
     </row>
-    <row r="547" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:38" ht="15.95" customHeight="1">
       <c r="A547" s="3"/>
       <c r="B547" s="3"/>
       <c r="C547" s="3"/>
@@ -23163,7 +23169,7 @@
       <c r="AK547" s="6"/>
       <c r="AL547" s="6"/>
     </row>
-    <row r="548" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:38" ht="15.95" customHeight="1">
       <c r="A548" s="3"/>
       <c r="B548" s="3"/>
       <c r="C548" s="3"/>
@@ -23203,7 +23209,7 @@
       <c r="AK548" s="6"/>
       <c r="AL548" s="6"/>
     </row>
-    <row r="549" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:38" ht="15.95" customHeight="1">
       <c r="A549" s="3"/>
       <c r="B549" s="3"/>
       <c r="C549" s="3"/>
@@ -23243,7 +23249,7 @@
       <c r="AK549" s="6"/>
       <c r="AL549" s="6"/>
     </row>
-    <row r="550" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:38" ht="15.95" customHeight="1">
       <c r="A550" s="3"/>
       <c r="B550" s="3"/>
       <c r="C550" s="3"/>
@@ -23283,7 +23289,7 @@
       <c r="AK550" s="6"/>
       <c r="AL550" s="6"/>
     </row>
-    <row r="551" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:38" ht="15.95" customHeight="1">
       <c r="A551" s="3"/>
       <c r="B551" s="3"/>
       <c r="C551" s="3"/>
@@ -23323,7 +23329,7 @@
       <c r="AK551" s="6"/>
       <c r="AL551" s="6"/>
     </row>
-    <row r="552" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:38" ht="15.95" customHeight="1">
       <c r="A552" s="3"/>
       <c r="B552" s="3"/>
       <c r="C552" s="3"/>
@@ -23363,7 +23369,7 @@
       <c r="AK552" s="6"/>
       <c r="AL552" s="6"/>
     </row>
-    <row r="553" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:38" ht="15.95" customHeight="1">
       <c r="A553" s="3"/>
       <c r="B553" s="3"/>
       <c r="C553" s="3"/>
@@ -23403,7 +23409,7 @@
       <c r="AK553" s="6"/>
       <c r="AL553" s="6"/>
     </row>
-    <row r="554" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:38" ht="15.95" customHeight="1">
       <c r="A554" s="3"/>
       <c r="B554" s="3"/>
       <c r="C554" s="3"/>
@@ -23443,7 +23449,7 @@
       <c r="AK554" s="6"/>
       <c r="AL554" s="6"/>
     </row>
-    <row r="555" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:38" ht="15.95" customHeight="1">
       <c r="A555" s="3"/>
       <c r="B555" s="3"/>
       <c r="C555" s="3"/>
@@ -23483,7 +23489,7 @@
       <c r="AK555" s="6"/>
       <c r="AL555" s="6"/>
     </row>
-    <row r="556" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:38" ht="15.95" customHeight="1">
       <c r="A556" s="3"/>
       <c r="B556" s="3"/>
       <c r="C556" s="3"/>
@@ -23523,7 +23529,7 @@
       <c r="AK556" s="6"/>
       <c r="AL556" s="6"/>
     </row>
-    <row r="557" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:38" ht="15.95" customHeight="1">
       <c r="A557" s="3"/>
       <c r="B557" s="3"/>
       <c r="C557" s="3"/>
@@ -23563,7 +23569,7 @@
       <c r="AK557" s="6"/>
       <c r="AL557" s="6"/>
     </row>
-    <row r="558" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:38" ht="15.95" customHeight="1">
       <c r="A558" s="3"/>
       <c r="B558" s="3"/>
       <c r="C558" s="3"/>
@@ -23603,7 +23609,7 @@
       <c r="AK558" s="6"/>
       <c r="AL558" s="6"/>
     </row>
-    <row r="559" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:38" ht="15.95" customHeight="1">
       <c r="A559" s="3"/>
       <c r="B559" s="3"/>
       <c r="C559" s="3"/>
@@ -23643,7 +23649,7 @@
       <c r="AK559" s="6"/>
       <c r="AL559" s="6"/>
     </row>
-    <row r="560" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:38" ht="15.95" customHeight="1">
       <c r="A560" s="3"/>
       <c r="B560" s="3"/>
       <c r="C560" s="3"/>
@@ -23683,7 +23689,7 @@
       <c r="AK560" s="6"/>
       <c r="AL560" s="6"/>
     </row>
-    <row r="561" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:38" ht="15.95" customHeight="1">
       <c r="A561" s="3"/>
       <c r="B561" s="3"/>
       <c r="C561" s="3"/>
@@ -23723,7 +23729,7 @@
       <c r="AK561" s="6"/>
       <c r="AL561" s="6"/>
     </row>
-    <row r="562" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:38" ht="15.95" customHeight="1">
       <c r="A562" s="3"/>
       <c r="B562" s="3"/>
       <c r="C562" s="3"/>
@@ -23763,7 +23769,7 @@
       <c r="AK562" s="6"/>
       <c r="AL562" s="6"/>
     </row>
-    <row r="563" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:38" ht="15.95" customHeight="1">
       <c r="A563" s="3"/>
       <c r="B563" s="3"/>
       <c r="C563" s="3"/>
@@ -23803,7 +23809,7 @@
       <c r="AK563" s="6"/>
       <c r="AL563" s="6"/>
     </row>
-    <row r="564" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:38" ht="15.95" customHeight="1">
       <c r="A564" s="3"/>
       <c r="B564" s="3"/>
       <c r="C564" s="3"/>
@@ -23843,7 +23849,7 @@
       <c r="AK564" s="6"/>
       <c r="AL564" s="6"/>
     </row>
-    <row r="565" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:38" ht="15.95" customHeight="1">
       <c r="A565" s="3"/>
       <c r="B565" s="3"/>
       <c r="C565" s="3"/>
@@ -23883,7 +23889,7 @@
       <c r="AK565" s="6"/>
       <c r="AL565" s="6"/>
     </row>
-    <row r="566" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:38" ht="15.95" customHeight="1">
       <c r="A566" s="3"/>
       <c r="B566" s="3"/>
       <c r="C566" s="3"/>
@@ -23923,7 +23929,7 @@
       <c r="AK566" s="6"/>
       <c r="AL566" s="6"/>
     </row>
-    <row r="567" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:38" ht="15.95" customHeight="1">
       <c r="A567" s="3"/>
       <c r="B567" s="3"/>
       <c r="C567" s="3"/>
@@ -23963,7 +23969,7 @@
       <c r="AK567" s="6"/>
       <c r="AL567" s="6"/>
     </row>
-    <row r="568" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:38" ht="15.95" customHeight="1">
       <c r="A568" s="3"/>
       <c r="B568" s="3"/>
       <c r="C568" s="3"/>
@@ -24003,7 +24009,7 @@
       <c r="AK568" s="6"/>
       <c r="AL568" s="6"/>
     </row>
-    <row r="569" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:38" ht="15.95" customHeight="1">
       <c r="A569" s="3"/>
       <c r="B569" s="3"/>
       <c r="C569" s="3"/>
@@ -24043,7 +24049,7 @@
       <c r="AK569" s="6"/>
       <c r="AL569" s="6"/>
     </row>
-    <row r="570" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:38" ht="15.95" customHeight="1">
       <c r="A570" s="3"/>
       <c r="B570" s="3"/>
       <c r="C570" s="3"/>
@@ -24083,7 +24089,7 @@
       <c r="AK570" s="6"/>
       <c r="AL570" s="6"/>
     </row>
-    <row r="571" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:38" ht="15.95" customHeight="1">
       <c r="A571" s="3"/>
       <c r="B571" s="3"/>
       <c r="C571" s="3"/>
@@ -24123,7 +24129,7 @@
       <c r="AK571" s="6"/>
       <c r="AL571" s="6"/>
     </row>
-    <row r="572" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:38" ht="15.95" customHeight="1">
       <c r="A572" s="3"/>
       <c r="B572" s="3"/>
       <c r="C572" s="3"/>
@@ -24163,7 +24169,7 @@
       <c r="AK572" s="6"/>
       <c r="AL572" s="6"/>
     </row>
-    <row r="573" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:38" ht="15.95" customHeight="1">
       <c r="A573" s="3"/>
       <c r="B573" s="3"/>
       <c r="C573" s="3"/>
@@ -24203,7 +24209,7 @@
       <c r="AK573" s="6"/>
       <c r="AL573" s="6"/>
     </row>
-    <row r="574" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:38" ht="15.95" customHeight="1">
       <c r="A574" s="3"/>
       <c r="B574" s="3"/>
       <c r="C574" s="3"/>
@@ -24243,7 +24249,7 @@
       <c r="AK574" s="6"/>
       <c r="AL574" s="6"/>
     </row>
-    <row r="575" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:38" ht="15.95" customHeight="1">
       <c r="A575" s="3"/>
       <c r="B575" s="3"/>
       <c r="C575" s="3"/>
@@ -24283,7 +24289,7 @@
       <c r="AK575" s="6"/>
       <c r="AL575" s="6"/>
     </row>
-    <row r="576" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:38" ht="15.95" customHeight="1">
       <c r="A576" s="3"/>
       <c r="B576" s="3"/>
       <c r="C576" s="3"/>
@@ -24323,7 +24329,7 @@
       <c r="AK576" s="6"/>
       <c r="AL576" s="6"/>
     </row>
-    <row r="577" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:38" ht="15.95" customHeight="1">
       <c r="A577" s="3"/>
       <c r="B577" s="3"/>
       <c r="C577" s="3"/>
@@ -24363,7 +24369,7 @@
       <c r="AK577" s="6"/>
       <c r="AL577" s="6"/>
     </row>
-    <row r="578" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:38" ht="15.95" customHeight="1">
       <c r="A578" s="3"/>
       <c r="B578" s="3"/>
       <c r="C578" s="3"/>
@@ -24403,7 +24409,7 @@
       <c r="AK578" s="6"/>
       <c r="AL578" s="6"/>
     </row>
-    <row r="579" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:38" ht="15.95" customHeight="1">
       <c r="A579" s="3"/>
       <c r="B579" s="3"/>
       <c r="C579" s="3"/>
@@ -24443,7 +24449,7 @@
       <c r="AK579" s="6"/>
       <c r="AL579" s="6"/>
     </row>
-    <row r="580" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:38" ht="15.95" customHeight="1">
       <c r="A580" s="3"/>
       <c r="B580" s="3"/>
       <c r="C580" s="3"/>
@@ -24483,7 +24489,7 @@
       <c r="AK580" s="6"/>
       <c r="AL580" s="6"/>
     </row>
-    <row r="581" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:38" ht="15.95" customHeight="1">
       <c r="A581" s="3"/>
       <c r="B581" s="3"/>
       <c r="C581" s="3"/>
@@ -24523,7 +24529,7 @@
       <c r="AK581" s="6"/>
       <c r="AL581" s="6"/>
     </row>
-    <row r="582" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:38" ht="15.95" customHeight="1">
       <c r="A582" s="3"/>
       <c r="B582" s="3"/>
       <c r="C582" s="3"/>
@@ -24563,7 +24569,7 @@
       <c r="AK582" s="6"/>
       <c r="AL582" s="6"/>
     </row>
-    <row r="583" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:38" ht="15.95" customHeight="1">
       <c r="A583" s="3"/>
       <c r="B583" s="3"/>
       <c r="C583" s="3"/>
@@ -24603,7 +24609,7 @@
       <c r="AK583" s="6"/>
       <c r="AL583" s="6"/>
     </row>
-    <row r="584" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:38" ht="15.95" customHeight="1">
       <c r="A584" s="3"/>
       <c r="B584" s="3"/>
       <c r="C584" s="3"/>
@@ -24643,7 +24649,7 @@
       <c r="AK584" s="6"/>
       <c r="AL584" s="6"/>
     </row>
-    <row r="585" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:38" ht="15.95" customHeight="1">
       <c r="A585" s="3"/>
       <c r="B585" s="3"/>
       <c r="C585" s="3"/>
@@ -24683,7 +24689,7 @@
       <c r="AK585" s="6"/>
       <c r="AL585" s="6"/>
     </row>
-    <row r="586" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:38" ht="15.95" customHeight="1">
       <c r="A586" s="3"/>
       <c r="B586" s="3"/>
       <c r="C586" s="3"/>
@@ -24723,7 +24729,7 @@
       <c r="AK586" s="6"/>
       <c r="AL586" s="6"/>
     </row>
-    <row r="587" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:38" ht="15.95" customHeight="1">
       <c r="A587" s="3"/>
       <c r="B587" s="3"/>
       <c r="C587" s="3"/>
@@ -24763,7 +24769,7 @@
       <c r="AK587" s="6"/>
       <c r="AL587" s="6"/>
     </row>
-    <row r="588" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:38" ht="15.95" customHeight="1">
       <c r="A588" s="3"/>
       <c r="B588" s="3"/>
       <c r="C588" s="3"/>
@@ -24803,7 +24809,7 @@
       <c r="AK588" s="6"/>
       <c r="AL588" s="6"/>
     </row>
-    <row r="589" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:38" ht="15.95" customHeight="1">
       <c r="A589" s="3"/>
       <c r="B589" s="3"/>
       <c r="C589" s="3"/>
@@ -24843,7 +24849,7 @@
       <c r="AK589" s="6"/>
       <c r="AL589" s="6"/>
     </row>
-    <row r="590" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:38" ht="15.95" customHeight="1">
       <c r="A590" s="3"/>
       <c r="B590" s="3"/>
       <c r="C590" s="3"/>
@@ -24883,7 +24889,7 @@
       <c r="AK590" s="6"/>
       <c r="AL590" s="6"/>
     </row>
-    <row r="591" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:38" ht="15.95" customHeight="1">
       <c r="A591" s="3"/>
       <c r="B591" s="3"/>
       <c r="C591" s="3"/>
@@ -24923,7 +24929,7 @@
       <c r="AK591" s="6"/>
       <c r="AL591" s="6"/>
     </row>
-    <row r="592" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:38" ht="15.95" customHeight="1">
       <c r="A592" s="3"/>
       <c r="B592" s="3"/>
       <c r="C592" s="3"/>
@@ -24963,7 +24969,7 @@
       <c r="AK592" s="6"/>
       <c r="AL592" s="6"/>
     </row>
-    <row r="593" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:38" ht="15.95" customHeight="1">
       <c r="A593" s="3"/>
       <c r="B593" s="3"/>
       <c r="C593" s="3"/>
@@ -25003,7 +25009,7 @@
       <c r="AK593" s="6"/>
       <c r="AL593" s="6"/>
     </row>
-    <row r="594" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:38" ht="15.95" customHeight="1">
       <c r="A594" s="3"/>
       <c r="B594" s="3"/>
       <c r="C594" s="3"/>
@@ -25043,7 +25049,7 @@
       <c r="AK594" s="6"/>
       <c r="AL594" s="6"/>
     </row>
-    <row r="595" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:38" ht="15.95" customHeight="1">
       <c r="A595" s="3"/>
       <c r="B595" s="3"/>
       <c r="C595" s="3"/>
@@ -25083,7 +25089,7 @@
       <c r="AK595" s="6"/>
       <c r="AL595" s="6"/>
     </row>
-    <row r="596" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:38" ht="15.95" customHeight="1">
       <c r="A596" s="3"/>
       <c r="B596" s="3"/>
       <c r="C596" s="3"/>
@@ -25123,7 +25129,7 @@
       <c r="AK596" s="6"/>
       <c r="AL596" s="6"/>
     </row>
-    <row r="597" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:38" ht="15.95" customHeight="1">
       <c r="A597" s="3"/>
       <c r="B597" s="3"/>
       <c r="C597" s="3"/>
@@ -25163,7 +25169,7 @@
       <c r="AK597" s="6"/>
       <c r="AL597" s="6"/>
     </row>
-    <row r="598" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:38" ht="15.95" customHeight="1">
       <c r="A598" s="3"/>
       <c r="B598" s="3"/>
       <c r="C598" s="3"/>
@@ -25203,7 +25209,7 @@
       <c r="AK598" s="6"/>
       <c r="AL598" s="6"/>
     </row>
-    <row r="599" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:38" ht="15.95" customHeight="1">
       <c r="A599" s="3"/>
       <c r="B599" s="3"/>
       <c r="C599" s="3"/>
@@ -25243,7 +25249,7 @@
       <c r="AK599" s="6"/>
       <c r="AL599" s="6"/>
     </row>
-    <row r="600" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:38" ht="15.95" customHeight="1">
       <c r="A600" s="3"/>
       <c r="B600" s="3"/>
       <c r="C600" s="3"/>
@@ -25283,7 +25289,7 @@
       <c r="AK600" s="6"/>
       <c r="AL600" s="6"/>
     </row>
-    <row r="601" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:38" ht="15.95" customHeight="1">
       <c r="A601" s="3"/>
       <c r="B601" s="3"/>
       <c r="C601" s="3"/>
@@ -25323,7 +25329,7 @@
       <c r="AK601" s="6"/>
       <c r="AL601" s="6"/>
     </row>
-    <row r="602" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:38" ht="15.95" customHeight="1">
       <c r="A602" s="3"/>
       <c r="B602" s="3"/>
       <c r="C602" s="3"/>
@@ -25363,7 +25369,7 @@
       <c r="AK602" s="6"/>
       <c r="AL602" s="6"/>
     </row>
-    <row r="603" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:38" ht="15.95" customHeight="1">
       <c r="A603" s="3"/>
       <c r="B603" s="3"/>
       <c r="C603" s="3"/>
@@ -25403,7 +25409,7 @@
       <c r="AK603" s="6"/>
       <c r="AL603" s="6"/>
     </row>
-    <row r="604" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:38" ht="15.95" customHeight="1">
       <c r="A604" s="3"/>
       <c r="B604" s="3"/>
       <c r="C604" s="3"/>
@@ -25443,7 +25449,7 @@
       <c r="AK604" s="6"/>
       <c r="AL604" s="6"/>
     </row>
-    <row r="605" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:38" ht="15.95" customHeight="1">
       <c r="A605" s="3"/>
       <c r="B605" s="3"/>
       <c r="C605" s="3"/>
@@ -25483,7 +25489,7 @@
       <c r="AK605" s="6"/>
       <c r="AL605" s="6"/>
     </row>
-    <row r="606" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:38" ht="15.95" customHeight="1">
       <c r="A606" s="3"/>
       <c r="B606" s="3"/>
       <c r="C606" s="3"/>
@@ -25523,7 +25529,7 @@
       <c r="AK606" s="6"/>
       <c r="AL606" s="6"/>
     </row>
-    <row r="607" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:38" ht="15.95" customHeight="1">
       <c r="A607" s="3"/>
       <c r="B607" s="3"/>
       <c r="C607" s="3"/>
@@ -25563,7 +25569,7 @@
       <c r="AK607" s="6"/>
       <c r="AL607" s="6"/>
     </row>
-    <row r="608" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:38" ht="15.95" customHeight="1">
       <c r="A608" s="3"/>
       <c r="B608" s="3"/>
       <c r="C608" s="3"/>
@@ -25603,7 +25609,7 @@
       <c r="AK608" s="6"/>
       <c r="AL608" s="6"/>
     </row>
-    <row r="609" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:38" ht="15.95" customHeight="1">
       <c r="A609" s="3"/>
       <c r="B609" s="3"/>
       <c r="C609" s="3"/>
@@ -25643,7 +25649,7 @@
       <c r="AK609" s="6"/>
       <c r="AL609" s="6"/>
     </row>
-    <row r="610" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:38" ht="15.95" customHeight="1">
       <c r="A610" s="3"/>
       <c r="B610" s="3"/>
       <c r="C610" s="3"/>
@@ -25683,7 +25689,7 @@
       <c r="AK610" s="6"/>
       <c r="AL610" s="6"/>
     </row>
-    <row r="611" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:38" ht="15.95" customHeight="1">
       <c r="A611" s="3"/>
       <c r="B611" s="3"/>
       <c r="C611" s="3"/>
@@ -25723,7 +25729,7 @@
       <c r="AK611" s="6"/>
       <c r="AL611" s="6"/>
     </row>
-    <row r="612" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:38" ht="15.95" customHeight="1">
       <c r="A612" s="3"/>
       <c r="B612" s="3"/>
       <c r="C612" s="3"/>
@@ -25763,7 +25769,7 @@
       <c r="AK612" s="6"/>
       <c r="AL612" s="6"/>
     </row>
-    <row r="613" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:38" ht="15.95" customHeight="1">
       <c r="A613" s="3"/>
       <c r="B613" s="3"/>
       <c r="C613" s="3"/>
@@ -25803,7 +25809,7 @@
       <c r="AK613" s="6"/>
       <c r="AL613" s="6"/>
     </row>
-    <row r="614" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:38" ht="15.95" customHeight="1">
       <c r="A614" s="3"/>
       <c r="B614" s="3"/>
       <c r="C614" s="3"/>
@@ -25843,7 +25849,7 @@
       <c r="AK614" s="6"/>
       <c r="AL614" s="6"/>
     </row>
-    <row r="615" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:38" ht="15.95" customHeight="1">
       <c r="A615" s="3"/>
       <c r="B615" s="3"/>
       <c r="C615" s="3"/>
@@ -25883,7 +25889,7 @@
       <c r="AK615" s="6"/>
       <c r="AL615" s="6"/>
     </row>
-    <row r="616" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:38" ht="15.95" customHeight="1">
       <c r="A616" s="3"/>
       <c r="B616" s="3"/>
       <c r="C616" s="3"/>
@@ -25923,7 +25929,7 @@
       <c r="AK616" s="6"/>
       <c r="AL616" s="6"/>
     </row>
-    <row r="617" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:38" ht="15.95" customHeight="1">
       <c r="A617" s="3"/>
       <c r="B617" s="3"/>
       <c r="C617" s="3"/>
@@ -25963,7 +25969,7 @@
       <c r="AK617" s="6"/>
       <c r="AL617" s="6"/>
     </row>
-    <row r="618" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:38" ht="15.95" customHeight="1">
       <c r="A618" s="3"/>
       <c r="B618" s="3"/>
       <c r="C618" s="3"/>
@@ -26003,7 +26009,7 @@
       <c r="AK618" s="6"/>
       <c r="AL618" s="6"/>
     </row>
-    <row r="619" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:38" ht="15.95" customHeight="1">
       <c r="A619" s="3"/>
       <c r="B619" s="3"/>
       <c r="C619" s="3"/>
@@ -26043,7 +26049,7 @@
       <c r="AK619" s="6"/>
       <c r="AL619" s="6"/>
     </row>
-    <row r="620" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:38" ht="15.95" customHeight="1">
       <c r="A620" s="3"/>
       <c r="B620" s="3"/>
       <c r="C620" s="3"/>
@@ -26083,7 +26089,7 @@
       <c r="AK620" s="6"/>
       <c r="AL620" s="6"/>
     </row>
-    <row r="621" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:38" ht="15.95" customHeight="1">
       <c r="A621" s="3"/>
       <c r="B621" s="3"/>
       <c r="C621" s="3"/>
@@ -26123,7 +26129,7 @@
       <c r="AK621" s="6"/>
       <c r="AL621" s="6"/>
     </row>
-    <row r="622" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:38" ht="15.95" customHeight="1">
       <c r="A622" s="3"/>
       <c r="B622" s="3"/>
       <c r="C622" s="3"/>
@@ -26163,7 +26169,7 @@
       <c r="AK622" s="6"/>
       <c r="AL622" s="6"/>
     </row>
-    <row r="623" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:38" ht="15.95" customHeight="1">
       <c r="A623" s="3"/>
       <c r="B623" s="3"/>
       <c r="C623" s="3"/>
@@ -26203,7 +26209,7 @@
       <c r="AK623" s="6"/>
       <c r="AL623" s="6"/>
     </row>
-    <row r="624" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:38" ht="15.95" customHeight="1">
       <c r="A624" s="3"/>
       <c r="B624" s="3"/>
       <c r="C624" s="3"/>
@@ -26243,7 +26249,7 @@
       <c r="AK624" s="6"/>
       <c r="AL624" s="6"/>
     </row>
-    <row r="625" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:38" ht="15.95" customHeight="1">
       <c r="A625" s="3"/>
       <c r="B625" s="3"/>
       <c r="C625" s="3"/>
@@ -26283,7 +26289,7 @@
       <c r="AK625" s="6"/>
       <c r="AL625" s="6"/>
     </row>
-    <row r="626" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:38" ht="15.95" customHeight="1">
       <c r="A626" s="3"/>
       <c r="B626" s="3"/>
       <c r="C626" s="3"/>
@@ -26323,7 +26329,7 @@
       <c r="AK626" s="6"/>
       <c r="AL626" s="6"/>
     </row>
-    <row r="627" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:38" ht="15.95" customHeight="1">
       <c r="A627" s="3"/>
       <c r="B627" s="3"/>
       <c r="C627" s="3"/>
@@ -26363,7 +26369,7 @@
       <c r="AK627" s="6"/>
       <c r="AL627" s="6"/>
     </row>
-    <row r="628" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:38" ht="15.95" customHeight="1">
       <c r="A628" s="3"/>
       <c r="B628" s="3"/>
       <c r="C628" s="3"/>
@@ -26403,7 +26409,7 @@
       <c r="AK628" s="6"/>
       <c r="AL628" s="6"/>
     </row>
-    <row r="629" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:38" ht="15.95" customHeight="1">
       <c r="A629" s="3"/>
       <c r="B629" s="3"/>
       <c r="C629" s="3"/>
@@ -26443,7 +26449,7 @@
       <c r="AK629" s="6"/>
       <c r="AL629" s="6"/>
     </row>
-    <row r="630" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:38" ht="15.95" customHeight="1">
       <c r="A630" s="3"/>
       <c r="B630" s="3"/>
       <c r="C630" s="3"/>
@@ -26483,7 +26489,7 @@
       <c r="AK630" s="6"/>
       <c r="AL630" s="6"/>
     </row>
-    <row r="631" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:38" ht="15.95" customHeight="1">
       <c r="A631" s="3"/>
       <c r="B631" s="3"/>
       <c r="C631" s="3"/>
@@ -26523,7 +26529,7 @@
       <c r="AK631" s="6"/>
       <c r="AL631" s="6"/>
     </row>
-    <row r="632" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:38" ht="15.95" customHeight="1">
       <c r="A632" s="3"/>
       <c r="B632" s="3"/>
       <c r="C632" s="3"/>
@@ -26563,7 +26569,7 @@
       <c r="AK632" s="6"/>
       <c r="AL632" s="6"/>
     </row>
-    <row r="633" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:38" ht="15.95" customHeight="1">
       <c r="A633" s="3"/>
       <c r="B633" s="3"/>
       <c r="C633" s="3"/>
@@ -26603,7 +26609,7 @@
       <c r="AK633" s="6"/>
       <c r="AL633" s="6"/>
     </row>
-    <row r="634" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:38" ht="15.95" customHeight="1">
       <c r="A634" s="3"/>
       <c r="B634" s="3"/>
       <c r="C634" s="3"/>
@@ -26643,7 +26649,7 @@
       <c r="AK634" s="6"/>
       <c r="AL634" s="6"/>
     </row>
-    <row r="635" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:38" ht="15.95" customHeight="1">
       <c r="A635" s="3"/>
       <c r="B635" s="3"/>
       <c r="C635" s="3"/>
@@ -26683,7 +26689,7 @@
       <c r="AK635" s="6"/>
       <c r="AL635" s="6"/>
     </row>
-    <row r="636" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:38" ht="15.95" customHeight="1">
       <c r="A636" s="3"/>
       <c r="B636" s="3"/>
       <c r="C636" s="3"/>
@@ -26723,7 +26729,7 @@
       <c r="AK636" s="6"/>
       <c r="AL636" s="6"/>
     </row>
-    <row r="637" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:38" ht="15.95" customHeight="1">
       <c r="A637" s="3"/>
       <c r="B637" s="3"/>
       <c r="C637" s="3"/>
@@ -26763,7 +26769,7 @@
       <c r="AK637" s="6"/>
       <c r="AL637" s="6"/>
     </row>
-    <row r="638" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:38" ht="15.95" customHeight="1">
       <c r="A638" s="3"/>
       <c r="B638" s="3"/>
       <c r="C638" s="3"/>
@@ -26803,7 +26809,7 @@
       <c r="AK638" s="6"/>
       <c r="AL638" s="6"/>
     </row>
-    <row r="639" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:38" ht="15.95" customHeight="1">
       <c r="A639" s="3"/>
       <c r="B639" s="3"/>
       <c r="C639" s="3"/>
@@ -26843,7 +26849,7 @@
       <c r="AK639" s="6"/>
       <c r="AL639" s="6"/>
     </row>
-    <row r="640" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:38" ht="15.95" customHeight="1">
       <c r="A640" s="3"/>
       <c r="B640" s="3"/>
       <c r="C640" s="3"/>
@@ -26883,7 +26889,7 @@
       <c r="AK640" s="6"/>
       <c r="AL640" s="6"/>
     </row>
-    <row r="641" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:38" ht="15.95" customHeight="1">
       <c r="A641" s="3"/>
       <c r="B641" s="3"/>
       <c r="C641" s="3"/>
@@ -26923,7 +26929,7 @@
       <c r="AK641" s="6"/>
       <c r="AL641" s="6"/>
     </row>
-    <row r="642" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:38" ht="15.95" customHeight="1">
       <c r="A642" s="3"/>
       <c r="B642" s="3"/>
       <c r="C642" s="3"/>
@@ -26963,7 +26969,7 @@
       <c r="AK642" s="6"/>
       <c r="AL642" s="6"/>
     </row>
-    <row r="643" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:38" ht="15.95" customHeight="1">
       <c r="A643" s="3"/>
       <c r="B643" s="3"/>
       <c r="C643" s="3"/>
@@ -27003,7 +27009,7 @@
       <c r="AK643" s="6"/>
       <c r="AL643" s="6"/>
     </row>
-    <row r="644" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:38" ht="15.95" customHeight="1">
       <c r="A644" s="3"/>
       <c r="B644" s="3"/>
       <c r="C644" s="3"/>
@@ -27043,7 +27049,7 @@
       <c r="AK644" s="6"/>
       <c r="AL644" s="6"/>
     </row>
-    <row r="645" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:38" ht="15.95" customHeight="1">
       <c r="A645" s="3"/>
       <c r="B645" s="3"/>
       <c r="C645" s="3"/>
@@ -27083,7 +27089,7 @@
       <c r="AK645" s="6"/>
       <c r="AL645" s="6"/>
     </row>
-    <row r="646" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:38" ht="15.95" customHeight="1">
       <c r="A646" s="3"/>
       <c r="B646" s="3"/>
       <c r="C646" s="3"/>
@@ -27123,7 +27129,7 @@
       <c r="AK646" s="6"/>
       <c r="AL646" s="6"/>
     </row>
-    <row r="647" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:38" ht="15.95" customHeight="1">
       <c r="A647" s="3"/>
       <c r="B647" s="3"/>
       <c r="C647" s="3"/>
@@ -27163,7 +27169,7 @@
       <c r="AK647" s="6"/>
       <c r="AL647" s="6"/>
     </row>
-    <row r="648" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:38" ht="15.95" customHeight="1">
       <c r="A648" s="3"/>
       <c r="B648" s="3"/>
       <c r="C648" s="3"/>
@@ -27203,7 +27209,7 @@
       <c r="AK648" s="6"/>
       <c r="AL648" s="6"/>
     </row>
-    <row r="649" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:38" ht="15.95" customHeight="1">
       <c r="A649" s="3"/>
       <c r="B649" s="3"/>
       <c r="C649" s="3"/>
@@ -27243,7 +27249,7 @@
       <c r="AK649" s="6"/>
       <c r="AL649" s="6"/>
     </row>
-    <row r="650" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:38" ht="15.95" customHeight="1">
       <c r="A650" s="3"/>
       <c r="B650" s="3"/>
       <c r="C650" s="3"/>
@@ -27283,7 +27289,7 @@
       <c r="AK650" s="6"/>
       <c r="AL650" s="6"/>
     </row>
-    <row r="651" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:38" ht="15.95" customHeight="1">
       <c r="A651" s="3"/>
       <c r="B651" s="3"/>
       <c r="C651" s="3"/>
@@ -27323,7 +27329,7 @@
       <c r="AK651" s="6"/>
       <c r="AL651" s="6"/>
     </row>
-    <row r="652" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:38" ht="15.95" customHeight="1">
       <c r="A652" s="3"/>
       <c r="B652" s="3"/>
       <c r="C652" s="3"/>
@@ -27363,7 +27369,7 @@
       <c r="AK652" s="6"/>
       <c r="AL652" s="6"/>
     </row>
-    <row r="653" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:38" ht="15.95" customHeight="1">
       <c r="A653" s="3"/>
       <c r="B653" s="3"/>
       <c r="C653" s="3"/>
@@ -27403,7 +27409,7 @@
       <c r="AK653" s="6"/>
       <c r="AL653" s="6"/>
     </row>
-    <row r="654" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:38" ht="15.95" customHeight="1">
       <c r="A654" s="3"/>
       <c r="B654" s="3"/>
       <c r="C654" s="3"/>
@@ -27443,7 +27449,7 @@
       <c r="AK654" s="6"/>
       <c r="AL654" s="6"/>
     </row>
-    <row r="655" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:38" ht="15.95" customHeight="1">
       <c r="A655" s="3"/>
       <c r="B655" s="3"/>
       <c r="C655" s="3"/>
@@ -27483,7 +27489,7 @@
       <c r="AK655" s="6"/>
       <c r="AL655" s="6"/>
     </row>
-    <row r="656" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:38" ht="15.95" customHeight="1">
       <c r="A656" s="3"/>
       <c r="B656" s="3"/>
       <c r="C656" s="3"/>
@@ -27523,7 +27529,7 @@
       <c r="AK656" s="6"/>
       <c r="AL656" s="6"/>
     </row>
-    <row r="657" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:38" ht="15.95" customHeight="1">
       <c r="A657" s="3"/>
       <c r="B657" s="3"/>
       <c r="C657" s="3"/>
@@ -27563,7 +27569,7 @@
       <c r="AK657" s="6"/>
       <c r="AL657" s="6"/>
     </row>
-    <row r="658" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:38" ht="15.95" customHeight="1">
       <c r="A658" s="3"/>
       <c r="B658" s="3"/>
       <c r="C658" s="3"/>
@@ -27603,7 +27609,7 @@
       <c r="AK658" s="6"/>
       <c r="AL658" s="6"/>
     </row>
-    <row r="659" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:38" ht="15.95" customHeight="1">
       <c r="A659" s="3"/>
       <c r="B659" s="3"/>
       <c r="C659" s="3"/>
@@ -27643,7 +27649,7 @@
       <c r="AK659" s="6"/>
       <c r="AL659" s="6"/>
     </row>
-    <row r="660" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:38" ht="15.95" customHeight="1">
       <c r="A660" s="3"/>
       <c r="B660" s="3"/>
       <c r="C660" s="3"/>
@@ -27683,7 +27689,7 @@
       <c r="AK660" s="6"/>
       <c r="AL660" s="6"/>
     </row>
-    <row r="661" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:38" ht="15.95" customHeight="1">
       <c r="A661" s="3"/>
       <c r="B661" s="3"/>
       <c r="C661" s="3"/>
@@ -27723,7 +27729,7 @@
       <c r="AK661" s="6"/>
       <c r="AL661" s="6"/>
     </row>
-    <row r="662" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:38" ht="15.95" customHeight="1">
       <c r="A662" s="3"/>
       <c r="B662" s="3"/>
       <c r="C662" s="3"/>
@@ -27763,7 +27769,7 @@
       <c r="AK662" s="6"/>
       <c r="AL662" s="6"/>
     </row>
-    <row r="663" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:38" ht="15.95" customHeight="1">
       <c r="A663" s="3"/>
       <c r="B663" s="3"/>
       <c r="C663" s="3"/>
@@ -27803,7 +27809,7 @@
       <c r="AK663" s="6"/>
       <c r="AL663" s="6"/>
     </row>
-    <row r="664" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:38" ht="15.95" customHeight="1">
       <c r="A664" s="3"/>
       <c r="B664" s="3"/>
       <c r="C664" s="3"/>
@@ -27843,7 +27849,7 @@
       <c r="AK664" s="6"/>
       <c r="AL664" s="6"/>
     </row>
-    <row r="665" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:38" ht="15.95" customHeight="1">
       <c r="A665" s="3"/>
       <c r="B665" s="3"/>
       <c r="C665" s="3"/>
@@ -27883,7 +27889,7 @@
       <c r="AK665" s="6"/>
       <c r="AL665" s="6"/>
     </row>
-    <row r="666" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:38" ht="15.95" customHeight="1">
       <c r="A666" s="3"/>
       <c r="B666" s="3"/>
       <c r="C666" s="3"/>
@@ -27923,7 +27929,7 @@
       <c r="AK666" s="6"/>
       <c r="AL666" s="6"/>
     </row>
-    <row r="667" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:38" ht="15.95" customHeight="1">
       <c r="A667" s="3"/>
       <c r="B667" s="3"/>
       <c r="C667" s="3"/>
@@ -27963,7 +27969,7 @@
       <c r="AK667" s="6"/>
       <c r="AL667" s="6"/>
     </row>
-    <row r="668" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:38" ht="15.95" customHeight="1">
       <c r="A668" s="3"/>
       <c r="B668" s="3"/>
       <c r="C668" s="3"/>
@@ -28003,7 +28009,7 @@
       <c r="AK668" s="6"/>
       <c r="AL668" s="6"/>
     </row>
-    <row r="669" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:38" ht="15.95" customHeight="1">
       <c r="A669" s="3"/>
       <c r="B669" s="3"/>
       <c r="C669" s="3"/>
@@ -28043,7 +28049,7 @@
       <c r="AK669" s="6"/>
       <c r="AL669" s="6"/>
     </row>
-    <row r="670" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:38" ht="15.95" customHeight="1">
       <c r="A670" s="3"/>
       <c r="B670" s="3"/>
       <c r="C670" s="3"/>
@@ -28083,7 +28089,7 @@
       <c r="AK670" s="6"/>
       <c r="AL670" s="6"/>
     </row>
-    <row r="671" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:38" ht="15.95" customHeight="1">
       <c r="A671" s="3"/>
       <c r="B671" s="3"/>
       <c r="C671" s="3"/>
@@ -28123,7 +28129,7 @@
       <c r="AK671" s="6"/>
       <c r="AL671" s="6"/>
     </row>
-    <row r="672" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:38" ht="15.95" customHeight="1">
       <c r="A672" s="3"/>
       <c r="B672" s="3"/>
       <c r="C672" s="3"/>
@@ -28163,7 +28169,7 @@
       <c r="AK672" s="6"/>
       <c r="AL672" s="6"/>
     </row>
-    <row r="673" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:38" ht="15.95" customHeight="1">
       <c r="A673" s="3"/>
       <c r="B673" s="3"/>
       <c r="C673" s="3"/>
@@ -28203,7 +28209,7 @@
       <c r="AK673" s="6"/>
       <c r="AL673" s="6"/>
     </row>
-    <row r="674" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:38" ht="15.95" customHeight="1">
       <c r="A674" s="3"/>
       <c r="B674" s="3"/>
       <c r="C674" s="3"/>
@@ -28243,7 +28249,7 @@
       <c r="AK674" s="6"/>
       <c r="AL674" s="6"/>
     </row>
-    <row r="675" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:38" ht="15.95" customHeight="1">
       <c r="A675" s="3"/>
       <c r="B675" s="3"/>
       <c r="C675" s="3"/>
@@ -28283,7 +28289,7 @@
       <c r="AK675" s="6"/>
       <c r="AL675" s="6"/>
     </row>
-    <row r="676" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:38" ht="15.95" customHeight="1">
       <c r="A676" s="3"/>
       <c r="B676" s="3"/>
       <c r="C676" s="3"/>
@@ -28323,7 +28329,7 @@
       <c r="AK676" s="6"/>
       <c r="AL676" s="6"/>
     </row>
-    <row r="677" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:38" ht="15.95" customHeight="1">
       <c r="A677" s="3"/>
       <c r="B677" s="3"/>
       <c r="C677" s="3"/>
@@ -28363,7 +28369,7 @@
       <c r="AK677" s="6"/>
       <c r="AL677" s="6"/>
     </row>
-    <row r="678" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:38" ht="15.95" customHeight="1">
       <c r="A678" s="3"/>
       <c r="B678" s="3"/>
       <c r="C678" s="3"/>
@@ -28403,7 +28409,7 @@
       <c r="AK678" s="6"/>
       <c r="AL678" s="6"/>
     </row>
-    <row r="679" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:38" ht="15.95" customHeight="1">
       <c r="A679" s="3"/>
       <c r="B679" s="3"/>
       <c r="C679" s="3"/>
@@ -28443,7 +28449,7 @@
       <c r="AK679" s="6"/>
       <c r="AL679" s="6"/>
     </row>
-    <row r="680" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:38" ht="15.95" customHeight="1">
       <c r="A680" s="3"/>
       <c r="B680" s="3"/>
       <c r="C680" s="3"/>
@@ -28483,7 +28489,7 @@
       <c r="AK680" s="6"/>
       <c r="AL680" s="6"/>
     </row>
-    <row r="681" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:38" ht="15.95" customHeight="1">
       <c r="A681" s="3"/>
       <c r="B681" s="3"/>
       <c r="C681" s="3"/>
@@ -28523,7 +28529,7 @@
       <c r="AK681" s="6"/>
       <c r="AL681" s="6"/>
     </row>
-    <row r="682" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:38" ht="15.95" customHeight="1">
       <c r="A682" s="3"/>
       <c r="B682" s="3"/>
       <c r="C682" s="3"/>
@@ -28563,7 +28569,7 @@
       <c r="AK682" s="6"/>
       <c r="AL682" s="6"/>
     </row>
-    <row r="683" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:38" ht="15.95" customHeight="1">
       <c r="A683" s="3"/>
       <c r="B683" s="3"/>
       <c r="C683" s="3"/>
@@ -28603,7 +28609,7 @@
       <c r="AK683" s="6"/>
       <c r="AL683" s="6"/>
     </row>
-    <row r="684" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:38" ht="15.95" customHeight="1">
       <c r="A684" s="3"/>
       <c r="B684" s="3"/>
       <c r="C684" s="3"/>
@@ -28643,7 +28649,7 @@
       <c r="AK684" s="6"/>
       <c r="AL684" s="6"/>
     </row>
-    <row r="685" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:38" ht="15.95" customHeight="1">
       <c r="A685" s="3"/>
       <c r="B685" s="3"/>
       <c r="C685" s="3"/>
@@ -28683,7 +28689,7 @@
       <c r="AK685" s="6"/>
       <c r="AL685" s="6"/>
     </row>
-    <row r="686" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:38" ht="15.95" customHeight="1">
       <c r="A686" s="3"/>
       <c r="B686" s="3"/>
       <c r="C686" s="3"/>
@@ -28723,7 +28729,7 @@
       <c r="AK686" s="6"/>
       <c r="AL686" s="6"/>
     </row>
-    <row r="687" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:38" ht="15.95" customHeight="1">
       <c r="A687" s="3"/>
       <c r="B687" s="3"/>
       <c r="C687" s="3"/>
@@ -28763,7 +28769,7 @@
       <c r="AK687" s="6"/>
       <c r="AL687" s="6"/>
     </row>
-    <row r="688" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:38" ht="15.95" customHeight="1">
       <c r="A688" s="3"/>
       <c r="B688" s="3"/>
       <c r="C688" s="3"/>
@@ -28803,7 +28809,7 @@
       <c r="AK688" s="6"/>
       <c r="AL688" s="6"/>
     </row>
-    <row r="689" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:38" ht="15.95" customHeight="1">
       <c r="A689" s="3"/>
       <c r="B689" s="3"/>
       <c r="C689" s="3"/>
@@ -28843,7 +28849,7 @@
       <c r="AK689" s="6"/>
       <c r="AL689" s="6"/>
     </row>
-    <row r="690" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:38" ht="15.95" customHeight="1">
       <c r="A690" s="3"/>
       <c r="B690" s="3"/>
       <c r="C690" s="3"/>
@@ -28883,7 +28889,7 @@
       <c r="AK690" s="6"/>
       <c r="AL690" s="6"/>
     </row>
-    <row r="691" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:38" ht="15.95" customHeight="1">
       <c r="A691" s="3"/>
       <c r="B691" s="3"/>
       <c r="C691" s="3"/>
@@ -28923,7 +28929,7 @@
       <c r="AK691" s="6"/>
       <c r="AL691" s="6"/>
     </row>
-    <row r="692" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:38" ht="15.95" customHeight="1">
       <c r="A692" s="3"/>
       <c r="B692" s="3"/>
       <c r="C692" s="3"/>
@@ -28963,7 +28969,7 @@
       <c r="AK692" s="6"/>
       <c r="AL692" s="6"/>
     </row>
-    <row r="693" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:38" ht="15.95" customHeight="1">
       <c r="A693" s="3"/>
       <c r="B693" s="3"/>
       <c r="C693" s="3"/>
@@ -29003,7 +29009,7 @@
       <c r="AK693" s="6"/>
       <c r="AL693" s="6"/>
     </row>
-    <row r="694" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:38" ht="15.95" customHeight="1">
       <c r="A694" s="3"/>
       <c r="B694" s="3"/>
       <c r="C694" s="3"/>
@@ -29043,7 +29049,7 @@
       <c r="AK694" s="6"/>
       <c r="AL694" s="6"/>
     </row>
-    <row r="695" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:38" ht="15.95" customHeight="1">
       <c r="A695" s="3"/>
       <c r="B695" s="3"/>
       <c r="C695" s="3"/>
@@ -29083,7 +29089,7 @@
       <c r="AK695" s="6"/>
       <c r="AL695" s="6"/>
     </row>
-    <row r="696" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:38" ht="15.95" customHeight="1">
       <c r="A696" s="3"/>
       <c r="B696" s="3"/>
       <c r="C696" s="3"/>
@@ -29123,7 +29129,7 @@
       <c r="AK696" s="6"/>
       <c r="AL696" s="6"/>
     </row>
-    <row r="697" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:38" ht="15.95" customHeight="1">
       <c r="A697" s="3"/>
       <c r="B697" s="3"/>
       <c r="C697" s="3"/>
@@ -29163,7 +29169,7 @@
       <c r="AK697" s="6"/>
       <c r="AL697" s="6"/>
     </row>
-    <row r="698" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:38" ht="15.95" customHeight="1">
       <c r="A698" s="3"/>
       <c r="B698" s="3"/>
       <c r="C698" s="3"/>
@@ -29203,7 +29209,7 @@
       <c r="AK698" s="6"/>
       <c r="AL698" s="6"/>
     </row>
-    <row r="699" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:38" ht="15.95" customHeight="1">
       <c r="A699" s="3"/>
       <c r="B699" s="3"/>
       <c r="C699" s="3"/>
@@ -29243,7 +29249,7 @@
       <c r="AK699" s="6"/>
       <c r="AL699" s="6"/>
     </row>
-    <row r="700" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:38" ht="15.95" customHeight="1">
       <c r="A700" s="3"/>
       <c r="B700" s="3"/>
       <c r="C700" s="3"/>
@@ -29283,7 +29289,7 @@
       <c r="AK700" s="6"/>
       <c r="AL700" s="6"/>
     </row>
-    <row r="701" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:38" ht="15.95" customHeight="1">
       <c r="A701" s="3"/>
       <c r="B701" s="3"/>
       <c r="C701" s="3"/>
@@ -29323,7 +29329,7 @@
       <c r="AK701" s="6"/>
       <c r="AL701" s="6"/>
     </row>
-    <row r="702" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:38" ht="15.95" customHeight="1">
       <c r="A702" s="3"/>
       <c r="B702" s="3"/>
       <c r="C702" s="3"/>
@@ -29363,7 +29369,7 @@
       <c r="AK702" s="6"/>
       <c r="AL702" s="6"/>
     </row>
-    <row r="703" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:38" ht="15.95" customHeight="1">
       <c r="A703" s="3"/>
       <c r="B703" s="3"/>
       <c r="C703" s="3"/>
@@ -29403,7 +29409,7 @@
       <c r="AK703" s="6"/>
       <c r="AL703" s="6"/>
     </row>
-    <row r="704" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:38" ht="15.95" customHeight="1">
       <c r="A704" s="3"/>
       <c r="B704" s="3"/>
       <c r="C704" s="3"/>
@@ -29443,7 +29449,7 @@
       <c r="AK704" s="6"/>
       <c r="AL704" s="6"/>
     </row>
-    <row r="705" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:38" ht="15.95" customHeight="1">
       <c r="A705" s="3"/>
       <c r="B705" s="3"/>
       <c r="C705" s="3"/>
@@ -29483,7 +29489,7 @@
       <c r="AK705" s="6"/>
       <c r="AL705" s="6"/>
     </row>
-    <row r="706" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:38" ht="15.95" customHeight="1">
       <c r="A706" s="3"/>
       <c r="B706" s="3"/>
       <c r="C706" s="3"/>
@@ -29523,7 +29529,7 @@
       <c r="AK706" s="6"/>
       <c r="AL706" s="6"/>
     </row>
-    <row r="707" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:38" ht="15.95" customHeight="1">
       <c r="A707" s="3"/>
       <c r="B707" s="3"/>
       <c r="C707" s="3"/>
@@ -29563,7 +29569,7 @@
       <c r="AK707" s="6"/>
       <c r="AL707" s="6"/>
     </row>
-    <row r="708" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:38" ht="15.95" customHeight="1">
       <c r="A708" s="3"/>
       <c r="B708" s="3"/>
       <c r="C708" s="3"/>
@@ -29603,7 +29609,7 @@
       <c r="AK708" s="6"/>
       <c r="AL708" s="6"/>
     </row>
-    <row r="709" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:38" ht="15.95" customHeight="1">
       <c r="A709" s="3"/>
       <c r="B709" s="3"/>
       <c r="C709" s="3"/>
@@ -29643,7 +29649,7 @@
       <c r="AK709" s="6"/>
       <c r="AL709" s="6"/>
     </row>
-    <row r="710" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:38" ht="15.95" customHeight="1">
       <c r="A710" s="3"/>
       <c r="B710" s="3"/>
       <c r="C710" s="3"/>
@@ -29683,7 +29689,7 @@
       <c r="AK710" s="6"/>
       <c r="AL710" s="6"/>
     </row>
-    <row r="711" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:38" ht="15.95" customHeight="1">
       <c r="A711" s="3"/>
       <c r="B711" s="3"/>
       <c r="C711" s="3"/>
@@ -29723,7 +29729,7 @@
       <c r="AK711" s="6"/>
       <c r="AL711" s="6"/>
     </row>
-    <row r="712" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:38" ht="15.95" customHeight="1">
       <c r="A712" s="3"/>
       <c r="B712" s="3"/>
       <c r="C712" s="3"/>
@@ -29763,7 +29769,7 @@
       <c r="AK712" s="6"/>
       <c r="AL712" s="6"/>
     </row>
-    <row r="713" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:38" ht="15.95" customHeight="1">
       <c r="A713" s="3"/>
       <c r="B713" s="3"/>
       <c r="C713" s="3"/>
@@ -29803,7 +29809,7 @@
       <c r="AK713" s="6"/>
       <c r="AL713" s="6"/>
     </row>
-    <row r="714" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:38" ht="15.95" customHeight="1">
       <c r="A714" s="3"/>
       <c r="B714" s="3"/>
       <c r="C714" s="3"/>
@@ -29843,7 +29849,7 @@
       <c r="AK714" s="6"/>
       <c r="AL714" s="6"/>
     </row>
-    <row r="715" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:38" ht="15.95" customHeight="1">
       <c r="A715" s="3"/>
       <c r="B715" s="3"/>
       <c r="C715" s="3"/>
@@ -29883,7 +29889,7 @@
       <c r="AK715" s="6"/>
       <c r="AL715" s="6"/>
     </row>
-    <row r="716" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:38" ht="15.95" customHeight="1">
       <c r="A716" s="3"/>
       <c r="B716" s="3"/>
       <c r="C716" s="3"/>
@@ -29923,7 +29929,7 @@
       <c r="AK716" s="6"/>
       <c r="AL716" s="6"/>
     </row>
-    <row r="717" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:38" ht="15.95" customHeight="1">
       <c r="A717" s="3"/>
       <c r="B717" s="3"/>
       <c r="C717" s="3"/>
@@ -29963,7 +29969,7 @@
       <c r="AK717" s="6"/>
       <c r="AL717" s="6"/>
     </row>
-    <row r="718" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:38" ht="15.95" customHeight="1">
       <c r="A718" s="3"/>
       <c r="B718" s="3"/>
       <c r="C718" s="3"/>
@@ -30003,7 +30009,7 @@
       <c r="AK718" s="6"/>
       <c r="AL718" s="6"/>
     </row>
-    <row r="719" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:38" ht="15.95" customHeight="1">
       <c r="A719" s="3"/>
       <c r="B719" s="3"/>
       <c r="C719" s="3"/>
@@ -30043,7 +30049,7 @@
       <c r="AK719" s="6"/>
       <c r="AL719" s="6"/>
     </row>
-    <row r="720" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:38" ht="15.95" customHeight="1">
       <c r="A720" s="3"/>
       <c r="B720" s="3"/>
       <c r="C720" s="3"/>
@@ -30083,7 +30089,7 @@
       <c r="AK720" s="6"/>
       <c r="AL720" s="6"/>
     </row>
-    <row r="721" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:38" ht="15.95" customHeight="1">
       <c r="A721" s="3"/>
       <c r="B721" s="3"/>
       <c r="C721" s="3"/>
@@ -30123,7 +30129,7 @@
       <c r="AK721" s="6"/>
       <c r="AL721" s="6"/>
     </row>
-    <row r="722" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:38" ht="15.95" customHeight="1">
       <c r="A722" s="3"/>
       <c r="B722" s="3"/>
       <c r="C722" s="3"/>
@@ -30163,7 +30169,7 @@
       <c r="AK722" s="6"/>
       <c r="AL722" s="6"/>
     </row>
-    <row r="723" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:38" ht="15.95" customHeight="1">
       <c r="A723" s="3"/>
       <c r="B723" s="3"/>
       <c r="C723" s="3"/>
@@ -30203,7 +30209,7 @@
       <c r="AK723" s="6"/>
       <c r="AL723" s="6"/>
     </row>
-    <row r="724" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:38" ht="15.95" customHeight="1">
       <c r="A724" s="3"/>
       <c r="B724" s="3"/>
       <c r="C724" s="3"/>
@@ -30243,7 +30249,7 @@
       <c r="AK724" s="6"/>
       <c r="AL724" s="6"/>
     </row>
-    <row r="725" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:38" ht="15.95" customHeight="1">
       <c r="A725" s="3"/>
       <c r="B725" s="3"/>
       <c r="C725" s="3"/>
@@ -30283,7 +30289,7 @@
       <c r="AK725" s="6"/>
       <c r="AL725" s="6"/>
     </row>
-    <row r="726" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:38" ht="15.95" customHeight="1">
       <c r="A726" s="3"/>
       <c r="B726" s="3"/>
       <c r="C726" s="3"/>
@@ -30323,7 +30329,7 @@
       <c r="AK726" s="6"/>
       <c r="AL726" s="6"/>
     </row>
-    <row r="727" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:38" ht="15.95" customHeight="1">
       <c r="A727" s="3"/>
       <c r="B727" s="3"/>
       <c r="C727" s="3"/>
@@ -30363,7 +30369,7 @@
       <c r="AK727" s="6"/>
       <c r="AL727" s="6"/>
     </row>
-    <row r="728" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:38" ht="15.95" customHeight="1">
       <c r="A728" s="3"/>
       <c r="B728" s="3"/>
       <c r="C728" s="3"/>
@@ -30403,7 +30409,7 @@
       <c r="AK728" s="6"/>
       <c r="AL728" s="6"/>
     </row>
-    <row r="729" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:38" ht="15.95" customHeight="1">
       <c r="A729" s="3"/>
       <c r="B729" s="3"/>
       <c r="C729" s="3"/>
@@ -30443,7 +30449,7 @@
       <c r="AK729" s="6"/>
       <c r="AL729" s="6"/>
     </row>
-    <row r="730" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:38" ht="15.95" customHeight="1">
       <c r="A730" s="3"/>
       <c r="B730" s="3"/>
       <c r="C730" s="3"/>
@@ -30483,7 +30489,7 @@
       <c r="AK730" s="6"/>
       <c r="AL730" s="6"/>
     </row>
-    <row r="731" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:38" ht="15.95" customHeight="1">
       <c r="A731" s="3"/>
       <c r="B731" s="3"/>
       <c r="C731" s="3"/>
@@ -30523,7 +30529,7 @@
       <c r="AK731" s="6"/>
       <c r="AL731" s="6"/>
     </row>
-    <row r="732" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:38" ht="15.95" customHeight="1">
       <c r="A732" s="3"/>
       <c r="B732" s="3"/>
       <c r="C732" s="3"/>
@@ -30563,7 +30569,7 @@
       <c r="AK732" s="6"/>
       <c r="AL732" s="6"/>
     </row>
-    <row r="733" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:38" ht="15.95" customHeight="1">
       <c r="A733" s="3"/>
       <c r="B733" s="3"/>
       <c r="C733" s="3"/>
@@ -30603,7 +30609,7 @@
       <c r="AK733" s="6"/>
       <c r="AL733" s="6"/>
     </row>
-    <row r="734" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:38" ht="15.95" customHeight="1">
       <c r="A734" s="3"/>
       <c r="B734" s="3"/>
       <c r="C734" s="3"/>
@@ -30643,7 +30649,7 @@
       <c r="AK734" s="6"/>
       <c r="AL734" s="6"/>
     </row>
-    <row r="735" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:38" ht="15.95" customHeight="1">
       <c r="A735" s="3"/>
       <c r="B735" s="3"/>
       <c r="C735" s="3"/>
@@ -30683,7 +30689,7 @@
       <c r="AK735" s="6"/>
       <c r="AL735" s="6"/>
     </row>
-    <row r="736" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:38" ht="15.95" customHeight="1">
       <c r="A736" s="3"/>
       <c r="B736" s="3"/>
       <c r="C736" s="3"/>
@@ -30723,7 +30729,7 @@
       <c r="AK736" s="6"/>
       <c r="AL736" s="6"/>
     </row>
-    <row r="737" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:38" ht="15.95" customHeight="1">
       <c r="A737" s="3"/>
       <c r="B737" s="3"/>
       <c r="C737" s="3"/>
@@ -30763,7 +30769,7 @@
       <c r="AK737" s="6"/>
       <c r="AL737" s="6"/>
     </row>
-    <row r="738" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:38" ht="15.95" customHeight="1">
       <c r="A738" s="3"/>
       <c r="B738" s="3"/>
       <c r="C738" s="3"/>
@@ -30803,7 +30809,7 @@
       <c r="AK738" s="6"/>
       <c r="AL738" s="6"/>
     </row>
-    <row r="739" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:38" ht="15.95" customHeight="1">
       <c r="A739" s="3"/>
       <c r="B739" s="3"/>
       <c r="C739" s="3"/>
@@ -30843,7 +30849,7 @@
       <c r="AK739" s="6"/>
       <c r="AL739" s="6"/>
     </row>
-    <row r="740" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:38" ht="15.95" customHeight="1">
       <c r="A740" s="3"/>
       <c r="B740" s="3"/>
       <c r="C740" s="3"/>
@@ -30883,7 +30889,7 @@
       <c r="AK740" s="6"/>
       <c r="AL740" s="6"/>
     </row>
-    <row r="741" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:38" ht="15.95" customHeight="1">
       <c r="A741" s="3"/>
       <c r="B741" s="3"/>
       <c r="C741" s="3"/>
@@ -30923,7 +30929,7 @@
       <c r="AK741" s="6"/>
       <c r="AL741" s="6"/>
     </row>
-    <row r="742" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:38" ht="15.95" customHeight="1">
       <c r="A742" s="3"/>
       <c r="B742" s="3"/>
       <c r="C742" s="3"/>
@@ -30963,7 +30969,7 @@
       <c r="AK742" s="6"/>
       <c r="AL742" s="6"/>
     </row>
-    <row r="743" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:38" ht="15.95" customHeight="1">
       <c r="A743" s="3"/>
       <c r="B743" s="3"/>
       <c r="C743" s="3"/>
@@ -31003,7 +31009,7 @@
       <c r="AK743" s="6"/>
       <c r="AL743" s="6"/>
     </row>
-    <row r="744" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:38" ht="15.95" customHeight="1">
       <c r="A744" s="3"/>
       <c r="B744" s="3"/>
       <c r="C744" s="3"/>
@@ -31043,7 +31049,7 @@
       <c r="AK744" s="6"/>
       <c r="AL744" s="6"/>
     </row>
-    <row r="745" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:38" ht="15.95" customHeight="1">
       <c r="A745" s="3"/>
       <c r="B745" s="3"/>
       <c r="C745" s="3"/>
@@ -31083,7 +31089,7 @@
       <c r="AK745" s="6"/>
       <c r="AL745" s="6"/>
     </row>
-    <row r="746" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:38" ht="15.95" customHeight="1">
       <c r="A746" s="3"/>
       <c r="B746" s="3"/>
       <c r="C746" s="3"/>
@@ -31123,7 +31129,7 @@
       <c r="AK746" s="6"/>
       <c r="AL746" s="6"/>
     </row>
-    <row r="747" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:38" ht="15.95" customHeight="1">
       <c r="A747" s="3"/>
       <c r="B747" s="3"/>
       <c r="C747" s="3"/>
@@ -31163,7 +31169,7 @@
       <c r="AK747" s="6"/>
       <c r="AL747" s="6"/>
     </row>
-    <row r="748" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:38" ht="15.95" customHeight="1">
       <c r="A748" s="3"/>
       <c r="B748" s="3"/>
       <c r="C748" s="3"/>
@@ -31203,7 +31209,7 @@
       <c r="AK748" s="6"/>
       <c r="AL748" s="6"/>
     </row>
-    <row r="749" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:38" ht="15.95" customHeight="1">
       <c r="A749" s="3"/>
       <c r="B749" s="3"/>
       <c r="C749" s="3"/>
@@ -31243,7 +31249,7 @@
       <c r="AK749" s="6"/>
       <c r="AL749" s="6"/>
     </row>
-    <row r="750" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:38" ht="15.95" customHeight="1">
       <c r="A750" s="3"/>
       <c r="B750" s="3"/>
       <c r="C750" s="3"/>
@@ -31283,7 +31289,7 @@
       <c r="AK750" s="6"/>
       <c r="AL750" s="6"/>
     </row>
-    <row r="751" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:38" ht="15.95" customHeight="1">
       <c r="A751" s="3"/>
       <c r="B751" s="3"/>
       <c r="C751" s="3"/>
@@ -31323,7 +31329,7 @@
       <c r="AK751" s="6"/>
       <c r="AL751" s="6"/>
     </row>
-    <row r="752" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:38" ht="15.95" customHeight="1">
       <c r="A752" s="3"/>
       <c r="B752" s="3"/>
       <c r="C752" s="3"/>
@@ -31363,7 +31369,7 @@
       <c r="AK752" s="6"/>
       <c r="AL752" s="6"/>
     </row>
-    <row r="753" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:38" ht="15.95" customHeight="1">
       <c r="A753" s="3"/>
       <c r="B753" s="3"/>
       <c r="C753" s="3"/>
@@ -31403,7 +31409,7 @@
       <c r="AK753" s="6"/>
       <c r="AL753" s="6"/>
     </row>
-    <row r="754" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:38" ht="15.95" customHeight="1">
       <c r="A754" s="3"/>
       <c r="B754" s="3"/>
       <c r="C754" s="3"/>
@@ -31443,7 +31449,7 @@
       <c r="AK754" s="6"/>
       <c r="AL754" s="6"/>
     </row>
-    <row r="755" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:38" ht="15.95" customHeight="1">
       <c r="A755" s="3"/>
       <c r="B755" s="3"/>
       <c r="C755" s="3"/>
@@ -31483,7 +31489,7 @@
       <c r="AK755" s="6"/>
       <c r="AL755" s="6"/>
     </row>
-    <row r="756" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:38" ht="15.95" customHeight="1">
       <c r="A756" s="3"/>
       <c r="B756" s="3"/>
       <c r="C756" s="3"/>
@@ -31523,7 +31529,7 @@
       <c r="AK756" s="6"/>
       <c r="AL756" s="6"/>
     </row>
-    <row r="757" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:38" ht="15.95" customHeight="1">
       <c r="A757" s="3"/>
       <c r="B757" s="3"/>
       <c r="C757" s="3"/>
@@ -31563,7 +31569,7 @@
       <c r="AK757" s="6"/>
       <c r="AL757" s="6"/>
     </row>
-    <row r="758" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:38" ht="15.95" customHeight="1">
       <c r="A758" s="3"/>
       <c r="B758" s="3"/>
       <c r="C758" s="3"/>
@@ -31603,7 +31609,7 @@
       <c r="AK758" s="6"/>
       <c r="AL758" s="6"/>
     </row>
-    <row r="759" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:38" ht="15.95" customHeight="1">
       <c r="A759" s="3"/>
       <c r="B759" s="3"/>
       <c r="C759" s="3"/>
@@ -31643,7 +31649,7 @@
       <c r="AK759" s="6"/>
       <c r="AL759" s="6"/>
     </row>
-    <row r="760" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:38" ht="15.95" customHeight="1">
       <c r="A760" s="3"/>
       <c r="B760" s="3"/>
       <c r="C760" s="3"/>
@@ -31683,7 +31689,7 @@
       <c r="AK760" s="6"/>
       <c r="AL760" s="6"/>
     </row>
-    <row r="761" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:38" ht="15.95" customHeight="1">
       <c r="A761" s="3"/>
       <c r="B761" s="3"/>
       <c r="C761" s="3"/>
@@ -31723,7 +31729,7 @@
       <c r="AK761" s="6"/>
       <c r="AL761" s="6"/>
     </row>
-    <row r="762" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:38" ht="15.95" customHeight="1">
       <c r="A762" s="3"/>
       <c r="B762" s="3"/>
       <c r="C762" s="3"/>
@@ -31763,7 +31769,7 @@
       <c r="AK762" s="6"/>
       <c r="AL762" s="6"/>
     </row>
-    <row r="763" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:38" ht="15.95" customHeight="1">
       <c r="A763" s="3"/>
       <c r="B763" s="3"/>
       <c r="C763" s="3"/>
@@ -31803,7 +31809,7 @@
       <c r="AK763" s="6"/>
       <c r="AL763" s="6"/>
     </row>
-    <row r="764" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:38" ht="15.95" customHeight="1">
       <c r="A764" s="3"/>
       <c r="B764" s="3"/>
       <c r="C764" s="3"/>
@@ -31843,7 +31849,7 @@
       <c r="AK764" s="6"/>
       <c r="AL764" s="6"/>
     </row>
-    <row r="765" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:38" ht="15.95" customHeight="1">
       <c r="A765" s="3"/>
       <c r="B765" s="3"/>
       <c r="C765" s="3"/>
@@ -31883,7 +31889,7 @@
       <c r="AK765" s="6"/>
       <c r="AL765" s="6"/>
     </row>
-    <row r="766" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:38" ht="15.95" customHeight="1">
       <c r="A766" s="3"/>
       <c r="B766" s="3"/>
       <c r="C766" s="3"/>
@@ -31923,7 +31929,7 @@
       <c r="AK766" s="6"/>
       <c r="AL766" s="6"/>
     </row>
-    <row r="767" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:38" ht="15.95" customHeight="1">
       <c r="A767" s="3"/>
       <c r="B767" s="3"/>
       <c r="C767" s="3"/>
@@ -31963,7 +31969,7 @@
       <c r="AK767" s="6"/>
       <c r="AL767" s="6"/>
     </row>
-    <row r="768" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:38" ht="15.95" customHeight="1">
       <c r="A768" s="3"/>
       <c r="B768" s="3"/>
       <c r="C768" s="3"/>
@@ -32003,7 +32009,7 @@
       <c r="AK768" s="6"/>
       <c r="AL768" s="6"/>
     </row>
-    <row r="769" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:38" ht="15.95" customHeight="1">
       <c r="A769" s="3"/>
       <c r="B769" s="3"/>
       <c r="C769" s="3"/>
@@ -32043,7 +32049,7 @@
       <c r="AK769" s="6"/>
       <c r="AL769" s="6"/>
     </row>
-    <row r="770" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:38" ht="15.95" customHeight="1">
       <c r="A770" s="3"/>
       <c r="B770" s="3"/>
       <c r="C770" s="3"/>
@@ -32083,7 +32089,7 @@
       <c r="AK770" s="6"/>
       <c r="AL770" s="6"/>
     </row>
-    <row r="771" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:38" ht="15.95" customHeight="1">
       <c r="A771" s="3"/>
       <c r="B771" s="3"/>
       <c r="C771" s="3"/>
@@ -32123,7 +32129,7 @@
       <c r="AK771" s="6"/>
       <c r="AL771" s="6"/>
     </row>
-    <row r="772" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:38" ht="15.95" customHeight="1">
       <c r="A772" s="3"/>
       <c r="B772" s="3"/>
       <c r="C772" s="3"/>
@@ -32163,7 +32169,7 @@
       <c r="AK772" s="6"/>
       <c r="AL772" s="6"/>
     </row>
-    <row r="773" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:38" ht="15.95" customHeight="1">
       <c r="A773" s="3"/>
       <c r="B773" s="3"/>
       <c r="C773" s="3"/>
@@ -32203,7 +32209,7 @@
       <c r="AK773" s="6"/>
       <c r="AL773" s="6"/>
     </row>
-    <row r="774" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:38" ht="15.95" customHeight="1">
       <c r="A774" s="3"/>
       <c r="B774" s="3"/>
       <c r="C774" s="3"/>
@@ -32243,7 +32249,7 @@
       <c r="AK774" s="6"/>
       <c r="AL774" s="6"/>
     </row>
-    <row r="775" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:38" ht="15.95" customHeight="1">
       <c r="A775" s="3"/>
       <c r="B775" s="3"/>
       <c r="C775" s="3"/>
@@ -32283,7 +32289,7 @@
       <c r="AK775" s="6"/>
       <c r="AL775" s="6"/>
     </row>
-    <row r="776" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:38" ht="15.95" customHeight="1">
       <c r="A776" s="3"/>
       <c r="B776" s="3"/>
       <c r="C776" s="3"/>
@@ -32323,7 +32329,7 @@
       <c r="AK776" s="6"/>
       <c r="AL776" s="6"/>
     </row>
-    <row r="777" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:38" ht="15.95" customHeight="1">
       <c r="A777" s="3"/>
       <c r="B777" s="3"/>
       <c r="C777" s="3"/>
@@ -32363,7 +32369,7 @@
       <c r="AK777" s="6"/>
       <c r="AL777" s="6"/>
     </row>
-    <row r="778" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:38" ht="15.95" customHeight="1">
       <c r="A778" s="3"/>
       <c r="B778" s="3"/>
       <c r="C778" s="3"/>
@@ -32403,7 +32409,7 @@
       <c r="AK778" s="6"/>
       <c r="AL778" s="6"/>
     </row>
-    <row r="779" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:38" ht="15.95" customHeight="1">
       <c r="A779" s="3"/>
       <c r="B779" s="3"/>
       <c r="C779" s="3"/>
@@ -32443,7 +32449,7 @@
       <c r="AK779" s="6"/>
       <c r="AL779" s="6"/>
     </row>
-    <row r="780" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:38" ht="15.95" customHeight="1">
       <c r="A780" s="3"/>
       <c r="B780" s="3"/>
       <c r="C780" s="3"/>
@@ -32483,7 +32489,7 @@
       <c r="AK780" s="6"/>
       <c r="AL780" s="6"/>
     </row>
-    <row r="781" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:38" ht="15.95" customHeight="1">
       <c r="A781" s="3"/>
       <c r="B781" s="3"/>
       <c r="C781" s="3"/>
@@ -32523,7 +32529,7 @@
       <c r="AK781" s="6"/>
       <c r="AL781" s="6"/>
     </row>
-    <row r="782" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:38" ht="15.95" customHeight="1">
       <c r="A782" s="3"/>
       <c r="B782" s="3"/>
       <c r="C782" s="3"/>
@@ -32563,7 +32569,7 @@
       <c r="AK782" s="6"/>
       <c r="AL782" s="6"/>
     </row>
-    <row r="783" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:38" ht="15.95" customHeight="1">
       <c r="A783" s="3"/>
       <c r="B783" s="3"/>
       <c r="C783" s="3"/>
@@ -32603,7 +32609,7 @@
       <c r="AK783" s="6"/>
       <c r="AL783" s="6"/>
     </row>
-    <row r="784" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:38" ht="15.95" customHeight="1">
       <c r="A784" s="3"/>
       <c r="B784" s="3"/>
       <c r="C784" s="3"/>
@@ -32643,7 +32649,7 @@
       <c r="AK784" s="6"/>
       <c r="AL784" s="6"/>
     </row>
-    <row r="785" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:38" ht="15.95" customHeight="1">
       <c r="A785" s="3"/>
       <c r="B785" s="3"/>
       <c r="C785" s="3"/>
@@ -32683,7 +32689,7 @@
       <c r="AK785" s="6"/>
       <c r="AL785" s="6"/>
     </row>
-    <row r="786" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:38" ht="15.95" customHeight="1">
       <c r="A786" s="3"/>
       <c r="B786" s="3"/>
       <c r="C786" s="3"/>
@@ -32723,7 +32729,7 @@
       <c r="AK786" s="6"/>
       <c r="AL786" s="6"/>
     </row>
-    <row r="787" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:38" ht="15.95" customHeight="1">
       <c r="A787" s="3"/>
       <c r="B787" s="3"/>
       <c r="C787" s="3"/>
@@ -32763,7 +32769,7 @@
       <c r="AK787" s="6"/>
       <c r="AL787" s="6"/>
     </row>
-    <row r="788" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:38" ht="15.95" customHeight="1">
       <c r="A788" s="3"/>
       <c r="B788" s="3"/>
       <c r="C788" s="3"/>
@@ -32803,7 +32809,7 @@
       <c r="AK788" s="6"/>
       <c r="AL788" s="6"/>
     </row>
-    <row r="789" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:38" ht="15.95" customHeight="1">
       <c r="A789" s="3"/>
       <c r="B789" s="3"/>
       <c r="C789" s="3"/>
@@ -32843,7 +32849,7 @@
       <c r="AK789" s="6"/>
       <c r="AL789" s="6"/>
     </row>
-    <row r="790" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:38" ht="15.95" customHeight="1">
       <c r="A790" s="3"/>
       <c r="B790" s="3"/>
       <c r="C790" s="3"/>
@@ -32883,7 +32889,7 @@
       <c r="AK790" s="6"/>
       <c r="AL790" s="6"/>
     </row>
-    <row r="791" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:38" ht="15.95" customHeight="1">
       <c r="A791" s="3"/>
       <c r="B791" s="3"/>
       <c r="C791" s="3"/>
@@ -32923,7 +32929,7 @@
       <c r="AK791" s="6"/>
       <c r="AL791" s="6"/>
     </row>
-    <row r="792" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:38" ht="15.95" customHeight="1">
       <c r="A792" s="3"/>
       <c r="B792" s="3"/>
       <c r="C792" s="3"/>
@@ -32963,7 +32969,7 @@
       <c r="AK792" s="6"/>
       <c r="AL792" s="6"/>
     </row>
-    <row r="793" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:38" ht="15.95" customHeight="1">
       <c r="A793" s="3"/>
       <c r="B793" s="3"/>
       <c r="C793" s="3"/>
@@ -33003,7 +33009,7 @@
       <c r="AK793" s="6"/>
       <c r="AL793" s="6"/>
     </row>
-    <row r="794" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:38" ht="15.95" customHeight="1">
       <c r="A794" s="3"/>
       <c r="B794" s="3"/>
       <c r="C794" s="3"/>
@@ -33043,7 +33049,7 @@
       <c r="AK794" s="6"/>
       <c r="AL794" s="6"/>
     </row>
-    <row r="795" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:38" ht="15.95" customHeight="1">
       <c r="A795" s="3"/>
       <c r="B795" s="3"/>
       <c r="C795" s="3"/>
@@ -33083,7 +33089,7 @@
       <c r="AK795" s="6"/>
       <c r="AL795" s="6"/>
     </row>
-    <row r="796" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:38" ht="15.95" customHeight="1">
       <c r="A796" s="3"/>
       <c r="B796" s="3"/>
       <c r="C796" s="3"/>
@@ -33123,7 +33129,7 @@
       <c r="AK796" s="6"/>
       <c r="AL796" s="6"/>
     </row>
-    <row r="797" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:38" ht="15.95" customHeight="1">
       <c r="A797" s="3"/>
       <c r="B797" s="3"/>
       <c r="C797" s="3"/>
@@ -33163,7 +33169,7 @@
       <c r="AK797" s="6"/>
       <c r="AL797" s="6"/>
     </row>
-    <row r="798" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:38" ht="15.95" customHeight="1">
       <c r="A798" s="3"/>
       <c r="B798" s="3"/>
       <c r="C798" s="3"/>
@@ -33203,7 +33209,7 @@
       <c r="AK798" s="6"/>
       <c r="AL798" s="6"/>
     </row>
-    <row r="799" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:38" ht="15.95" customHeight="1">
       <c r="A799" s="3"/>
       <c r="B799" s="3"/>
       <c r="C799" s="3"/>
@@ -33243,7 +33249,7 @@
       <c r="AK799" s="6"/>
       <c r="AL799" s="6"/>
     </row>
-    <row r="800" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:38" ht="15.95" customHeight="1">
       <c r="A800" s="3"/>
       <c r="B800" s="3"/>
       <c r="C800" s="3"/>
@@ -33283,7 +33289,7 @@
       <c r="AK800" s="6"/>
       <c r="AL800" s="6"/>
     </row>
-    <row r="801" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:38" ht="15.95" customHeight="1">
       <c r="A801" s="3"/>
       <c r="B801" s="3"/>
       <c r="C801" s="3"/>
@@ -33323,7 +33329,7 @@
       <c r="AK801" s="6"/>
       <c r="AL801" s="6"/>
     </row>
-    <row r="802" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:38" ht="15.95" customHeight="1">
       <c r="A802" s="3"/>
       <c r="B802" s="3"/>
       <c r="C802" s="3"/>
@@ -33363,7 +33369,7 @@
       <c r="AK802" s="6"/>
       <c r="AL802" s="6"/>
     </row>
-    <row r="803" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:38" ht="15.95" customHeight="1">
       <c r="A803" s="3"/>
       <c r="B803" s="3"/>
       <c r="C803" s="3"/>
@@ -33403,7 +33409,7 @@
       <c r="AK803" s="6"/>
       <c r="AL803" s="6"/>
     </row>
-    <row r="804" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:38" ht="15.95" customHeight="1">
       <c r="A804" s="3"/>
       <c r="B804" s="3"/>
       <c r="C804" s="3"/>
@@ -33443,7 +33449,7 @@
       <c r="AK804" s="6"/>
       <c r="AL804" s="6"/>
     </row>
-    <row r="805" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:38" ht="15.95" customHeight="1">
       <c r="A805" s="3"/>
       <c r="B805" s="3"/>
       <c r="C805" s="3"/>
@@ -33483,7 +33489,7 @@
       <c r="AK805" s="6"/>
       <c r="AL805" s="6"/>
     </row>
-    <row r="806" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:38" ht="15.95" customHeight="1">
       <c r="A806" s="3"/>
       <c r="B806" s="3"/>
       <c r="C806" s="3"/>
@@ -33523,7 +33529,7 @@
       <c r="AK806" s="6"/>
       <c r="AL806" s="6"/>
     </row>
-    <row r="807" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:38" ht="15.95" customHeight="1">
       <c r="A807" s="3"/>
       <c r="B807" s="3"/>
       <c r="C807" s="3"/>
@@ -33563,7 +33569,7 @@
       <c r="AK807" s="6"/>
       <c r="AL807" s="6"/>
     </row>
-    <row r="808" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:38" ht="15.95" customHeight="1">
       <c r="A808" s="3"/>
       <c r="B808" s="3"/>
       <c r="C808" s="3"/>
@@ -33603,7 +33609,7 @@
       <c r="AK808" s="6"/>
       <c r="AL808" s="6"/>
     </row>
-    <row r="809" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:38" ht="15.95" customHeight="1">
       <c r="A809" s="3"/>
       <c r="B809" s="3"/>
       <c r="C809" s="3"/>
@@ -33643,7 +33649,7 @@
       <c r="AK809" s="6"/>
       <c r="AL809" s="6"/>
     </row>
-    <row r="810" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:38" ht="15.95" customHeight="1">
       <c r="A810" s="3"/>
       <c r="B810" s="3"/>
       <c r="C810" s="3"/>
@@ -33683,7 +33689,7 @@
       <c r="AK810" s="6"/>
       <c r="AL810" s="6"/>
     </row>
-    <row r="811" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:38" ht="15.95" customHeight="1">
       <c r="A811" s="3"/>
       <c r="B811" s="3"/>
       <c r="C811" s="3"/>
@@ -33723,7 +33729,7 @@
       <c r="AK811" s="6"/>
       <c r="AL811" s="6"/>
     </row>
-    <row r="812" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:38" ht="15.95" customHeight="1">
       <c r="A812" s="3"/>
       <c r="B812" s="3"/>
       <c r="C812" s="3"/>
@@ -33763,7 +33769,7 @@
       <c r="AK812" s="6"/>
       <c r="AL812" s="6"/>
     </row>
-    <row r="813" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:38" ht="15.95" customHeight="1">
       <c r="A813" s="3"/>
       <c r="B813" s="3"/>
       <c r="C813" s="3"/>
@@ -33803,7 +33809,7 @@
       <c r="AK813" s="6"/>
       <c r="AL813" s="6"/>
     </row>
-    <row r="814" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:38" ht="15.95" customHeight="1">
       <c r="A814" s="3"/>
       <c r="B814" s="3"/>
       <c r="C814" s="3"/>
@@ -33843,7 +33849,7 @@
       <c r="AK814" s="6"/>
       <c r="AL814" s="6"/>
     </row>
-    <row r="815" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:38" ht="15.95" customHeight="1">
       <c r="A815" s="3"/>
       <c r="B815" s="3"/>
       <c r="C815" s="3"/>
@@ -33883,7 +33889,7 @@
       <c r="AK815" s="6"/>
       <c r="AL815" s="6"/>
     </row>
-    <row r="816" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:38" ht="15.95" customHeight="1">
       <c r="A816" s="3"/>
       <c r="B816" s="3"/>
       <c r="C816" s="3"/>
@@ -33923,7 +33929,7 @@
       <c r="AK816" s="6"/>
       <c r="AL816" s="6"/>
     </row>
-    <row r="817" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:38" ht="15.95" customHeight="1">
       <c r="A817" s="3"/>
       <c r="B817" s="3"/>
       <c r="C817" s="3"/>
@@ -33963,7 +33969,7 @@
       <c r="AK817" s="6"/>
       <c r="AL817" s="6"/>
     </row>
-    <row r="818" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:38" ht="15.95" customHeight="1">
       <c r="A818" s="3"/>
       <c r="B818" s="3"/>
       <c r="C818" s="3"/>
@@ -34003,7 +34009,7 @@
       <c r="AK818" s="6"/>
       <c r="AL818" s="6"/>
     </row>
-    <row r="819" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:38" ht="15.95" customHeight="1">
       <c r="A819" s="3"/>
       <c r="B819" s="3"/>
       <c r="C819" s="3"/>
@@ -34043,7 +34049,7 @@
       <c r="AK819" s="6"/>
       <c r="AL819" s="6"/>
     </row>
-    <row r="820" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:38" ht="15.95" customHeight="1">
       <c r="A820" s="3"/>
       <c r="B820" s="3"/>
       <c r="C820" s="3"/>
@@ -34083,7 +34089,7 @@
       <c r="AK820" s="6"/>
       <c r="AL820" s="6"/>
     </row>
-    <row r="821" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:38" ht="15.95" customHeight="1">
       <c r="A821" s="3"/>
       <c r="B821" s="3"/>
       <c r="C821" s="3"/>
@@ -34123,7 +34129,7 @@
       <c r="AK821" s="6"/>
       <c r="AL821" s="6"/>
     </row>
-    <row r="822" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:38" ht="15.95" customHeight="1">
       <c r="A822" s="3"/>
       <c r="B822" s="3"/>
       <c r="C822" s="3"/>
@@ -34163,7 +34169,7 @@
       <c r="AK822" s="6"/>
       <c r="AL822" s="6"/>
     </row>
-    <row r="823" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:38" ht="15.95" customHeight="1">
       <c r="A823" s="3"/>
       <c r="B823" s="3"/>
       <c r="C823" s="3"/>
@@ -34203,7 +34209,7 @@
       <c r="AK823" s="6"/>
       <c r="AL823" s="6"/>
     </row>
-    <row r="824" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:38" ht="15.95" customHeight="1">
       <c r="A824" s="3"/>
       <c r="B824" s="3"/>
       <c r="C824" s="3"/>
@@ -34243,7 +34249,7 @@
       <c r="AK824" s="6"/>
       <c r="AL824" s="6"/>
     </row>
-    <row r="825" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:38" ht="15.95" customHeight="1">
       <c r="A825" s="3"/>
       <c r="B825" s="3"/>
       <c r="C825" s="3"/>
@@ -34283,7 +34289,7 @@
       <c r="AK825" s="6"/>
       <c r="AL825" s="6"/>
     </row>
-    <row r="826" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:38" ht="15.95" customHeight="1">
       <c r="A826" s="3"/>
       <c r="B826" s="3"/>
       <c r="C826" s="3"/>
@@ -34323,7 +34329,7 @@
       <c r="AK826" s="6"/>
       <c r="AL826" s="6"/>
     </row>
-    <row r="827" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:38" ht="15.95" customHeight="1">
       <c r="A827" s="3"/>
       <c r="B827" s="3"/>
       <c r="C827" s="3"/>
@@ -34363,7 +34369,7 @@
       <c r="AK827" s="6"/>
       <c r="AL827" s="6"/>
     </row>
-    <row r="828" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:38" ht="15.95" customHeight="1">
       <c r="A828" s="3"/>
       <c r="B828" s="3"/>
       <c r="C828" s="3"/>
@@ -34403,7 +34409,7 @@
       <c r="AK828" s="6"/>
       <c r="AL828" s="6"/>
     </row>
-    <row r="829" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:38" ht="15.95" customHeight="1">
       <c r="A829" s="3"/>
       <c r="B829" s="3"/>
       <c r="C829" s="3"/>
@@ -34443,7 +34449,7 @@
       <c r="AK829" s="6"/>
       <c r="AL829" s="6"/>
     </row>
-    <row r="830" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:38" ht="15.95" customHeight="1">
       <c r="A830" s="3"/>
       <c r="B830" s="3"/>
       <c r="C830" s="3"/>
@@ -34483,7 +34489,7 @@
       <c r="AK830" s="6"/>
       <c r="AL830" s="6"/>
     </row>
-    <row r="831" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:38" ht="15.95" customHeight="1">
       <c r="A831" s="3"/>
       <c r="B831" s="3"/>
       <c r="C831" s="3"/>
@@ -34523,7 +34529,7 @@
       <c r="AK831" s="6"/>
       <c r="AL831" s="6"/>
     </row>
-    <row r="832" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:38" ht="15.95" customHeight="1">
       <c r="A832" s="3"/>
       <c r="B832" s="3"/>
       <c r="C832" s="3"/>
@@ -34563,7 +34569,7 @@
       <c r="AK832" s="6"/>
       <c r="AL832" s="6"/>
     </row>
-    <row r="833" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:38" ht="15.95" customHeight="1">
       <c r="A833" s="3"/>
       <c r="B833" s="3"/>
       <c r="C833" s="3"/>
@@ -34603,7 +34609,7 @@
       <c r="AK833" s="6"/>
       <c r="AL833" s="6"/>
     </row>
-    <row r="834" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:38" ht="15.95" customHeight="1">
       <c r="A834" s="3"/>
       <c r="B834" s="3"/>
       <c r="C834" s="3"/>
@@ -34643,7 +34649,7 @@
       <c r="AK834" s="6"/>
       <c r="AL834" s="6"/>
     </row>
-    <row r="835" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:38" ht="15.95" customHeight="1">
       <c r="A835" s="3"/>
       <c r="B835" s="3"/>
       <c r="C835" s="3"/>
@@ -34683,7 +34689,7 @@
       <c r="AK835" s="6"/>
       <c r="AL835" s="6"/>
     </row>
-    <row r="836" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:38" ht="15.95" customHeight="1">
       <c r="A836" s="3"/>
       <c r="B836" s="3"/>
       <c r="C836" s="3"/>
@@ -34723,7 +34729,7 @@
       <c r="AK836" s="6"/>
       <c r="AL836" s="6"/>
     </row>
-    <row r="837" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:38" ht="15.95" customHeight="1">
       <c r="A837" s="3"/>
       <c r="B837" s="3"/>
       <c r="C837" s="3"/>
@@ -34763,7 +34769,7 @@
       <c r="AK837" s="6"/>
       <c r="AL837" s="6"/>
     </row>
-    <row r="838" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:38" ht="15.95" customHeight="1">
       <c r="A838" s="3"/>
       <c r="B838" s="3"/>
       <c r="C838" s="3"/>
@@ -34803,7 +34809,7 @@
       <c r="AK838" s="6"/>
       <c r="AL838" s="6"/>
     </row>
-    <row r="839" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:38" ht="15.95" customHeight="1">
       <c r="A839" s="3"/>
       <c r="B839" s="3"/>
       <c r="C839" s="3"/>
@@ -34843,7 +34849,7 @@
       <c r="AK839" s="6"/>
       <c r="AL839" s="6"/>
     </row>
-    <row r="840" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:38" ht="15.95" customHeight="1">
       <c r="A840" s="3"/>
       <c r="B840" s="3"/>
       <c r="C840" s="3"/>
@@ -34883,7 +34889,7 @@
       <c r="AK840" s="6"/>
       <c r="AL840" s="6"/>
     </row>
-    <row r="841" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:38" ht="15.95" customHeight="1">
       <c r="A841" s="3"/>
       <c r="B841" s="3"/>
       <c r="C841" s="3"/>
@@ -34923,7 +34929,7 @@
       <c r="AK841" s="6"/>
       <c r="AL841" s="6"/>
     </row>
-    <row r="842" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:38" ht="15.95" customHeight="1">
       <c r="A842" s="3"/>
       <c r="B842" s="3"/>
       <c r="C842" s="3"/>
@@ -34963,7 +34969,7 @@
       <c r="AK842" s="6"/>
       <c r="AL842" s="6"/>
     </row>
-    <row r="843" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:38" ht="15.95" customHeight="1">
       <c r="A843" s="3"/>
       <c r="B843" s="3"/>
       <c r="C843" s="3"/>
@@ -35003,7 +35009,7 @@
       <c r="AK843" s="6"/>
       <c r="AL843" s="6"/>
     </row>
-    <row r="844" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:38" ht="15.95" customHeight="1">
       <c r="A844" s="3"/>
       <c r="B844" s="3"/>
       <c r="C844" s="3"/>
@@ -35043,7 +35049,7 @@
       <c r="AK844" s="6"/>
       <c r="AL844" s="6"/>
     </row>
-    <row r="845" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:38" ht="15.95" customHeight="1">
       <c r="A845" s="3"/>
       <c r="B845" s="3"/>
       <c r="C845" s="3"/>
@@ -35083,7 +35089,7 @@
       <c r="AK845" s="6"/>
       <c r="AL845" s="6"/>
     </row>
-    <row r="846" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:38" ht="15.95" customHeight="1">
       <c r="A846" s="3"/>
       <c r="B846" s="3"/>
       <c r="C846" s="3"/>
@@ -35123,7 +35129,7 @@
       <c r="AK846" s="6"/>
       <c r="AL846" s="6"/>
     </row>
-    <row r="847" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:38" ht="15.95" customHeight="1">
       <c r="A847" s="3"/>
       <c r="B847" s="3"/>
       <c r="C847" s="3"/>
@@ -35163,7 +35169,7 @@
       <c r="AK847" s="6"/>
       <c r="AL847" s="6"/>
     </row>
-    <row r="848" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:38" ht="15.95" customHeight="1">
       <c r="A848" s="3"/>
       <c r="B848" s="3"/>
       <c r="C848" s="3"/>
@@ -35203,7 +35209,7 @@
       <c r="AK848" s="6"/>
       <c r="AL848" s="6"/>
     </row>
-    <row r="849" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="849" spans="1:38" ht="15.95" customHeight="1">
       <c r="A849" s="3"/>
       <c r="B849" s="3"/>
       <c r="C849" s="3"/>
@@ -35243,7 +35249,7 @@
       <c r="AK849" s="6"/>
       <c r="AL849" s="6"/>
     </row>
-    <row r="850" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="850" spans="1:38" ht="15.95" customHeight="1">
       <c r="A850" s="3"/>
       <c r="B850" s="3"/>
       <c r="C850" s="3"/>
@@ -35283,7 +35289,7 @@
       <c r="AK850" s="6"/>
       <c r="AL850" s="6"/>
     </row>
-    <row r="851" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="851" spans="1:38" ht="15.95" customHeight="1">
       <c r="A851" s="3"/>
       <c r="B851" s="3"/>
       <c r="C851" s="3"/>
@@ -35323,7 +35329,7 @@
       <c r="AK851" s="6"/>
       <c r="AL851" s="6"/>
     </row>
-    <row r="852" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="852" spans="1:38" ht="15.95" customHeight="1">
       <c r="A852" s="3"/>
       <c r="B852" s="3"/>
       <c r="C852" s="3"/>
@@ -35363,7 +35369,7 @@
       <c r="AK852" s="6"/>
       <c r="AL852" s="6"/>
     </row>
-    <row r="853" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="853" spans="1:38" ht="15.95" customHeight="1">
       <c r="A853" s="3"/>
       <c r="B853" s="3"/>
       <c r="C853" s="3"/>
@@ -35403,7 +35409,7 @@
       <c r="AK853" s="6"/>
       <c r="AL853" s="6"/>
     </row>
-    <row r="854" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="854" spans="1:38" ht="15.95" customHeight="1">
       <c r="A854" s="3"/>
       <c r="B854" s="3"/>
       <c r="C854" s="3"/>
@@ -35443,7 +35449,7 @@
       <c r="AK854" s="6"/>
       <c r="AL854" s="6"/>
     </row>
-    <row r="855" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="855" spans="1:38" ht="15.95" customHeight="1">
       <c r="A855" s="3"/>
       <c r="B855" s="3"/>
       <c r="C855" s="3"/>
@@ -35483,7 +35489,7 @@
       <c r="AK855" s="6"/>
       <c r="AL855" s="6"/>
     </row>
-    <row r="856" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="856" spans="1:38" ht="15.95" customHeight="1">
       <c r="A856" s="3"/>
       <c r="B856" s="3"/>
       <c r="C856" s="3"/>
@@ -35523,7 +35529,7 @@
       <c r="AK856" s="6"/>
       <c r="AL856" s="6"/>
     </row>
-    <row r="857" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="857" spans="1:38" ht="15.95" customHeight="1">
       <c r="A857" s="3"/>
       <c r="B857" s="3"/>
       <c r="C857" s="3"/>
@@ -35563,7 +35569,7 @@
       <c r="AK857" s="6"/>
       <c r="AL857" s="6"/>
     </row>
-    <row r="858" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="858" spans="1:38" ht="15.95" customHeight="1">
       <c r="A858" s="3"/>
       <c r="B858" s="3"/>
       <c r="C858" s="3"/>
@@ -35603,7 +35609,7 @@
       <c r="AK858" s="6"/>
       <c r="AL858" s="6"/>
     </row>
-    <row r="859" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:38" ht="15.95" customHeight="1">
       <c r="A859" s="3"/>
       <c r="B859" s="3"/>
       <c r="C859" s="3"/>
@@ -35643,7 +35649,7 @@
       <c r="AK859" s="6"/>
       <c r="AL859" s="6"/>
     </row>
-    <row r="860" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="860" spans="1:38" ht="15.95" customHeight="1">
       <c r="A860" s="3"/>
       <c r="B860" s="3"/>
       <c r="C860" s="3"/>
@@ -35683,7 +35689,7 @@
       <c r="AK860" s="6"/>
       <c r="AL860" s="6"/>
     </row>
-    <row r="861" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="861" spans="1:38" ht="15.95" customHeight="1">
       <c r="A861" s="3"/>
       <c r="B861" s="3"/>
       <c r="C861" s="3"/>
@@ -35723,7 +35729,7 @@
       <c r="AK861" s="6"/>
       <c r="AL861" s="6"/>
     </row>
-    <row r="862" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="862" spans="1:38" ht="15.95" customHeight="1">
       <c r="A862" s="3"/>
       <c r="B862" s="3"/>
       <c r="C862" s="3"/>
@@ -35763,7 +35769,7 @@
       <c r="AK862" s="6"/>
       <c r="AL862" s="6"/>
     </row>
-    <row r="863" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="863" spans="1:38" ht="15.95" customHeight="1">
       <c r="A863" s="3"/>
       <c r="B863" s="3"/>
       <c r="C863" s="3"/>
@@ -35803,7 +35809,7 @@
       <c r="AK863" s="6"/>
       <c r="AL863" s="6"/>
     </row>
-    <row r="864" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="864" spans="1:38" ht="15.95" customHeight="1">
       <c r="A864" s="3"/>
       <c r="B864" s="3"/>
       <c r="C864" s="3"/>
@@ -35843,7 +35849,7 @@
       <c r="AK864" s="6"/>
       <c r="AL864" s="6"/>
     </row>
-    <row r="865" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="865" spans="1:38" ht="15.95" customHeight="1">
       <c r="A865" s="3"/>
       <c r="B865" s="3"/>
       <c r="C865" s="3"/>
@@ -35883,7 +35889,7 @@
       <c r="AK865" s="6"/>
       <c r="AL865" s="6"/>
     </row>
-    <row r="866" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="866" spans="1:38" ht="15.95" customHeight="1">
       <c r="A866" s="3"/>
       <c r="B866" s="3"/>
       <c r="C866" s="3"/>
@@ -35923,7 +35929,7 @@
       <c r="AK866" s="6"/>
       <c r="AL866" s="6"/>
     </row>
-    <row r="867" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="867" spans="1:38" ht="15.95" customHeight="1">
       <c r="A867" s="3"/>
       <c r="B867" s="3"/>
       <c r="C867" s="3"/>
@@ -35963,7 +35969,7 @@
       <c r="AK867" s="6"/>
       <c r="AL867" s="6"/>
     </row>
-    <row r="868" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="868" spans="1:38" ht="15.95" customHeight="1">
       <c r="A868" s="3"/>
       <c r="B868" s="3"/>
       <c r="C868" s="3"/>
@@ -36003,7 +36009,7 @@
       <c r="AK868" s="6"/>
       <c r="AL868" s="6"/>
     </row>
-    <row r="869" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="869" spans="1:38" ht="15.95" customHeight="1">
       <c r="A869" s="3"/>
       <c r="B869" s="3"/>
       <c r="C869" s="3"/>
@@ -36043,7 +36049,7 @@
       <c r="AK869" s="6"/>
       <c r="AL869" s="6"/>
     </row>
-    <row r="870" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="870" spans="1:38" ht="15.95" customHeight="1">
       <c r="A870" s="3"/>
       <c r="B870" s="3"/>
       <c r="C870" s="3"/>
@@ -36083,7 +36089,7 @@
       <c r="AK870" s="6"/>
       <c r="AL870" s="6"/>
     </row>
-    <row r="871" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="871" spans="1:38" ht="15.95" customHeight="1">
       <c r="A871" s="3"/>
       <c r="B871" s="3"/>
       <c r="C871" s="3"/>
@@ -36123,7 +36129,7 @@
       <c r="AK871" s="6"/>
       <c r="AL871" s="6"/>
     </row>
-    <row r="872" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="872" spans="1:38" ht="15.95" customHeight="1">
       <c r="A872" s="3"/>
       <c r="B872" s="3"/>
       <c r="C872" s="3"/>
@@ -36163,7 +36169,7 @@
       <c r="AK872" s="6"/>
       <c r="AL872" s="6"/>
     </row>
-    <row r="873" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="873" spans="1:38" ht="15.95" customHeight="1">
       <c r="A873" s="3"/>
       <c r="B873" s="3"/>
       <c r="C873" s="3"/>
@@ -36203,7 +36209,7 @@
       <c r="AK873" s="6"/>
       <c r="AL873" s="6"/>
     </row>
-    <row r="874" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="874" spans="1:38" ht="15.95" customHeight="1">
       <c r="A874" s="3"/>
       <c r="B874" s="3"/>
       <c r="C874" s="3"/>
@@ -36243,7 +36249,7 @@
       <c r="AK874" s="6"/>
       <c r="AL874" s="6"/>
     </row>
-    <row r="875" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="875" spans="1:38" ht="15.95" customHeight="1">
       <c r="A875" s="3"/>
       <c r="B875" s="3"/>
       <c r="C875" s="3"/>
@@ -36283,7 +36289,7 @@
       <c r="AK875" s="6"/>
       <c r="AL875" s="6"/>
     </row>
-    <row r="876" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="876" spans="1:38" ht="15.95" customHeight="1">
       <c r="A876" s="3"/>
       <c r="B876" s="3"/>
       <c r="C876" s="3"/>
@@ -36323,7 +36329,7 @@
       <c r="AK876" s="6"/>
       <c r="AL876" s="6"/>
     </row>
-    <row r="877" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="877" spans="1:38" ht="15.95" customHeight="1">
       <c r="A877" s="3"/>
       <c r="B877" s="3"/>
       <c r="C877" s="3"/>
@@ -36363,7 +36369,7 @@
       <c r="AK877" s="6"/>
       <c r="AL877" s="6"/>
     </row>
-    <row r="878" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="878" spans="1:38" ht="15.95" customHeight="1">
       <c r="A878" s="3"/>
       <c r="B878" s="3"/>
       <c r="C878" s="3"/>
@@ -36403,7 +36409,7 @@
       <c r="AK878" s="6"/>
       <c r="AL878" s="6"/>
     </row>
-    <row r="879" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="879" spans="1:38" ht="15.95" customHeight="1">
       <c r="A879" s="3"/>
       <c r="B879" s="3"/>
       <c r="C879" s="3"/>
@@ -36443,7 +36449,7 @@
       <c r="AK879" s="6"/>
       <c r="AL879" s="6"/>
     </row>
-    <row r="880" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="880" spans="1:38" ht="15.95" customHeight="1">
       <c r="A880" s="3"/>
       <c r="B880" s="3"/>
       <c r="C880" s="3"/>
@@ -36483,7 +36489,7 @@
       <c r="AK880" s="6"/>
       <c r="AL880" s="6"/>
     </row>
-    <row r="881" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="881" spans="1:38" ht="15.95" customHeight="1">
       <c r="A881" s="3"/>
       <c r="B881" s="3"/>
       <c r="C881" s="3"/>
@@ -36523,7 +36529,7 @@
       <c r="AK881" s="6"/>
       <c r="AL881" s="6"/>
     </row>
-    <row r="882" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="882" spans="1:38" ht="15.95" customHeight="1">
       <c r="A882" s="3"/>
       <c r="B882" s="3"/>
       <c r="C882" s="3"/>
@@ -36563,7 +36569,7 @@
       <c r="AK882" s="6"/>
       <c r="AL882" s="6"/>
     </row>
-    <row r="883" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="883" spans="1:38" ht="15.95" customHeight="1">
       <c r="A883" s="3"/>
       <c r="B883" s="3"/>
       <c r="C883" s="3"/>
@@ -36603,7 +36609,7 @@
       <c r="AK883" s="6"/>
       <c r="AL883" s="6"/>
     </row>
-    <row r="884" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="884" spans="1:38" ht="15.95" customHeight="1">
       <c r="A884" s="3"/>
       <c r="B884" s="3"/>
       <c r="C884" s="3"/>
@@ -36643,7 +36649,7 @@
       <c r="AK884" s="6"/>
       <c r="AL884" s="6"/>
     </row>
-    <row r="885" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="885" spans="1:38" ht="15.95" customHeight="1">
       <c r="A885" s="3"/>
       <c r="B885" s="3"/>
       <c r="C885" s="3"/>
@@ -36683,7 +36689,7 @@
       <c r="AK885" s="6"/>
       <c r="AL885" s="6"/>
     </row>
-    <row r="886" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:38" ht="15.95" customHeight="1">
       <c r="A886" s="3"/>
       <c r="B886" s="3"/>
       <c r="C886" s="3"/>
@@ -36723,7 +36729,7 @@
       <c r="AK886" s="6"/>
       <c r="AL886" s="6"/>
     </row>
-    <row r="887" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:38" ht="15.95" customHeight="1">
       <c r="A887" s="3"/>
       <c r="B887" s="3"/>
       <c r="C887" s="3"/>
@@ -36763,7 +36769,7 @@
       <c r="AK887" s="6"/>
       <c r="AL887" s="6"/>
     </row>
-    <row r="888" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:38" ht="15.95" customHeight="1">
       <c r="A888" s="3"/>
       <c r="B888" s="3"/>
       <c r="C888" s="3"/>
@@ -36803,7 +36809,7 @@
       <c r="AK888" s="6"/>
       <c r="AL888" s="6"/>
     </row>
-    <row r="889" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:38" ht="15.95" customHeight="1">
       <c r="A889" s="3"/>
       <c r="B889" s="3"/>
       <c r="C889" s="3"/>
@@ -36843,7 +36849,7 @@
       <c r="AK889" s="6"/>
       <c r="AL889" s="6"/>
     </row>
-    <row r="890" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:38" ht="15.95" customHeight="1">
       <c r="A890" s="3"/>
       <c r="B890" s="3"/>
       <c r="C890" s="3"/>
@@ -36883,7 +36889,7 @@
       <c r="AK890" s="6"/>
       <c r="AL890" s="6"/>
     </row>
-    <row r="891" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:38" ht="15.95" customHeight="1">
       <c r="A891" s="3"/>
       <c r="B891" s="3"/>
       <c r="C891" s="3"/>
@@ -36923,7 +36929,7 @@
       <c r="AK891" s="6"/>
       <c r="AL891" s="6"/>
     </row>
-    <row r="892" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:38" ht="15.95" customHeight="1">
       <c r="A892" s="3"/>
       <c r="B892" s="3"/>
       <c r="C892" s="3"/>
@@ -36963,7 +36969,7 @@
       <c r="AK892" s="6"/>
       <c r="AL892" s="6"/>
     </row>
-    <row r="893" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:38" ht="15.95" customHeight="1">
       <c r="A893" s="3"/>
       <c r="B893" s="3"/>
       <c r="C893" s="3"/>
@@ -37003,7 +37009,7 @@
       <c r="AK893" s="6"/>
       <c r="AL893" s="6"/>
     </row>
-    <row r="894" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:38" ht="15.95" customHeight="1">
       <c r="A894" s="3"/>
       <c r="B894" s="3"/>
       <c r="C894" s="3"/>
@@ -37043,7 +37049,7 @@
       <c r="AK894" s="6"/>
       <c r="AL894" s="6"/>
     </row>
-    <row r="895" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:38" ht="15.95" customHeight="1">
       <c r="A895" s="3"/>
       <c r="B895" s="3"/>
       <c r="C895" s="3"/>
@@ -37083,7 +37089,7 @@
       <c r="AK895" s="6"/>
       <c r="AL895" s="6"/>
     </row>
-    <row r="896" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:38" ht="15.95" customHeight="1">
       <c r="A896" s="3"/>
       <c r="B896" s="3"/>
       <c r="C896" s="3"/>
@@ -37123,7 +37129,7 @@
       <c r="AK896" s="6"/>
       <c r="AL896" s="6"/>
     </row>
-    <row r="897" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:38" ht="15.95" customHeight="1">
       <c r="A897" s="3"/>
       <c r="B897" s="3"/>
       <c r="C897" s="3"/>
@@ -37163,7 +37169,7 @@
       <c r="AK897" s="6"/>
       <c r="AL897" s="6"/>
     </row>
-    <row r="898" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:38" ht="15.95" customHeight="1">
       <c r="A898" s="3"/>
       <c r="B898" s="3"/>
       <c r="C898" s="3"/>
@@ -37203,7 +37209,7 @@
       <c r="AK898" s="6"/>
       <c r="AL898" s="6"/>
     </row>
-    <row r="899" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:38" ht="15.95" customHeight="1">
       <c r="A899" s="3"/>
       <c r="B899" s="3"/>
       <c r="C899" s="3"/>
@@ -37243,7 +37249,7 @@
       <c r="AK899" s="6"/>
       <c r="AL899" s="6"/>
     </row>
-    <row r="900" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="900" spans="1:38" ht="15.95" customHeight="1">
       <c r="A900" s="3"/>
       <c r="B900" s="3"/>
       <c r="C900" s="3"/>
@@ -37283,7 +37289,7 @@
       <c r="AK900" s="6"/>
       <c r="AL900" s="6"/>
     </row>
-    <row r="901" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="901" spans="1:38" ht="15.95" customHeight="1">
       <c r="A901" s="3"/>
       <c r="B901" s="3"/>
       <c r="C901" s="3"/>
@@ -37323,7 +37329,7 @@
       <c r="AK901" s="6"/>
       <c r="AL901" s="6"/>
     </row>
-    <row r="902" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="902" spans="1:38" ht="15.95" customHeight="1">
       <c r="A902" s="3"/>
       <c r="B902" s="3"/>
       <c r="C902" s="3"/>
@@ -37363,7 +37369,7 @@
       <c r="AK902" s="6"/>
       <c r="AL902" s="6"/>
     </row>
-    <row r="903" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="903" spans="1:38" ht="15.95" customHeight="1">
       <c r="A903" s="3"/>
       <c r="B903" s="3"/>
       <c r="C903" s="3"/>
@@ -37403,7 +37409,7 @@
       <c r="AK903" s="6"/>
       <c r="AL903" s="6"/>
     </row>
-    <row r="904" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="904" spans="1:38" ht="15.95" customHeight="1">
       <c r="A904" s="3"/>
       <c r="B904" s="3"/>
       <c r="C904" s="3"/>
@@ -37443,7 +37449,7 @@
       <c r="AK904" s="6"/>
       <c r="AL904" s="6"/>
     </row>
-    <row r="905" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="905" spans="1:38" ht="15.95" customHeight="1">
       <c r="A905" s="3"/>
       <c r="B905" s="3"/>
       <c r="C905" s="3"/>
@@ -37483,7 +37489,7 @@
       <c r="AK905" s="6"/>
       <c r="AL905" s="6"/>
     </row>
-    <row r="906" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="906" spans="1:38" ht="15.95" customHeight="1">
       <c r="A906" s="3"/>
       <c r="B906" s="3"/>
       <c r="C906" s="3"/>
@@ -37523,7 +37529,7 @@
       <c r="AK906" s="6"/>
       <c r="AL906" s="6"/>
     </row>
-    <row r="907" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="907" spans="1:38" ht="15.95" customHeight="1">
       <c r="A907" s="3"/>
       <c r="B907" s="3"/>
       <c r="C907" s="3"/>
@@ -37563,7 +37569,7 @@
       <c r="AK907" s="6"/>
       <c r="AL907" s="6"/>
     </row>
-    <row r="908" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="908" spans="1:38" ht="15.95" customHeight="1">
       <c r="A908" s="3"/>
       <c r="B908" s="3"/>
       <c r="C908" s="3"/>
@@ -37603,7 +37609,7 @@
       <c r="AK908" s="6"/>
       <c r="AL908" s="6"/>
     </row>
-    <row r="909" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="909" spans="1:38" ht="15.95" customHeight="1">
       <c r="A909" s="3"/>
       <c r="B909" s="3"/>
       <c r="C909" s="3"/>
@@ -37643,7 +37649,7 @@
       <c r="AK909" s="6"/>
       <c r="AL909" s="6"/>
     </row>
-    <row r="910" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="910" spans="1:38" ht="15.95" customHeight="1">
       <c r="A910" s="3"/>
       <c r="B910" s="3"/>
       <c r="C910" s="3"/>
@@ -37683,7 +37689,7 @@
       <c r="AK910" s="6"/>
       <c r="AL910" s="6"/>
     </row>
-    <row r="911" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="911" spans="1:38" ht="15.95" customHeight="1">
       <c r="A911" s="3"/>
       <c r="B911" s="3"/>
       <c r="C911" s="3"/>
@@ -37723,7 +37729,7 @@
       <c r="AK911" s="6"/>
       <c r="AL911" s="6"/>
     </row>
-    <row r="912" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="912" spans="1:38" ht="15.95" customHeight="1">
       <c r="A912" s="3"/>
       <c r="B912" s="3"/>
       <c r="C912" s="3"/>
@@ -37763,7 +37769,7 @@
       <c r="AK912" s="6"/>
       <c r="AL912" s="6"/>
     </row>
-    <row r="913" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="913" spans="1:38" ht="15.95" customHeight="1">
       <c r="A913" s="3"/>
       <c r="B913" s="3"/>
       <c r="C913" s="3"/>
@@ -37803,7 +37809,7 @@
       <c r="AK913" s="6"/>
       <c r="AL913" s="6"/>
     </row>
-    <row r="914" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="914" spans="1:38" ht="15.95" customHeight="1">
       <c r="A914" s="3"/>
       <c r="B914" s="3"/>
       <c r="C914" s="3"/>
@@ -37843,7 +37849,7 @@
       <c r="AK914" s="6"/>
       <c r="AL914" s="6"/>
     </row>
-    <row r="915" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="915" spans="1:38" ht="15.95" customHeight="1">
       <c r="A915" s="3"/>
       <c r="B915" s="3"/>
       <c r="C915" s="3"/>
@@ -37883,7 +37889,7 @@
       <c r="AK915" s="6"/>
       <c r="AL915" s="6"/>
     </row>
-    <row r="916" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="916" spans="1:38" ht="15.95" customHeight="1">
       <c r="A916" s="3"/>
       <c r="B916" s="3"/>
       <c r="C916" s="3"/>
@@ -37923,7 +37929,7 @@
       <c r="AK916" s="6"/>
       <c r="AL916" s="6"/>
     </row>
-    <row r="917" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="917" spans="1:38" ht="15.95" customHeight="1">
       <c r="A917" s="3"/>
       <c r="B917" s="3"/>
       <c r="C917" s="3"/>
@@ -37963,7 +37969,7 @@
       <c r="AK917" s="6"/>
       <c r="AL917" s="6"/>
     </row>
-    <row r="918" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="918" spans="1:38" ht="15.95" customHeight="1">
       <c r="A918" s="3"/>
       <c r="B918" s="3"/>
       <c r="C918" s="3"/>
@@ -38003,7 +38009,7 @@
       <c r="AK918" s="6"/>
       <c r="AL918" s="6"/>
     </row>
-    <row r="919" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="919" spans="1:38" ht="15.95" customHeight="1">
       <c r="A919" s="3"/>
       <c r="B919" s="3"/>
       <c r="C919" s="3"/>
@@ -38043,7 +38049,7 @@
       <c r="AK919" s="6"/>
       <c r="AL919" s="6"/>
     </row>
-    <row r="920" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="920" spans="1:38" ht="15.95" customHeight="1">
       <c r="A920" s="3"/>
       <c r="B920" s="3"/>
       <c r="C920" s="3"/>
@@ -38083,7 +38089,7 @@
       <c r="AK920" s="6"/>
       <c r="AL920" s="6"/>
     </row>
-    <row r="921" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="921" spans="1:38" ht="15.95" customHeight="1">
       <c r="A921" s="3"/>
       <c r="B921" s="3"/>
       <c r="C921" s="3"/>
@@ -38123,7 +38129,7 @@
       <c r="AK921" s="6"/>
       <c r="AL921" s="6"/>
     </row>
-    <row r="922" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="922" spans="1:38" ht="15.95" customHeight="1">
       <c r="A922" s="3"/>
       <c r="B922" s="3"/>
       <c r="C922" s="3"/>
@@ -38163,7 +38169,7 @@
       <c r="AK922" s="6"/>
       <c r="AL922" s="6"/>
     </row>
-    <row r="923" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="923" spans="1:38" ht="15.95" customHeight="1">
       <c r="A923" s="3"/>
       <c r="B923" s="3"/>
       <c r="C923" s="3"/>
@@ -38203,7 +38209,7 @@
       <c r="AK923" s="6"/>
       <c r="AL923" s="6"/>
     </row>
-    <row r="924" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="924" spans="1:38" ht="15.95" customHeight="1">
       <c r="A924" s="3"/>
       <c r="B924" s="3"/>
       <c r="C924" s="3"/>
@@ -38243,7 +38249,7 @@
       <c r="AK924" s="6"/>
       <c r="AL924" s="6"/>
     </row>
-    <row r="925" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="925" spans="1:38" ht="15.95" customHeight="1">
       <c r="A925" s="3"/>
       <c r="B925" s="3"/>
       <c r="C925" s="3"/>
@@ -38283,7 +38289,7 @@
       <c r="AK925" s="6"/>
       <c r="AL925" s="6"/>
     </row>
-    <row r="926" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="926" spans="1:38" ht="15.95" customHeight="1">
       <c r="A926" s="3"/>
       <c r="B926" s="3"/>
       <c r="C926" s="3"/>
@@ -38323,7 +38329,7 @@
       <c r="AK926" s="6"/>
       <c r="AL926" s="6"/>
     </row>
-    <row r="927" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="927" spans="1:38" ht="15.95" customHeight="1">
       <c r="A927" s="3"/>
       <c r="B927" s="3"/>
       <c r="C927" s="3"/>
@@ -38363,7 +38369,7 @@
       <c r="AK927" s="6"/>
       <c r="AL927" s="6"/>
     </row>
-    <row r="928" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="928" spans="1:38" ht="15.95" customHeight="1">
       <c r="A928" s="3"/>
       <c r="B928" s="3"/>
       <c r="C928" s="3"/>
@@ -38403,7 +38409,7 @@
       <c r="AK928" s="6"/>
       <c r="AL928" s="6"/>
     </row>
-    <row r="929" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="929" spans="1:38" ht="15.95" customHeight="1">
       <c r="A929" s="3"/>
       <c r="B929" s="3"/>
       <c r="C929" s="3"/>
@@ -38443,7 +38449,7 @@
       <c r="AK929" s="6"/>
       <c r="AL929" s="6"/>
     </row>
-    <row r="930" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="930" spans="1:38" ht="15.95" customHeight="1">
       <c r="A930" s="3"/>
       <c r="B930" s="3"/>
       <c r="C930" s="3"/>
@@ -38483,7 +38489,7 @@
       <c r="AK930" s="6"/>
       <c r="AL930" s="6"/>
     </row>
-    <row r="931" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="931" spans="1:38" ht="15.95" customHeight="1">
       <c r="A931" s="3"/>
       <c r="B931" s="3"/>
       <c r="C931" s="3"/>
@@ -38523,7 +38529,7 @@
       <c r="AK931" s="6"/>
       <c r="AL931" s="6"/>
     </row>
-    <row r="932" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="932" spans="1:38" ht="15.95" customHeight="1">
       <c r="A932" s="3"/>
       <c r="B932" s="3"/>
       <c r="C932" s="3"/>
@@ -38563,7 +38569,7 @@
       <c r="AK932" s="6"/>
       <c r="AL932" s="6"/>
     </row>
-    <row r="933" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="933" spans="1:38" ht="15.95" customHeight="1">
       <c r="A933" s="3"/>
       <c r="B933" s="3"/>
       <c r="C933" s="3"/>
@@ -38603,7 +38609,7 @@
       <c r="AK933" s="6"/>
       <c r="AL933" s="6"/>
     </row>
-    <row r="934" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="934" spans="1:38" ht="15.95" customHeight="1">
       <c r="A934" s="3"/>
       <c r="B934" s="3"/>
       <c r="C934" s="3"/>
@@ -38643,7 +38649,7 @@
       <c r="AK934" s="6"/>
       <c r="AL934" s="6"/>
     </row>
-    <row r="935" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="935" spans="1:38" ht="15.95" customHeight="1">
       <c r="A935" s="3"/>
       <c r="B935" s="3"/>
       <c r="C935" s="3"/>
@@ -38683,7 +38689,7 @@
       <c r="AK935" s="6"/>
       <c r="AL935" s="6"/>
     </row>
-    <row r="936" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="936" spans="1:38" ht="15.95" customHeight="1">
       <c r="A936" s="3"/>
       <c r="B936" s="3"/>
       <c r="C936" s="3"/>
@@ -38723,7 +38729,7 @@
       <c r="AK936" s="6"/>
       <c r="AL936" s="6"/>
     </row>
-    <row r="937" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="937" spans="1:38" ht="15.95" customHeight="1">
       <c r="A937" s="3"/>
       <c r="B937" s="3"/>
       <c r="C937" s="3"/>
@@ -38763,7 +38769,7 @@
       <c r="AK937" s="6"/>
       <c r="AL937" s="6"/>
     </row>
-    <row r="938" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="938" spans="1:38" ht="15.95" customHeight="1">
       <c r="A938" s="3"/>
       <c r="B938" s="3"/>
       <c r="C938" s="3"/>
@@ -38803,7 +38809,7 @@
       <c r="AK938" s="6"/>
       <c r="AL938" s="6"/>
     </row>
-    <row r="939" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="939" spans="1:38" ht="15.95" customHeight="1">
       <c r="A939" s="3"/>
       <c r="B939" s="3"/>
       <c r="C939" s="3"/>
@@ -38843,7 +38849,7 @@
       <c r="AK939" s="6"/>
       <c r="AL939" s="6"/>
     </row>
-    <row r="940" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="940" spans="1:38" ht="15.95" customHeight="1">
       <c r="A940" s="3"/>
       <c r="B940" s="3"/>
       <c r="C940" s="3"/>
@@ -38883,7 +38889,7 @@
       <c r="AK940" s="6"/>
       <c r="AL940" s="6"/>
     </row>
-    <row r="941" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="941" spans="1:38" ht="15.95" customHeight="1">
       <c r="A941" s="3"/>
       <c r="B941" s="3"/>
       <c r="C941" s="3"/>
@@ -38923,7 +38929,7 @@
       <c r="AK941" s="6"/>
       <c r="AL941" s="6"/>
     </row>
-    <row r="942" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="942" spans="1:38" ht="15.95" customHeight="1">
       <c r="A942" s="3"/>
       <c r="B942" s="3"/>
       <c r="C942" s="3"/>
@@ -38963,7 +38969,7 @@
       <c r="AK942" s="6"/>
       <c r="AL942" s="6"/>
     </row>
-    <row r="943" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="943" spans="1:38" ht="15.95" customHeight="1">
       <c r="A943" s="3"/>
       <c r="B943" s="3"/>
       <c r="C943" s="3"/>
@@ -39003,7 +39009,7 @@
       <c r="AK943" s="6"/>
       <c r="AL943" s="6"/>
     </row>
-    <row r="944" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="944" spans="1:38" ht="15.95" customHeight="1">
       <c r="A944" s="3"/>
       <c r="B944" s="3"/>
       <c r="C944" s="3"/>
@@ -39043,7 +39049,7 @@
       <c r="AK944" s="6"/>
       <c r="AL944" s="6"/>
     </row>
-    <row r="945" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="945" spans="1:38" ht="15.95" customHeight="1">
       <c r="A945" s="3"/>
       <c r="B945" s="3"/>
       <c r="C945" s="3"/>
@@ -39083,7 +39089,7 @@
       <c r="AK945" s="6"/>
       <c r="AL945" s="6"/>
     </row>
-    <row r="946" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="946" spans="1:38" ht="15.95" customHeight="1">
       <c r="A946" s="3"/>
       <c r="B946" s="3"/>
       <c r="C946" s="3"/>
@@ -39123,7 +39129,7 @@
       <c r="AK946" s="6"/>
       <c r="AL946" s="6"/>
     </row>
-    <row r="947" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="947" spans="1:38" ht="15.95" customHeight="1">
       <c r="A947" s="3"/>
       <c r="B947" s="3"/>
       <c r="C947" s="3"/>
@@ -39163,7 +39169,7 @@
       <c r="AK947" s="6"/>
       <c r="AL947" s="6"/>
     </row>
-    <row r="948" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="948" spans="1:38" ht="15.95" customHeight="1">
       <c r="A948" s="3"/>
       <c r="B948" s="3"/>
       <c r="C948" s="3"/>
@@ -39203,7 +39209,7 @@
       <c r="AK948" s="6"/>
       <c r="AL948" s="6"/>
     </row>
-    <row r="949" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="949" spans="1:38" ht="15.95" customHeight="1">
       <c r="A949" s="3"/>
       <c r="B949" s="3"/>
       <c r="C949" s="3"/>
@@ -39243,7 +39249,7 @@
       <c r="AK949" s="6"/>
       <c r="AL949" s="6"/>
     </row>
-    <row r="950" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="950" spans="1:38" ht="15.95" customHeight="1">
       <c r="A950" s="3"/>
       <c r="B950" s="3"/>
       <c r="C950" s="3"/>
@@ -39283,7 +39289,7 @@
       <c r="AK950" s="6"/>
       <c r="AL950" s="6"/>
     </row>
-    <row r="951" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="951" spans="1:38" ht="15.95" customHeight="1">
       <c r="A951" s="3"/>
       <c r="B951" s="3"/>
       <c r="C951" s="3"/>
@@ -39323,7 +39329,7 @@
       <c r="AK951" s="6"/>
       <c r="AL951" s="6"/>
     </row>
-    <row r="952" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="952" spans="1:38" ht="15.95" customHeight="1">
       <c r="A952" s="3"/>
       <c r="B952" s="3"/>
       <c r="C952" s="3"/>
@@ -39363,7 +39369,7 @@
       <c r="AK952" s="6"/>
       <c r="AL952" s="6"/>
     </row>
-    <row r="953" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="953" spans="1:38" ht="15.95" customHeight="1">
       <c r="A953" s="3"/>
       <c r="B953" s="3"/>
       <c r="C953" s="3"/>
@@ -39403,7 +39409,7 @@
       <c r="AK953" s="6"/>
       <c r="AL953" s="6"/>
     </row>
-    <row r="954" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="954" spans="1:38" ht="15.95" customHeight="1">
       <c r="A954" s="3"/>
       <c r="B954" s="3"/>
       <c r="C954" s="3"/>
@@ -39443,7 +39449,7 @@
       <c r="AK954" s="6"/>
       <c r="AL954" s="6"/>
     </row>
-    <row r="955" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="955" spans="1:38" ht="15.95" customHeight="1">
       <c r="A955" s="3"/>
       <c r="B955" s="3"/>
       <c r="C955" s="3"/>
@@ -39483,7 +39489,7 @@
       <c r="AK955" s="6"/>
       <c r="AL955" s="6"/>
     </row>
-    <row r="956" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="956" spans="1:38" ht="15.95" customHeight="1">
       <c r="A956" s="3"/>
       <c r="B956" s="3"/>
       <c r="C956" s="3"/>
@@ -39523,7 +39529,7 @@
       <c r="AK956" s="6"/>
       <c r="AL956" s="6"/>
     </row>
-    <row r="957" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="957" spans="1:38" ht="15.95" customHeight="1">
       <c r="A957" s="3"/>
       <c r="B957" s="3"/>
       <c r="C957" s="3"/>
@@ -39563,7 +39569,7 @@
       <c r="AK957" s="6"/>
       <c r="AL957" s="6"/>
     </row>
-    <row r="958" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="958" spans="1:38" ht="15.95" customHeight="1">
       <c r="A958" s="3"/>
       <c r="B958" s="3"/>
       <c r="C958" s="3"/>
@@ -39603,7 +39609,7 @@
       <c r="AK958" s="6"/>
       <c r="AL958" s="6"/>
     </row>
-    <row r="959" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="959" spans="1:38" ht="15.95" customHeight="1">
       <c r="A959" s="3"/>
       <c r="B959" s="3"/>
       <c r="C959" s="3"/>
@@ -39643,7 +39649,7 @@
       <c r="AK959" s="6"/>
       <c r="AL959" s="6"/>
     </row>
-    <row r="960" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="960" spans="1:38" ht="15.95" customHeight="1">
       <c r="A960" s="3"/>
       <c r="B960" s="3"/>
       <c r="C960" s="3"/>
@@ -39683,7 +39689,7 @@
       <c r="AK960" s="6"/>
       <c r="AL960" s="6"/>
     </row>
-    <row r="961" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="961" spans="1:38" ht="15.95" customHeight="1">
       <c r="A961" s="3"/>
       <c r="B961" s="3"/>
       <c r="C961" s="3"/>
@@ -39723,7 +39729,7 @@
       <c r="AK961" s="6"/>
       <c r="AL961" s="6"/>
     </row>
-    <row r="962" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="962" spans="1:38" ht="15.95" customHeight="1">
       <c r="A962" s="3"/>
       <c r="B962" s="3"/>
       <c r="C962" s="3"/>
@@ -39763,7 +39769,7 @@
       <c r="AK962" s="6"/>
       <c r="AL962" s="6"/>
     </row>
-    <row r="963" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="963" spans="1:38" ht="15.95" customHeight="1">
       <c r="A963" s="3"/>
       <c r="B963" s="3"/>
       <c r="C963" s="3"/>
@@ -39803,7 +39809,7 @@
       <c r="AK963" s="6"/>
       <c r="AL963" s="6"/>
     </row>
-    <row r="964" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="964" spans="1:38" ht="15.95" customHeight="1">
       <c r="A964" s="3"/>
       <c r="B964" s="3"/>
       <c r="C964" s="3"/>
@@ -39843,7 +39849,7 @@
       <c r="AK964" s="6"/>
       <c r="AL964" s="6"/>
     </row>
-    <row r="965" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="965" spans="1:38" ht="15.95" customHeight="1">
       <c r="A965" s="3"/>
       <c r="B965" s="3"/>
       <c r="C965" s="3"/>
@@ -39883,7 +39889,7 @@
       <c r="AK965" s="6"/>
       <c r="AL965" s="6"/>
     </row>
-    <row r="966" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="966" spans="1:38" ht="15.95" customHeight="1">
       <c r="A966" s="3"/>
       <c r="B966" s="3"/>
       <c r="C966" s="3"/>
@@ -39923,7 +39929,7 @@
       <c r="AK966" s="6"/>
       <c r="AL966" s="6"/>
     </row>
-    <row r="967" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="967" spans="1:38" ht="15.95" customHeight="1">
       <c r="A967" s="3"/>
       <c r="B967" s="3"/>
       <c r="C967" s="3"/>
@@ -39963,7 +39969,7 @@
       <c r="AK967" s="6"/>
       <c r="AL967" s="6"/>
     </row>
-    <row r="968" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="968" spans="1:38" ht="15.95" customHeight="1">
       <c r="A968" s="3"/>
       <c r="B968" s="3"/>
       <c r="C968" s="3"/>
@@ -40003,7 +40009,7 @@
       <c r="AK968" s="6"/>
       <c r="AL968" s="6"/>
     </row>
-    <row r="969" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="969" spans="1:38" ht="15.95" customHeight="1">
       <c r="A969" s="3"/>
       <c r="B969" s="3"/>
       <c r="C969" s="3"/>
@@ -40043,7 +40049,7 @@
       <c r="AK969" s="6"/>
       <c r="AL969" s="6"/>
     </row>
-    <row r="970" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="970" spans="1:38" ht="15.95" customHeight="1">
       <c r="A970" s="3"/>
       <c r="B970" s="3"/>
       <c r="C970" s="3"/>
@@ -40083,7 +40089,7 @@
       <c r="AK970" s="6"/>
       <c r="AL970" s="6"/>
     </row>
-    <row r="971" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="971" spans="1:38" ht="15.95" customHeight="1">
       <c r="A971" s="3"/>
       <c r="B971" s="3"/>
       <c r="C971" s="3"/>
@@ -40123,7 +40129,7 @@
       <c r="AK971" s="6"/>
       <c r="AL971" s="6"/>
     </row>
-    <row r="972" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="972" spans="1:38" ht="15.95" customHeight="1">
       <c r="A972" s="3"/>
       <c r="B972" s="3"/>
       <c r="C972" s="3"/>
@@ -40163,7 +40169,7 @@
       <c r="AK972" s="6"/>
       <c r="AL972" s="6"/>
     </row>
-    <row r="973" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="973" spans="1:38" ht="15.95" customHeight="1">
       <c r="A973" s="3"/>
       <c r="B973" s="3"/>
       <c r="C973" s="3"/>
@@ -40203,7 +40209,7 @@
       <c r="AK973" s="6"/>
       <c r="AL973" s="6"/>
     </row>
-    <row r="974" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="974" spans="1:38" ht="15.95" customHeight="1">
       <c r="A974" s="3"/>
       <c r="B974" s="3"/>
       <c r="C974" s="3"/>
@@ -40243,7 +40249,7 @@
       <c r="AK974" s="6"/>
       <c r="AL974" s="6"/>
     </row>
-    <row r="975" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="975" spans="1:38" ht="15.95" customHeight="1">
       <c r="A975" s="3"/>
       <c r="B975" s="3"/>
       <c r="C975" s="3"/>
@@ -40283,7 +40289,7 @@
       <c r="AK975" s="6"/>
       <c r="AL975" s="6"/>
     </row>
-    <row r="976" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="976" spans="1:38" ht="15.95" customHeight="1">
       <c r="A976" s="3"/>
       <c r="B976" s="3"/>
       <c r="C976" s="3"/>
@@ -40323,7 +40329,7 @@
       <c r="AK976" s="6"/>
       <c r="AL976" s="6"/>
     </row>
-    <row r="977" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="977" spans="1:38" ht="15.95" customHeight="1">
       <c r="A977" s="3"/>
       <c r="B977" s="3"/>
       <c r="C977" s="3"/>
@@ -40363,7 +40369,7 @@
       <c r="AK977" s="6"/>
       <c r="AL977" s="6"/>
     </row>
-    <row r="978" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="978" spans="1:38" ht="15.95" customHeight="1">
       <c r="A978" s="3"/>
       <c r="B978" s="3"/>
       <c r="C978" s="3"/>
@@ -40403,7 +40409,7 @@
       <c r="AK978" s="6"/>
       <c r="AL978" s="6"/>
     </row>
-    <row r="979" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="979" spans="1:38" ht="15.95" customHeight="1">
       <c r="A979" s="3"/>
       <c r="B979" s="3"/>
       <c r="C979" s="3"/>
@@ -40443,7 +40449,7 @@
       <c r="AK979" s="6"/>
       <c r="AL979" s="6"/>
     </row>
-    <row r="980" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="980" spans="1:38" ht="15.95" customHeight="1">
       <c r="A980" s="3"/>
       <c r="B980" s="3"/>
       <c r="C980" s="3"/>
@@ -40483,7 +40489,7 @@
       <c r="AK980" s="6"/>
       <c r="AL980" s="6"/>
     </row>
-    <row r="981" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="981" spans="1:38" ht="15.95" customHeight="1">
       <c r="A981" s="3"/>
       <c r="B981" s="3"/>
       <c r="C981" s="3"/>
@@ -40523,7 +40529,7 @@
       <c r="AK981" s="6"/>
       <c r="AL981" s="6"/>
     </row>
-    <row r="982" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="982" spans="1:38" ht="15.95" customHeight="1">
       <c r="A982" s="3"/>
       <c r="B982" s="3"/>
       <c r="C982" s="3"/>
@@ -40563,7 +40569,7 @@
       <c r="AK982" s="6"/>
       <c r="AL982" s="6"/>
     </row>
-    <row r="983" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="983" spans="1:38" ht="15.95" customHeight="1">
       <c r="A983" s="3"/>
       <c r="B983" s="3"/>
       <c r="C983" s="3"/>
@@ -40603,7 +40609,7 @@
       <c r="AK983" s="6"/>
       <c r="AL983" s="6"/>
     </row>
-    <row r="984" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="984" spans="1:38" ht="15.95" customHeight="1">
       <c r="A984" s="3"/>
       <c r="B984" s="3"/>
       <c r="C984" s="3"/>
@@ -40643,7 +40649,7 @@
       <c r="AK984" s="6"/>
       <c r="AL984" s="6"/>
     </row>
-    <row r="985" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="985" spans="1:38" ht="15.95" customHeight="1">
       <c r="A985" s="3"/>
       <c r="B985" s="3"/>
       <c r="C985" s="3"/>
@@ -40683,7 +40689,7 @@
       <c r="AK985" s="6"/>
       <c r="AL985" s="6"/>
     </row>
-    <row r="986" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="986" spans="1:38" ht="15.95" customHeight="1">
       <c r="A986" s="3"/>
       <c r="B986" s="3"/>
       <c r="C986" s="3"/>
@@ -40723,7 +40729,7 @@
       <c r="AK986" s="6"/>
       <c r="AL986" s="6"/>
     </row>
-    <row r="987" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="987" spans="1:38" ht="15.95" customHeight="1">
       <c r="A987" s="3"/>
       <c r="B987" s="3"/>
       <c r="C987" s="3"/>
@@ -40763,7 +40769,7 @@
       <c r="AK987" s="6"/>
       <c r="AL987" s="6"/>
     </row>
-    <row r="988" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="988" spans="1:38" ht="15.95" customHeight="1">
       <c r="A988" s="3"/>
       <c r="B988" s="3"/>
       <c r="C988" s="3"/>
@@ -40803,7 +40809,7 @@
       <c r="AK988" s="6"/>
       <c r="AL988" s="6"/>
     </row>
-    <row r="989" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="989" spans="1:38" ht="15.95" customHeight="1">
       <c r="A989" s="3"/>
       <c r="B989" s="3"/>
       <c r="C989" s="3"/>
@@ -40843,7 +40849,7 @@
       <c r="AK989" s="6"/>
       <c r="AL989" s="6"/>
     </row>
-    <row r="990" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="990" spans="1:38" ht="15.95" customHeight="1">
       <c r="A990" s="3"/>
       <c r="B990" s="3"/>
       <c r="C990" s="3"/>
@@ -40883,7 +40889,7 @@
       <c r="AK990" s="6"/>
       <c r="AL990" s="6"/>
     </row>
-    <row r="991" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="991" spans="1:38" ht="15.95" customHeight="1">
       <c r="A991" s="3"/>
       <c r="B991" s="3"/>
       <c r="C991" s="3"/>
@@ -40923,7 +40929,7 @@
       <c r="AK991" s="6"/>
       <c r="AL991" s="6"/>
     </row>
-    <row r="992" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="992" spans="1:38" ht="15.95" customHeight="1">
       <c r="A992" s="3"/>
       <c r="B992" s="3"/>
       <c r="C992" s="3"/>
@@ -40963,7 +40969,7 @@
       <c r="AK992" s="6"/>
       <c r="AL992" s="6"/>
     </row>
-    <row r="993" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="993" spans="1:38" ht="15.95" customHeight="1">
       <c r="A993" s="3"/>
       <c r="B993" s="3"/>
       <c r="C993" s="3"/>
@@ -41003,7 +41009,7 @@
       <c r="AK993" s="6"/>
       <c r="AL993" s="6"/>
     </row>
-    <row r="994" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="994" spans="1:38" ht="15.95" customHeight="1">
       <c r="A994" s="3"/>
       <c r="B994" s="3"/>
       <c r="C994" s="3"/>
@@ -41043,7 +41049,7 @@
       <c r="AK994" s="6"/>
       <c r="AL994" s="6"/>
     </row>
-    <row r="995" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="995" spans="1:38" ht="15.95" customHeight="1">
       <c r="A995" s="3"/>
       <c r="B995" s="3"/>
       <c r="C995" s="3"/>
@@ -41083,7 +41089,7 @@
       <c r="AK995" s="6"/>
       <c r="AL995" s="6"/>
     </row>
-    <row r="996" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="996" spans="1:38" ht="15.95" customHeight="1">
       <c r="A996" s="3"/>
       <c r="B996" s="3"/>
       <c r="C996" s="3"/>
@@ -41123,7 +41129,7 @@
       <c r="AK996" s="6"/>
       <c r="AL996" s="6"/>
     </row>
-    <row r="997" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="997" spans="1:38" ht="15.95" customHeight="1">
       <c r="A997" s="3"/>
       <c r="B997" s="3"/>
       <c r="C997" s="3"/>
@@ -41163,7 +41169,7 @@
       <c r="AK997" s="6"/>
       <c r="AL997" s="6"/>
     </row>
-    <row r="998" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="998" spans="1:38" ht="15.95" customHeight="1">
       <c r="A998" s="3"/>
       <c r="B998" s="3"/>
       <c r="C998" s="3"/>
@@ -41203,7 +41209,7 @@
       <c r="AK998" s="6"/>
       <c r="AL998" s="6"/>
     </row>
-    <row r="999" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="999" spans="1:38" ht="15.95" customHeight="1">
       <c r="A999" s="3"/>
       <c r="B999" s="3"/>
       <c r="C999" s="3"/>
@@ -41243,7 +41249,7 @@
       <c r="AK999" s="6"/>
       <c r="AL999" s="6"/>
     </row>
-    <row r="1000" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1000" spans="1:38" ht="15.95" customHeight="1">
       <c r="A1000" s="3"/>
       <c r="B1000" s="3"/>
       <c r="C1000" s="3"/>
@@ -41291,6 +41297,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -41301,15 +41316,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -41570,44 +41576,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44B7B1D8-F3F2-46A8-A792-B679C78EEEEB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="06a0b0f5-ab3f-4382-8730-459fb424e421"/>
-    <ds:schemaRef ds:uri="26f1519c-0a18-4175-bd8e-760b6597752e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D55B629F-9BAD-43E6-819F-B097A47F8C05}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D55B629F-9BAD-43E6-819F-B097A47F8C05}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44B7B1D8-F3F2-46A8-A792-B679C78EEEEB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8DF6AE6-9ACD-4783-B2E6-E54A88049822}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="26f1519c-0a18-4175-bd8e-760b6597752e"/>
-    <ds:schemaRef ds:uri="def454d3-7361-4a53-bd39-35a8c96a39c0"/>
-    <ds:schemaRef ds:uri="06a0b0f5-ab3f-4382-8730-459fb424e421"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8DF6AE6-9ACD-4783-B2E6-E54A88049822}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
